--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -994,7 +994,7 @@
         <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
         <v>2.88</v>
@@ -1006,19 +1006,19 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AD4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG4">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U5">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="V5">
         <v>1.36</v>
@@ -1163,10 +1163,10 @@
         <v>3.4</v>
       </c>
       <c r="AA5">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
         <v>3.35</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
         <v>2.45</v>
@@ -1317,22 +1317,22 @@
         <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB6">
         <v>2.4</v>
       </c>
       <c r="AC6">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD6">
         <v>1.53</v>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>1.95</v>
       </c>
       <c r="Q7">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
       <c r="R7">
         <v>2.38</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="O10">
         <v>3.38</v>
@@ -1951,22 +1951,22 @@
         <v>2.86</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S10">
         <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1.05</v>
@@ -1975,7 +1975,7 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA10">
         <v>1.91</v>
@@ -1990,13 +1990,13 @@
         <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
         <v>1.57</v>
@@ -2114,13 +2114,13 @@
         <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
         <v>2.75</v>
@@ -2147,7 +2147,7 @@
         <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AD11">
         <v>1.35</v>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,19 +2274,19 @@
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R12">
         <v>2.11</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T12">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="U12">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="V12">
         <v>1.32</v>
@@ -2298,13 +2298,13 @@
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z12">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA12">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AB12">
         <v>1.63</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="O14">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="P14">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -2606,13 +2606,13 @@
         <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
         <v>2.85</v>
       </c>
       <c r="U14">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
         <v>1.42</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
         <v>3</v>
@@ -4224,10 +4224,10 @@
         <v>1.54</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q24">
         <v>2.02</v>
@@ -4254,7 +4254,7 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -4263,13 +4263,13 @@
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AC24">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AD24">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE24">
         <v>1.16</v>
@@ -4414,7 +4414,7 @@
         <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
         <v>1.25</v>
@@ -4429,7 +4429,7 @@
         <v>1.93</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD25">
         <v>1.33</v>
@@ -4601,10 +4601,10 @@
         <v>1.03</v>
       </c>
       <c r="AF26">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG26">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5392,13 +5392,13 @@
         <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
         <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA31">
         <v>2.2</v>
@@ -5407,13 +5407,13 @@
         <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD31">
         <v>1.18</v>
       </c>
       <c r="AE31">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
         <v>1.88</v>
@@ -7004,7 +7004,7 @@
         <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
         <v>1.33</v>
@@ -7656,7 +7656,7 @@
         <v>2</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
         <v>1.33</v>
@@ -7671,7 +7671,7 @@
         <v>1.44</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7686,13 +7686,13 @@
         <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC45">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
         <v>1.13</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
         <v>2.3</v>
@@ -8954,10 +8954,10 @@
         <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q53">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="R53">
         <v>2.25</v>
@@ -8966,13 +8966,13 @@
         <v>1.3</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U53">
         <v>2.45</v>
       </c>
       <c r="V53">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
         <v>1.08</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>8.07</v>
+        <v>7.5</v>
       </c>
       <c r="O54">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P54">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q54">
         <v>7</v>
       </c>
       <c r="R54">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,22 +9132,22 @@
         <v>3.75</v>
       </c>
       <c r="U54">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V54">
         <v>1.64</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA54">
         <v>1.45</v>
@@ -9165,10 +9165,10 @@
         <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG54">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
         <v>3.3</v>
@@ -9313,13 +9313,13 @@
         <v>4</v>
       </c>
       <c r="AA55">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB55">
         <v>2</v>
       </c>
       <c r="AC55">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD55">
         <v>1.35</v>
@@ -9458,13 +9458,13 @@
         <v>2.75</v>
       </c>
       <c r="U56">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V56">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W56">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
         <v>1.06</v>
@@ -9476,7 +9476,7 @@
         <v>3.25</v>
       </c>
       <c r="AA56">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB56">
         <v>1.66</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="O57">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>3.03</v>
+        <v>2.68</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -9615,49 +9615,49 @@
         <v>2.25</v>
       </c>
       <c r="S57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U57">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="V57">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W57">
         <v>1.1</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z57">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA57">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB57">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC57">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD57">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG57">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK57">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9787,10 +9787,10 @@
         <v>2.45</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X58">
         <v>1.01</v>
@@ -9808,13 +9808,13 @@
         <v>2.07</v>
       </c>
       <c r="AC58">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD58">
         <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF58">
         <v>1.77</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10107,10 +10107,10 @@
         <v>1.26</v>
       </c>
       <c r="T60">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U60">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="V60">
         <v>1.59</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
         <v>2.1</v>
       </c>
-      <c r="O61">
-        <v>3.75</v>
-      </c>
-      <c r="P61">
-        <v>2.82</v>
-      </c>
-      <c r="Q61">
-        <v>2.4</v>
-      </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="V61">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA61">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AB61">
-        <v>2.48</v>
+        <v>3.16</v>
       </c>
       <c r="AC61">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD61">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AG61">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q62">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA62">
+        <v>1.5</v>
+      </c>
+      <c r="AB62">
+        <v>2.48</v>
+      </c>
+      <c r="AC62">
+        <v>2.2</v>
+      </c>
+      <c r="AD62">
+        <v>1.62</v>
+      </c>
+      <c r="AE62">
+        <v>1.22</v>
+      </c>
+      <c r="AF62">
+        <v>1.41</v>
+      </c>
+      <c r="AG62">
+        <v>2.7</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.33</v>
       </c>
-      <c r="AB62">
-        <v>3.15</v>
-      </c>
-      <c r="AC62">
-        <v>1.91</v>
-      </c>
-      <c r="AD62">
-        <v>1.9</v>
-      </c>
-      <c r="AE62">
-        <v>1.25</v>
-      </c>
-      <c r="AF62">
-        <v>1.39</v>
-      </c>
-      <c r="AG62">
-        <v>2.88</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.2</v>
-      </c>
       <c r="AK62">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P63">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
       <c r="Q63">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R63">
         <v>2.7</v>
@@ -10599,25 +10599,25 @@
         <v>3.75</v>
       </c>
       <c r="U63">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V63">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z63">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB63">
         <v>2.85</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10910,7 +10910,7 @@
         <v>3.22</v>
       </c>
       <c r="P65">
-        <v>3.26</v>
+        <v>3.07</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -10940,7 +10940,7 @@
         <v>1.4</v>
       </c>
       <c r="Z65">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AA65">
         <v>2.35</v>
@@ -10949,7 +10949,7 @@
         <v>1.7</v>
       </c>
       <c r="AC65">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="AD65">
         <v>1.18</v>
@@ -10958,10 +10958,10 @@
         <v>1.01</v>
       </c>
       <c r="AF65">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG65">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>3</v>
       </c>
       <c r="P66">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q66">
         <v>3.3</v>
@@ -11097,7 +11097,7 @@
         <v>1.04</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
         <v>1.3</v>
@@ -11106,10 +11106,10 @@
         <v>3.4</v>
       </c>
       <c r="AA66">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
         <v>3.5</v>
@@ -11121,7 +11121,7 @@
         <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
         <v>1.85</v>
@@ -11287,7 +11287,7 @@
         <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="O69">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="P69">
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="O70">
         <v>3.6</v>
@@ -11734,10 +11734,10 @@
         <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T70">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="U70">
         <v>2.5</v>
@@ -11749,7 +11749,7 @@
         <v>1.1</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
         <v>1.22</v>
@@ -11758,13 +11758,13 @@
         <v>3.6</v>
       </c>
       <c r="AA70">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB70">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC70">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD70">
         <v>1.36</v>
@@ -11773,10 +11773,10 @@
         <v>1.08</v>
       </c>
       <c r="AF70">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>2.03</v>
       </c>
       <c r="AD71">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AE71">
         <v>1.29</v>
@@ -12051,13 +12051,13 @@
         <v>3.15</v>
       </c>
       <c r="P72">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="Q72">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="R72">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S72">
         <v>1.44</v>
@@ -12087,7 +12087,7 @@
         <v>2.2</v>
       </c>
       <c r="AB72">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC72">
         <v>3.8</v>
@@ -12118,7 +12118,7 @@
         <v>1.34</v>
       </c>
       <c r="AK72">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,19 +12217,19 @@
         <v>3.5</v>
       </c>
       <c r="Q73">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="R73">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S73">
         <v>1.45</v>
       </c>
       <c r="T73">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U73">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="V73">
         <v>1.32</v>
@@ -12244,13 +12244,13 @@
         <v>1.38</v>
       </c>
       <c r="Z73">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA73">
         <v>2.17</v>
       </c>
       <c r="AB73">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC73">
         <v>3.75</v>
@@ -12374,7 +12374,7 @@
         <v>1.65</v>
       </c>
       <c r="O74">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
         <v>4.5</v>
@@ -12389,7 +12389,7 @@
         <v>1.42</v>
       </c>
       <c r="T74">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U74">
         <v>3</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK74">
         <v>2.1</v>
@@ -12706,13 +12706,13 @@
         <v>5</v>
       </c>
       <c r="Q76">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R76">
         <v>2.23</v>
       </c>
       <c r="S76">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
         <v>2.85</v>
@@ -12721,7 +12721,7 @@
         <v>3.08</v>
       </c>
       <c r="V76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W76">
         <v>1.05</v>
@@ -12733,13 +12733,13 @@
         <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="AA76">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AB76">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC76">
         <v>3.48</v>
@@ -12751,7 +12751,7 @@
         <v>1.09</v>
       </c>
       <c r="AF76">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
         <v>1.85</v>
@@ -13195,7 +13195,7 @@
         <v>2.85</v>
       </c>
       <c r="Q79">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R79">
         <v>2</v>
@@ -13204,7 +13204,7 @@
         <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U79">
         <v>3</v>
@@ -13234,7 +13234,7 @@
         <v>3.7</v>
       </c>
       <c r="AD79">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
         <v>1.1</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK79">
         <v>1.57</v>
@@ -13352,10 +13352,10 @@
         <v>3.3</v>
       </c>
       <c r="O80">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q80">
         <v>4</v>
@@ -13373,7 +13373,7 @@
         <v>2.16</v>
       </c>
       <c r="V80">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W80">
         <v>1.15</v>
@@ -13515,7 +13515,7 @@
         <v>1.64</v>
       </c>
       <c r="O81">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P81">
         <v>4.6</v>
@@ -13548,16 +13548,16 @@
         <v>1.17</v>
       </c>
       <c r="Z81">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="AA81">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB81">
         <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD81">
         <v>1.5</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB83">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14182,7 +14182,7 @@
         <v>1.43</v>
       </c>
       <c r="T85">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U85">
         <v>2.87</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="O87">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P87">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q87">
         <v>2.91</v>
@@ -14541,7 +14541,7 @@
         <v>1.6</v>
       </c>
       <c r="AE87">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF87">
         <v>1.44</v>
@@ -15021,7 +15021,7 @@
         <v>1.83</v>
       </c>
       <c r="AB90">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC90">
         <v>3.1</v>
@@ -15151,10 +15151,10 @@
         <v>4.55</v>
       </c>
       <c r="Q91">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="R91">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="S91">
         <v>1.24</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK91">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15646,16 +15646,16 @@
         <v>2</v>
       </c>
       <c r="S94">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T94">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="U94">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="V94">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W94">
         <v>1.03</v>
@@ -15797,22 +15797,22 @@
         <v>1.95</v>
       </c>
       <c r="O95">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P95">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q95">
         <v>2.3</v>
       </c>
       <c r="R95">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S95">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T95">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U95">
         <v>2.9</v>
@@ -15836,10 +15836,10 @@
         <v>2.2</v>
       </c>
       <c r="AB95">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC95">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AD95">
         <v>1.22</v>
@@ -15867,7 +15867,7 @@
         <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O96">
         <v>3.6</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,25 +16120,25 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R97">
         <v>1.83</v>
       </c>
       <c r="S97">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T97">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="U97">
         <v>3.75</v>
@@ -16147,37 +16147,37 @@
         <v>1.22</v>
       </c>
       <c r="W97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y97">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Z97">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA97">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AB97">
         <v>1.4</v>
       </c>
       <c r="AC97">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AD97">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE97">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG97">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,25 +16283,25 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R98">
         <v>1.83</v>
       </c>
       <c r="S98">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T98">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="U98">
         <v>3.75</v>
@@ -16310,37 +16310,37 @@
         <v>1.22</v>
       </c>
       <c r="W98">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y98">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Z98">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA98">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AB98">
         <v>1.4</v>
       </c>
       <c r="AC98">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AD98">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE98">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG98">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK98">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,7 +16455,7 @@
         <v>7.17</v>
       </c>
       <c r="Q99">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R99">
         <v>2.4</v>
@@ -16500,10 +16500,10 @@
         <v>1.13</v>
       </c>
       <c r="AF99">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG99">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.09</v>
       </c>
       <c r="AK99">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16663,7 +16663,7 @@
         <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG100">
         <v>1.83</v>
@@ -16787,10 +16787,10 @@
         <v>2.04</v>
       </c>
       <c r="S101">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U101">
         <v>2.62</v>
@@ -16953,7 +16953,7 @@
         <v>1.37</v>
       </c>
       <c r="T102">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U102">
         <v>2.75</v>
@@ -17107,7 +17107,7 @@
         <v>5.04</v>
       </c>
       <c r="Q103">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R103">
         <v>2.3</v>
@@ -17146,7 +17146,7 @@
         <v>2.49</v>
       </c>
       <c r="AD103">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE103">
         <v>1.13</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="R105">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T105">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U105">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.5</v>
       </c>
       <c r="W105">
+        <v>1.08</v>
+      </c>
+      <c r="X105">
+        <v>1.03</v>
+      </c>
+      <c r="Y105">
+        <v>1.17</v>
+      </c>
+      <c r="Z105">
+        <v>3.96</v>
+      </c>
+      <c r="AA105">
+        <v>1.69</v>
+      </c>
+      <c r="AB105">
+        <v>2.04</v>
+      </c>
+      <c r="AC105">
+        <v>2.7</v>
+      </c>
+      <c r="AD105">
+        <v>1.36</v>
+      </c>
+      <c r="AE105">
         <v>1.1</v>
       </c>
-      <c r="X105">
-        <v>1.02</v>
-      </c>
-      <c r="Y105">
-        <v>1.2</v>
-      </c>
-      <c r="Z105">
-        <v>4.5</v>
-      </c>
-      <c r="AA105">
-        <v>1.64</v>
-      </c>
-      <c r="AB105">
-        <v>2.2</v>
-      </c>
-      <c r="AC105">
-        <v>2.63</v>
-      </c>
-      <c r="AD105">
-        <v>1.47</v>
-      </c>
-      <c r="AE105">
-        <v>1.17</v>
-      </c>
       <c r="AF105">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG105">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK105">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17599,7 +17599,7 @@
         <v>2.96</v>
       </c>
       <c r="R106">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S106">
         <v>1.35</v>
@@ -17608,7 +17608,7 @@
         <v>2.92</v>
       </c>
       <c r="U106">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V106">
         <v>1.4</v>
@@ -17629,7 +17629,7 @@
         <v>1.86</v>
       </c>
       <c r="AB106">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC106">
         <v>3.25</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
         <v>1.47</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="R107">
+        <v>2.31</v>
+      </c>
+      <c r="S107">
+        <v>1.28</v>
+      </c>
+      <c r="T107">
+        <v>3.18</v>
+      </c>
+      <c r="U107">
         <v>2.4</v>
-      </c>
-      <c r="S107">
-        <v>1.29</v>
-      </c>
-      <c r="T107">
-        <v>3.3</v>
-      </c>
-      <c r="U107">
-        <v>2.55</v>
       </c>
       <c r="V107">
         <v>1.5</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>4.5</v>
+      </c>
+      <c r="AA107">
+        <v>1.64</v>
+      </c>
+      <c r="AB107">
+        <v>2.2</v>
+      </c>
+      <c r="AC107">
+        <v>2.63</v>
+      </c>
+      <c r="AD107">
+        <v>1.47</v>
+      </c>
+      <c r="AE107">
         <v>1.17</v>
       </c>
-      <c r="Z107">
-        <v>3.96</v>
-      </c>
-      <c r="AA107">
-        <v>1.69</v>
-      </c>
-      <c r="AB107">
-        <v>2.04</v>
-      </c>
-      <c r="AC107">
-        <v>2.7</v>
-      </c>
-      <c r="AD107">
-        <v>1.36</v>
-      </c>
-      <c r="AE107">
-        <v>1.1</v>
-      </c>
       <c r="AF107">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.55</v>
+        <v>1.11</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R109">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S109">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T109">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="U109">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="V109">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="W109">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y109">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z109">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="AA109">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB109">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC109">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD109">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE109">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF109">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG109">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,65 +18239,65 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q110">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="R110">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S110">
+        <v>1.55</v>
+      </c>
+      <c r="T110">
+        <v>2.39</v>
+      </c>
+      <c r="U110">
+        <v>3.42</v>
+      </c>
+      <c r="V110">
+        <v>1.23</v>
+      </c>
+      <c r="W110">
+        <v>1.01</v>
+      </c>
+      <c r="X110">
+        <v>1.11</v>
+      </c>
+      <c r="Y110">
+        <v>1.47</v>
+      </c>
+      <c r="Z110">
+        <v>2.4</v>
+      </c>
+      <c r="AA110">
+        <v>2.5</v>
+      </c>
+      <c r="AB110">
         <v>1.44</v>
       </c>
-      <c r="T110">
-        <v>2.53</v>
-      </c>
-      <c r="U110">
-        <v>3.03</v>
-      </c>
-      <c r="V110">
-        <v>1.34</v>
-      </c>
-      <c r="W110">
-        <v>1.06</v>
-      </c>
-      <c r="X110">
+      <c r="AC110">
+        <v>5</v>
+      </c>
+      <c r="AD110">
+        <v>1.14</v>
+      </c>
+      <c r="AE110">
         <v>1.04</v>
       </c>
-      <c r="Y110">
-        <v>1.35</v>
-      </c>
-      <c r="Z110">
-        <v>3.03</v>
-      </c>
-      <c r="AA110">
-        <v>2.05</v>
-      </c>
-      <c r="AB110">
+      <c r="AF110">
+        <v>2</v>
+      </c>
+      <c r="AG110">
         <v>1.7</v>
       </c>
-      <c r="AC110">
-        <v>3.8</v>
-      </c>
-      <c r="AD110">
-        <v>1.2</v>
-      </c>
-      <c r="AE110">
-        <v>1.07</v>
-      </c>
-      <c r="AF110">
-        <v>1.85</v>
-      </c>
-      <c r="AG110">
-        <v>1.83</v>
-      </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O111">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P111">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q111">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S111">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T111">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="U111">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="V111">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W111">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X111">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y111">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z111">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA111">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB111">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC111">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD111">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE111">
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG111">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK111">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,19 +18565,19 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="O112">
         <v>3.05</v>
       </c>
       <c r="P112">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="Q112">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="R112">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S112">
         <v>1.42</v>
@@ -18598,10 +18598,10 @@
         <v>1.07</v>
       </c>
       <c r="Y112">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z112">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AA112">
         <v>2.3</v>
@@ -18731,7 +18731,7 @@
         <v>2.74</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="P113">
         <v>2.81</v>
@@ -18746,7 +18746,7 @@
         <v>1.43</v>
       </c>
       <c r="T113">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U113">
         <v>2.99</v>
@@ -18764,19 +18764,19 @@
         <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="AA113">
         <v>2.09</v>
       </c>
       <c r="AB113">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC113">
         <v>3.58</v>
       </c>
       <c r="AD113">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE113">
         <v>1.04</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O114">
         <v>5.5</v>
       </c>
       <c r="P114">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -18933,7 +18933,7 @@
         <v>1.38</v>
       </c>
       <c r="AB114">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="AC114">
         <v>2.07</v>
@@ -19066,7 +19066,7 @@
         <v>1.78</v>
       </c>
       <c r="R115">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S115">
         <v>1.28</v>
@@ -19087,16 +19087,16 @@
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z115">
         <v>3.82</v>
       </c>
       <c r="AA115">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB115">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC115">
         <v>2.59</v>
@@ -19127,7 +19127,7 @@
         <v>1.12</v>
       </c>
       <c r="AK115">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1.22</v>
       </c>
       <c r="R116">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="S116">
         <v>1.08</v>
@@ -19241,7 +19241,7 @@
         <v>1.61</v>
       </c>
       <c r="V116">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="W116">
         <v>1.36</v>
@@ -19262,13 +19262,13 @@
         <v>5</v>
       </c>
       <c r="AC116">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD116">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AE116">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF116">
         <v>2.7</v>
@@ -19597,7 +19597,7 @@
         <v>1</v>
       </c>
       <c r="AF118">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG118">
         <v>1.72</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,31 +20032,31 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T121">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U121">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="V121">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W121">
         <v>0</v>
@@ -20065,31 +20065,31 @@
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z121">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB121">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC121">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD121">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE121">
         <v>0</v>
       </c>
       <c r="AF121">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG121">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK121">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,31 +20195,31 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W122">
         <v>0</v>
@@ -20228,31 +20228,31 @@
         <v>0</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE122">
         <v>0</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,31 +20358,31 @@
         </is>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O123">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q123">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="R123">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S123">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T123">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U123">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V123">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W123">
         <v>0</v>
@@ -20391,31 +20391,31 @@
         <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z123">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AA123">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB123">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC123">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD123">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE123">
         <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG123">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK123">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,31 +20521,31 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O124">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
+        <v>2.5</v>
+      </c>
+      <c r="Q124">
+        <v>3.38</v>
+      </c>
+      <c r="R124">
+        <v>2.03</v>
+      </c>
+      <c r="S124">
+        <v>1.35</v>
+      </c>
+      <c r="T124">
         <v>2.8</v>
       </c>
-      <c r="Q124">
-        <v>3.2</v>
-      </c>
-      <c r="R124">
-        <v>1.93</v>
-      </c>
-      <c r="S124">
-        <v>1.45</v>
-      </c>
-      <c r="T124">
-        <v>2.44</v>
-      </c>
       <c r="U124">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V124">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W124">
         <v>0</v>
@@ -20554,31 +20554,31 @@
         <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z124">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AA124">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB124">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AC124">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD124">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE124">
         <v>0</v>
       </c>
       <c r="AF124">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG124">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK124">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,31 +20684,31 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="O125">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P125">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q125">
-        <v>3.38</v>
+        <v>2.32</v>
       </c>
       <c r="R125">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="S125">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T125">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U125">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V125">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W125">
         <v>0</v>
@@ -20717,47 +20717,47 @@
         <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z125">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA125">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB125">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC125">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD125">
+        <v>1.24</v>
+      </c>
+      <c r="AE125">
+        <v>0</v>
+      </c>
+      <c r="AF125">
+        <v>1.83</v>
+      </c>
+      <c r="AG125">
+        <v>1.84</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.22</v>
       </c>
-      <c r="AE125">
-        <v>0</v>
-      </c>
-      <c r="AF125">
-        <v>1.87</v>
-      </c>
-      <c r="AG125">
-        <v>1.8</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.25</v>
-      </c>
       <c r="AK125">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Vitória Setúbal</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G127">
@@ -21019,22 +21019,22 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S127">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T127">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U127">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V127">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W127">
         <v>0</v>
@@ -21043,31 +21043,31 @@
         <v>0</v>
       </c>
       <c r="Y127">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z127">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA127">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB127">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC127">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD127">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE127">
         <v>0</v>
       </c>
       <c r="AF127">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG127">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK127">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vitória Setúbal</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O129">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P129">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W129">
         <v>0</v>
@@ -21369,31 +21369,31 @@
         <v>0</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE129">
         <v>0</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,19 +21499,19 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q130">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="R130">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S130">
         <v>1.4</v>
@@ -21520,10 +21520,10 @@
         <v>2.6</v>
       </c>
       <c r="U130">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="V130">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W130">
         <v>0</v>
@@ -21532,22 +21532,22 @@
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z130">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA130">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB130">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC130">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AD130">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE130">
         <v>0</v>
@@ -21556,7 +21556,7 @@
         <v>1.83</v>
       </c>
       <c r="AG130">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK130">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,31 +21662,31 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>2.58</v>
+        <v>3.24</v>
       </c>
       <c r="R131">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S131">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U131">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="V131">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W131">
         <v>0</v>
@@ -21695,31 +21695,31 @@
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z131">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA131">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB131">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC131">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD131">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE131">
         <v>0</v>
       </c>
       <c r="AF131">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG131">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="O134">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>3.46</v>
+        <v>5.3</v>
       </c>
       <c r="Q134">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="R134">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="S134">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="T134">
-        <v>2.31</v>
+        <v>2.92</v>
       </c>
       <c r="U134">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="V134">
+        <v>1.38</v>
+      </c>
+      <c r="W134">
+        <v>1.04</v>
+      </c>
+      <c r="X134">
+        <v>1.01</v>
+      </c>
+      <c r="Y134">
+        <v>1.28</v>
+      </c>
+      <c r="Z134">
+        <v>3.37</v>
+      </c>
+      <c r="AA134">
+        <v>2</v>
+      </c>
+      <c r="AB134">
+        <v>1.76</v>
+      </c>
+      <c r="AC134">
+        <v>3.28</v>
+      </c>
+      <c r="AD134">
         <v>1.25</v>
       </c>
-      <c r="W134">
-        <v>1.01</v>
-      </c>
-      <c r="X134">
-        <v>1.06</v>
-      </c>
-      <c r="Y134">
-        <v>1.47</v>
-      </c>
-      <c r="Z134">
-        <v>2.66</v>
-      </c>
-      <c r="AA134">
-        <v>2.47</v>
-      </c>
-      <c r="AB134">
-        <v>1.53</v>
-      </c>
-      <c r="AC134">
-        <v>4.33</v>
-      </c>
-      <c r="AD134">
-        <v>1.18</v>
-      </c>
       <c r="AE134">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF134">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AG134">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK134">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
+        <v>2.05</v>
+      </c>
+      <c r="O135">
+        <v>3</v>
+      </c>
+      <c r="P135">
+        <v>3.46</v>
+      </c>
+      <c r="Q135">
+        <v>2.54</v>
+      </c>
+      <c r="R135">
+        <v>2.01</v>
+      </c>
+      <c r="S135">
+        <v>1.55</v>
+      </c>
+      <c r="T135">
+        <v>2.33</v>
+      </c>
+      <c r="U135">
+        <v>3.36</v>
+      </c>
+      <c r="V135">
+        <v>1.25</v>
+      </c>
+      <c r="W135">
+        <v>1.01</v>
+      </c>
+      <c r="X135">
+        <v>1.06</v>
+      </c>
+      <c r="Y135">
+        <v>1.47</v>
+      </c>
+      <c r="Z135">
+        <v>2.65</v>
+      </c>
+      <c r="AA135">
+        <v>2.48</v>
+      </c>
+      <c r="AB135">
+        <v>1.53</v>
+      </c>
+      <c r="AC135">
+        <v>4.4</v>
+      </c>
+      <c r="AD135">
+        <v>1.18</v>
+      </c>
+      <c r="AE135">
+        <v>1.01</v>
+      </c>
+      <c r="AF135">
+        <v>2.05</v>
+      </c>
+      <c r="AG135">
+        <v>1.69</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>1.27</v>
+      </c>
+      <c r="AK135">
         <v>1.68</v>
-      </c>
-      <c r="O135">
-        <v>3.55</v>
-      </c>
-      <c r="P135">
-        <v>5.3</v>
-      </c>
-      <c r="Q135">
-        <v>2.27</v>
-      </c>
-      <c r="R135">
-        <v>2.24</v>
-      </c>
-      <c r="S135">
-        <v>1.39</v>
-      </c>
-      <c r="T135">
-        <v>2.9</v>
-      </c>
-      <c r="U135">
-        <v>2.99</v>
-      </c>
-      <c r="V135">
-        <v>1.37</v>
-      </c>
-      <c r="W135">
-        <v>1.03</v>
-      </c>
-      <c r="X135">
-        <v>1.01</v>
-      </c>
-      <c r="Y135">
-        <v>1.28</v>
-      </c>
-      <c r="Z135">
-        <v>3.34</v>
-      </c>
-      <c r="AA135">
-        <v>2</v>
-      </c>
-      <c r="AB135">
-        <v>1.76</v>
-      </c>
-      <c r="AC135">
-        <v>3.34</v>
-      </c>
-      <c r="AD135">
-        <v>1.24</v>
-      </c>
-      <c r="AE135">
-        <v>1.11</v>
-      </c>
-      <c r="AF135">
-        <v>1.9</v>
-      </c>
-      <c r="AG135">
-        <v>1.78</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.21</v>
-      </c>
-      <c r="AK135">
-        <v>2.09</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O136">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P136">
         <v>2.4</v>
@@ -22489,19 +22489,19 @@
         <v>3.2</v>
       </c>
       <c r="R136">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U136">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V136">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W136">
         <v>1.1</v>
@@ -22516,7 +22516,7 @@
         <v>3.58</v>
       </c>
       <c r="AA136">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB136">
         <v>1.96</v>
@@ -22528,13 +22528,13 @@
         <v>1.35</v>
       </c>
       <c r="AE136">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF136">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG136">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,31 +22640,31 @@
         </is>
       </c>
       <c r="N137">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="O137">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P137">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="Q137">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R137">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S137">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T137">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U137">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V137">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W137">
         <v>0</v>
@@ -22673,31 +22673,31 @@
         <v>0</v>
       </c>
       <c r="Y137">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z137">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA137">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC137">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD137">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE137">
         <v>0</v>
       </c>
       <c r="AF137">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG137">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK137">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,31 +22803,31 @@
         </is>
       </c>
       <c r="N138">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O138">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P138">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W138">
         <v>0</v>
@@ -22836,31 +22836,31 @@
         <v>0</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE138">
         <v>0</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,31 +22966,31 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.75</v>
+        <v>4.63</v>
       </c>
       <c r="O139">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P139">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="Q139">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S139">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T139">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U139">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="V139">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W139">
         <v>0</v>
@@ -22999,31 +22999,31 @@
         <v>0</v>
       </c>
       <c r="Y139">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z139">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA139">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC139">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD139">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE139">
         <v>0</v>
       </c>
       <c r="AF139">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG139">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK139">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,31 +23129,31 @@
         </is>
       </c>
       <c r="N140">
-        <v>4.63</v>
+        <v>2.38</v>
       </c>
       <c r="O140">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P140">
-        <v>1.68</v>
+        <v>3.2</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W140">
         <v>0</v>
@@ -23162,31 +23162,31 @@
         <v>0</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE140">
         <v>0</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,31 +23455,31 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="O142">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q142">
-        <v>2.93</v>
+        <v>2.56</v>
       </c>
       <c r="R142">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="S142">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T142">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="U142">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="V142">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W142">
         <v>0</v>
@@ -23488,31 +23488,31 @@
         <v>0</v>
       </c>
       <c r="Y142">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z142">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="AA142">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AB142">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AC142">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="AD142">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE142">
         <v>0</v>
       </c>
       <c r="AF142">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG142">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK142">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23790,19 +23790,19 @@
         <v>2.1</v>
       </c>
       <c r="Q144">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="R144">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S144">
         <v>1.28</v>
       </c>
       <c r="T144">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U144">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V144">
         <v>1.5</v>
@@ -23814,22 +23814,22 @@
         <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z144">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA144">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB144">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC144">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD144">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE144">
         <v>1.13</v>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK144">
         <v>1.32</v>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O149">
         <v>3.85</v>
@@ -24605,13 +24605,13 @@
         <v>4.45</v>
       </c>
       <c r="Q149">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="R149">
         <v>2.25</v>
       </c>
       <c r="S149">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T149">
         <v>3.04</v>
@@ -24629,10 +24629,10 @@
         <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z149">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="AA149">
         <v>1.92</v>
@@ -25257,7 +25257,7 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R153">
         <v>2.25</v>
@@ -25275,7 +25275,7 @@
         <v>1.5</v>
       </c>
       <c r="W153">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
         <v>1.03</v>
@@ -25302,7 +25302,7 @@
         <v>1.13</v>
       </c>
       <c r="AF153">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG153">
         <v>2.25</v>
@@ -25321,7 +25321,7 @@
         <v>1.33</v>
       </c>
       <c r="AK153">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O154">
         <v>3.42</v>
       </c>
       <c r="P154">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q154">
         <v>2.7</v>
@@ -26226,37 +26226,37 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O159">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P159">
-        <v>5.26</v>
+        <v>6.18</v>
       </c>
       <c r="Q159">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R159">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S159">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U159">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V159">
         <v>1.44</v>
       </c>
       <c r="W159">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y159">
         <v>1.22</v>
@@ -26280,10 +26280,10 @@
         <v>1.14</v>
       </c>
       <c r="AF159">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG159">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK159">
-        <v>2.12</v>
+        <v>2.57</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26561,7 +26561,7 @@
         <v>2.87</v>
       </c>
       <c r="Q161">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="R161">
         <v>1.91</v>
@@ -26588,10 +26588,10 @@
         <v>1.5</v>
       </c>
       <c r="Z161">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AA161">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AB161">
         <v>1.44</v>
@@ -26606,7 +26606,7 @@
         <v>1.04</v>
       </c>
       <c r="AF161">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG161">
         <v>1.7</v>
@@ -26622,7 +26622,7 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK161">
         <v>1.54</v>
@@ -26754,7 +26754,7 @@
         <v>8</v>
       </c>
       <c r="AA162">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AB162">
         <v>3.4</v>
@@ -26899,10 +26899,10 @@
         <v>4.05</v>
       </c>
       <c r="U163">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V163">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W163">
         <v>1.18</v>
@@ -26917,7 +26917,7 @@
         <v>6.5</v>
       </c>
       <c r="AA163">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AB163">
         <v>2.95</v>
@@ -26935,7 +26935,7 @@
         <v>1.36</v>
       </c>
       <c r="AG163">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>3.35</v>
       </c>
       <c r="O164">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P164">
         <v>2.05</v>
@@ -27225,13 +27225,13 @@
         <v>2.63</v>
       </c>
       <c r="U165">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V165">
         <v>1.4</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X165">
         <v>1.06</v>
@@ -28345,28 +28345,28 @@
         </is>
       </c>
       <c r="N172">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="O172">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P172">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q172">
         <v>6.5</v>
       </c>
       <c r="R172">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="S172">
         <v>1.36</v>
       </c>
       <c r="T172">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="U172">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="V172">
         <v>1.37</v>
@@ -28384,7 +28384,7 @@
         <v>3.4</v>
       </c>
       <c r="AA172">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AB172">
         <v>1.85</v>
@@ -28399,10 +28399,10 @@
         <v>1.08</v>
       </c>
       <c r="AF172">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AG172">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="O174">
         <v>4</v>
       </c>
       <c r="P174">
-        <v>4.27</v>
+        <v>4.02</v>
       </c>
       <c r="Q174">
         <v>2.05</v>
@@ -28686,16 +28686,16 @@
         <v>2.55</v>
       </c>
       <c r="S174">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T174">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="U174">
         <v>1.86</v>
       </c>
       <c r="V174">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="W174">
         <v>1.23</v>
@@ -28744,7 +28744,7 @@
         <v>1.22</v>
       </c>
       <c r="AK174">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29012,10 +29012,10 @@
         <v>2.3</v>
       </c>
       <c r="S176">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T176">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="U176">
         <v>2.63</v>
@@ -29024,7 +29024,7 @@
         <v>1.5</v>
       </c>
       <c r="W176">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X176">
         <v>1.03</v>
@@ -29326,16 +29326,16 @@
         <v>2.1</v>
       </c>
       <c r="O178">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P178">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q178">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R178">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S178">
         <v>1.25</v>
@@ -29362,16 +29362,16 @@
         <v>5.5</v>
       </c>
       <c r="AA178">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB178">
         <v>2.3</v>
       </c>
       <c r="AC178">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD178">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE178">
         <v>1.22</v>
@@ -30307,7 +30307,7 @@
         <v>3.2</v>
       </c>
       <c r="P184">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q184">
         <v>3.1</v>
@@ -30322,7 +30322,7 @@
         <v>2.45</v>
       </c>
       <c r="U184">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="V184">
         <v>1.33</v>
@@ -30334,10 +30334,10 @@
         <v>1.07</v>
       </c>
       <c r="Y184">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z184">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AA184">
         <v>2.21</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="O185">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="P185">
-        <v>1.47</v>
+        <v>3.55</v>
       </c>
       <c r="Q185">
-        <v>6.5</v>
+        <v>3.06</v>
       </c>
       <c r="R185">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="S185">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="T185">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U185">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="V185">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W185">
+        <v>1.03</v>
+      </c>
+      <c r="X185">
+        <v>1.1</v>
+      </c>
+      <c r="Y185">
+        <v>1.62</v>
+      </c>
+      <c r="Z185">
+        <v>2.38</v>
+      </c>
+      <c r="AA185">
+        <v>2.75</v>
+      </c>
+      <c r="AB185">
+        <v>1.34</v>
+      </c>
+      <c r="AC185">
+        <v>5.8</v>
+      </c>
+      <c r="AD185">
+        <v>1.13</v>
+      </c>
+      <c r="AE185">
         <v>1.02</v>
       </c>
-      <c r="X185">
-        <v>1.04</v>
-      </c>
-      <c r="Y185">
-        <v>1.38</v>
-      </c>
-      <c r="Z185">
-        <v>2.12</v>
-      </c>
-      <c r="AA185">
-        <v>2.03</v>
-      </c>
-      <c r="AB185">
-        <v>1.41</v>
-      </c>
-      <c r="AC185">
-        <v>4.4</v>
-      </c>
-      <c r="AD185">
-        <v>1.14</v>
-      </c>
-      <c r="AE185">
-        <v>1.01</v>
-      </c>
       <c r="AF185">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG185">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AK185">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O186">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P186">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q186">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="R186">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S186">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="T186">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y186">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z186">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF186">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG186">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK186">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,80 +30790,80 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.26</v>
+        <v>7</v>
       </c>
       <c r="O187">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P187">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="Q187">
-        <v>3.06</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R187">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="S187">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="T187">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="U187">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="V187">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W187">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X187">
+        <v>1.04</v>
+      </c>
+      <c r="Y187">
+        <v>1.41</v>
+      </c>
+      <c r="Z187">
+        <v>2.52</v>
+      </c>
+      <c r="AA187">
+        <v>2.38</v>
+      </c>
+      <c r="AB187">
+        <v>1.53</v>
+      </c>
+      <c r="AC187">
+        <v>4.4</v>
+      </c>
+      <c r="AD187">
+        <v>1.14</v>
+      </c>
+      <c r="AE187">
+        <v>1.01</v>
+      </c>
+      <c r="AF187">
+        <v>2.5</v>
+      </c>
+      <c r="AG187">
+        <v>1.45</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ187">
+        <v>1.29</v>
+      </c>
+      <c r="AK187">
         <v>1.08</v>
-      </c>
-      <c r="Y187">
-        <v>1.57</v>
-      </c>
-      <c r="Z187">
-        <v>2.23</v>
-      </c>
-      <c r="AA187">
-        <v>2.95</v>
-      </c>
-      <c r="AB187">
-        <v>1.35</v>
-      </c>
-      <c r="AC187">
-        <v>5.8</v>
-      </c>
-      <c r="AD187">
-        <v>1.07</v>
-      </c>
-      <c r="AE187">
-        <v>1.03</v>
-      </c>
-      <c r="AF187">
-        <v>2.2</v>
-      </c>
-      <c r="AG187">
-        <v>1.6</v>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ187">
-        <v>1.34</v>
-      </c>
-      <c r="AK187">
-        <v>1.53</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30983,7 +30983,7 @@
         <v>1.02</v>
       </c>
       <c r="X188">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y188">
         <v>1.46</v>
@@ -30998,19 +30998,19 @@
         <v>1.48</v>
       </c>
       <c r="AC188">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AD188">
         <v>1.13</v>
       </c>
       <c r="AE188">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF188">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AG188">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31155,10 +31155,10 @@
         <v>4.66</v>
       </c>
       <c r="AA189">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB189">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC189">
         <v>2.55</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="O197">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P197">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q197">
         <v>3.1</v>
@@ -32447,7 +32447,7 @@
         <v>1.89</v>
       </c>
       <c r="W197">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X197">
         <v>1.01</v>
@@ -32465,7 +32465,7 @@
         <v>3.2</v>
       </c>
       <c r="AC197">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD197">
         <v>2.02</v>
@@ -32474,7 +32474,7 @@
         <v>1.4</v>
       </c>
       <c r="AF197">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG197">
         <v>3.26</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="O198">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P198">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q198">
         <v>5.25</v>
@@ -32598,16 +32598,16 @@
         <v>2.75</v>
       </c>
       <c r="S198">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T198">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="U198">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V198">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="W198">
         <v>1.22</v>
@@ -32622,19 +32622,19 @@
         <v>7.5</v>
       </c>
       <c r="AA198">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB198">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AC198">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD198">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE198">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF198">
         <v>1.4</v>
@@ -32755,16 +32755,16 @@
         <v>6.23</v>
       </c>
       <c r="Q199">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="R199">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="S199">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T199">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U199">
         <v>1.84</v>
@@ -32773,13 +32773,13 @@
         <v>1.91</v>
       </c>
       <c r="W199">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X199">
         <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z199">
         <v>7.5</v>
@@ -32788,13 +32788,13 @@
         <v>1.25</v>
       </c>
       <c r="AB199">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="AC199">
         <v>1.69</v>
       </c>
       <c r="AD199">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE199">
         <v>1.38</v>
@@ -32912,13 +32912,13 @@
         <v>1.52</v>
       </c>
       <c r="O200">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P200">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q200">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R200">
         <v>2.9</v>
@@ -32936,34 +32936,34 @@
         <v>1.95</v>
       </c>
       <c r="W200">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X200">
         <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Z200">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA200">
         <v>1.25</v>
       </c>
       <c r="AB200">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AC200">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD200">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AE200">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AF200">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG200">
         <v>3</v>
@@ -32982,7 +32982,7 @@
         <v>1.16</v>
       </c>
       <c r="AK200">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,34 +33072,34 @@
         </is>
       </c>
       <c r="N201">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O201">
         <v>4.35</v>
       </c>
       <c r="P201">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q201">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="R201">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="S201">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="T201">
         <v>5.05</v>
       </c>
       <c r="U201">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V201">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W201">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X201">
         <v>1.01</v>
@@ -33120,7 +33120,7 @@
         <v>1.69</v>
       </c>
       <c r="AD201">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AE201">
         <v>1.45</v>
@@ -33235,34 +33235,34 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O202">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="P202">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q202">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R202">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S202">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T202">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="U202">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V202">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W202">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X202">
         <v>1.01</v>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK202">
         <v>1.68</v>
@@ -33398,31 +33398,31 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="O203">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P203">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q203">
         <v>2.9</v>
       </c>
       <c r="R203">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S203">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T203">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U203">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="V203">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W203">
         <v>1.17</v>
@@ -33431,31 +33431,31 @@
         <v>1.01</v>
       </c>
       <c r="Y203">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z203">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA203">
         <v>1.44</v>
       </c>
       <c r="AB203">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC203">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AD203">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE203">
         <v>1.25</v>
       </c>
       <c r="AF203">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG203">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AK203">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>2.65</v>
       </c>
       <c r="U205">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="V205">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W205">
         <v>1.04</v>
@@ -33899,7 +33899,7 @@
         <v>4.9</v>
       </c>
       <c r="R206">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="S206">
         <v>1.32</v>
@@ -33923,7 +33923,7 @@
         <v>1.22</v>
       </c>
       <c r="Z206">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA206">
         <v>1.67</v>
@@ -33941,7 +33941,7 @@
         <v>1.14</v>
       </c>
       <c r="AF206">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG206">
         <v>2.04</v>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK206">
         <v>1.16</v>
@@ -34059,7 +34059,7 @@
         <v>3.7</v>
       </c>
       <c r="Q207">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R207">
         <v>2.12</v>
@@ -34068,22 +34068,22 @@
         <v>1.36</v>
       </c>
       <c r="T207">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U207">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="V207">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W207">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z207">
         <v>3.05</v>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK207">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34252,7 +34252,7 @@
         <v>4.85</v>
       </c>
       <c r="AA208">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB208">
         <v>2.44</v>
@@ -34261,7 +34261,7 @@
         <v>2.2</v>
       </c>
       <c r="AD208">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE208">
         <v>1.23</v>
@@ -34270,7 +34270,7 @@
         <v>1.44</v>
       </c>
       <c r="AG208">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>11</v>
       </c>
       <c r="O217">
-        <v>8.35</v>
+        <v>8.1</v>
       </c>
       <c r="P217">
         <v>1.2</v>
@@ -35737,7 +35737,7 @@
         <v>1.53</v>
       </c>
       <c r="AG217">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35843,10 +35843,10 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O218">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P218">
         <v>2.4</v>
@@ -35855,31 +35855,31 @@
         <v>3.25</v>
       </c>
       <c r="R218">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S218">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T218">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U218">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="V218">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W218">
         <v>1.07</v>
       </c>
       <c r="X218">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y218">
         <v>1.29</v>
       </c>
       <c r="Z218">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA218">
         <v>1.78</v>
@@ -35891,16 +35891,16 @@
         <v>2.9</v>
       </c>
       <c r="AD218">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE218">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF218">
         <v>1.63</v>
       </c>
       <c r="AG218">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK218">
         <v>1.4</v>
@@ -36193,16 +36193,16 @@
         <v>2.47</v>
       </c>
       <c r="V220">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W220">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X220">
         <v>1.04</v>
       </c>
       <c r="Y220">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z220">
         <v>3.7</v>
@@ -36211,7 +36211,7 @@
         <v>1.75</v>
       </c>
       <c r="AB220">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC220">
         <v>2.9</v>
@@ -36984,10 +36984,10 @@
         </is>
       </c>
       <c r="N225">
-        <v>7.8</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O225">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P225">
         <v>1.38</v>
@@ -37005,10 +37005,10 @@
         <v>3.2</v>
       </c>
       <c r="U225">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V225">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W225">
         <v>1.04</v>
@@ -37023,10 +37023,10 @@
         <v>3.75</v>
       </c>
       <c r="AA225">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB225">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC225">
         <v>3.25</v>
@@ -37147,25 +37147,25 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O226">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P226">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q226">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="R226">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S226">
         <v>1.44</v>
       </c>
       <c r="T226">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="U226">
         <v>3.3</v>
@@ -37180,31 +37180,31 @@
         <v>1.07</v>
       </c>
       <c r="Y226">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z226">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AA226">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AB226">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AC226">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD226">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE226">
         <v>1.01</v>
       </c>
       <c r="AF226">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG226">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK226">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37319,7 +37319,7 @@
         <v>3.55</v>
       </c>
       <c r="Q227">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="R227">
         <v>2</v>
@@ -37340,7 +37340,7 @@
         <v>1.05</v>
       </c>
       <c r="X227">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y227">
         <v>1.32</v>
@@ -37361,7 +37361,7 @@
         <v>1.22</v>
       </c>
       <c r="AE227">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF227">
         <v>1.84</v>
@@ -37383,7 +37383,7 @@
         <v>1.29</v>
       </c>
       <c r="AK227">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37503,7 +37503,7 @@
         <v>1.07</v>
       </c>
       <c r="X228">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y228">
         <v>1.31</v>
@@ -37524,7 +37524,7 @@
         <v>1.2</v>
       </c>
       <c r="AE228">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF228">
         <v>1.83</v>
@@ -37546,7 +37546,7 @@
         <v>1.27</v>
       </c>
       <c r="AK228">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37811,7 +37811,7 @@
         <v>2.15</v>
       </c>
       <c r="R230">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="S230">
         <v>1.2</v>
@@ -37835,7 +37835,7 @@
         <v>1.09</v>
       </c>
       <c r="Z230">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="AA230">
         <v>1.4</v>
@@ -37847,7 +37847,7 @@
         <v>2.1</v>
       </c>
       <c r="AD230">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE230">
         <v>1.3</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O231">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P231">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Q231">
         <v>4</v>
@@ -37983,37 +37983,37 @@
         <v>2.9</v>
       </c>
       <c r="U231">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V231">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W231">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X231">
         <v>1.03</v>
       </c>
       <c r="Y231">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z231">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA231">
         <v>2</v>
       </c>
       <c r="AB231">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC231">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD231">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE231">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF231">
         <v>1.94</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK236">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38949,10 +38949,10 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R237">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S237">
         <v>1.4</v>
@@ -38964,7 +38964,7 @@
         <v>3.18</v>
       </c>
       <c r="V237">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W237">
         <v>1.05</v>
@@ -39601,7 +39601,7 @@
         <v>4.25</v>
       </c>
       <c r="Q241">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="R241">
         <v>2.4</v>
@@ -39616,7 +39616,7 @@
         <v>2.29</v>
       </c>
       <c r="V241">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W241">
         <v>1.1</v>
@@ -39631,19 +39631,19 @@
         <v>4.7</v>
       </c>
       <c r="AA241">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB241">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC241">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AD241">
         <v>1.48</v>
       </c>
       <c r="AE241">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF241">
         <v>1.57</v>
@@ -39764,28 +39764,28 @@
         <v>0</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y242">
         <v>1.35</v>
@@ -39806,7 +39806,7 @@
         <v>1.2</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF242">
         <v>1.86</v>
@@ -40084,7 +40084,7 @@
         <v>1.55</v>
       </c>
       <c r="O244">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P244">
         <v>4.9</v>
@@ -40096,16 +40096,16 @@
         <v>2.05</v>
       </c>
       <c r="S244">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T244">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U244">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V244">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W244">
         <v>1.06</v>
@@ -40114,31 +40114,31 @@
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z244">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA244">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB244">
         <v>1.73</v>
       </c>
       <c r="AC244">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD244">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE244">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF244">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG244">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.16</v>
       </c>
       <c r="AK244">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40419,7 +40419,7 @@
         <v>3.1</v>
       </c>
       <c r="R246">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="S246">
         <v>1.72</v>
@@ -40437,13 +40437,13 @@
         <v>1</v>
       </c>
       <c r="X246">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y246">
         <v>1.67</v>
       </c>
       <c r="Z246">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AA246">
         <v>3</v>
@@ -40452,7 +40452,7 @@
         <v>1.36</v>
       </c>
       <c r="AC246">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD246">
         <v>1.07</v>
@@ -40461,7 +40461,7 @@
         <v>1.01</v>
       </c>
       <c r="AF246">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AG246">
         <v>1.53</v>
@@ -40576,10 +40576,10 @@
         <v>6.25</v>
       </c>
       <c r="P247">
-        <v>9.85</v>
+        <v>10</v>
       </c>
       <c r="Q247">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R247">
         <v>2.77</v>
@@ -40591,10 +40591,10 @@
         <v>3.78</v>
       </c>
       <c r="U247">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V247">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W247">
         <v>1.14</v>
@@ -40606,19 +40606,19 @@
         <v>1.1</v>
       </c>
       <c r="Z247">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="AA247">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB247">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AC247">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AD247">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE247">
         <v>1.24</v>
@@ -40643,7 +40643,7 @@
         <v>1.14</v>
       </c>
       <c r="AK247">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,7 +40896,7 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="O249">
         <v>3.58</v>
@@ -41385,28 +41385,28 @@
         </is>
       </c>
       <c r="N252">
+        <v>7.25</v>
+      </c>
+      <c r="O252">
+        <v>5.7</v>
+      </c>
+      <c r="P252">
+        <v>1.24</v>
+      </c>
+      <c r="Q252">
         <v>7.4</v>
-      </c>
-      <c r="O252">
-        <v>5.8</v>
-      </c>
-      <c r="P252">
-        <v>1.23</v>
-      </c>
-      <c r="Q252">
-        <v>7.8</v>
       </c>
       <c r="R252">
         <v>2.43</v>
       </c>
       <c r="S252">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T252">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U252">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V252">
         <v>1.49</v>
@@ -41439,10 +41439,10 @@
         <v>1.22</v>
       </c>
       <c r="AF252">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG252">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK252">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -42040,7 +42040,7 @@
         <v>2.16</v>
       </c>
       <c r="O256">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="P256">
         <v>3.3</v>
@@ -43504,64 +43504,64 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -44002,7 +44002,7 @@
         <v>0</v>
       </c>
       <c r="Q268">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="R268">
         <v>2.04</v>
@@ -44032,10 +44032,10 @@
         <v>3.6</v>
       </c>
       <c r="AA268">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB268">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC268">
         <v>3.25</v>
@@ -44826,10 +44826,10 @@
         <v>1.22</v>
       </c>
       <c r="T273">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U273">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V273">
         <v>1.6</v>
@@ -44881,7 +44881,7 @@
         <v>1.07</v>
       </c>
       <c r="AK273">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45161,7 +45161,7 @@
         <v>1.62</v>
       </c>
       <c r="W275">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X275">
         <v>1.01</v>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AK275">
         <v>1.11</v>
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O276">
         <v>3.44</v>
       </c>
       <c r="P276">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q276">
         <v>4.4</v>
@@ -45312,10 +45312,10 @@
         <v>2.2</v>
       </c>
       <c r="S276">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T276">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U276">
         <v>2.88</v>
@@ -45342,7 +45342,7 @@
         <v>1.8</v>
       </c>
       <c r="AC276">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD276">
         <v>1.3</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O277">
         <v>3.4</v>
       </c>
       <c r="P277">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q277">
         <v>2.15</v>
@@ -45475,7 +45475,7 @@
         <v>2.2</v>
       </c>
       <c r="S277">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T277">
         <v>2.88</v>
@@ -45487,7 +45487,7 @@
         <v>1.4</v>
       </c>
       <c r="W277">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
         <v>1.01</v>
@@ -45623,16 +45623,16 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="O278">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P278">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q278">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R278">
         <v>2.1</v>
@@ -45644,10 +45644,10 @@
         <v>2.63</v>
       </c>
       <c r="U278">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V278">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W278">
         <v>1.06</v>
@@ -45659,28 +45659,28 @@
         <v>1.3</v>
       </c>
       <c r="Z278">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA278">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AB278">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC278">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD278">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE278">
         <v>1.05</v>
       </c>
       <c r="AF278">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AG278">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>1.17</v>
       </c>
       <c r="AK278">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="O279">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P279">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q279">
         <v>1.91</v>
@@ -45801,7 +45801,7 @@
         <v>2.4</v>
       </c>
       <c r="S279">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T279">
         <v>3.3</v>
@@ -45810,10 +45810,10 @@
         <v>2.35</v>
       </c>
       <c r="V279">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W279">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X279">
         <v>1.02</v>
@@ -45825,13 +45825,13 @@
         <v>4.33</v>
       </c>
       <c r="AA279">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB279">
         <v>2.15</v>
       </c>
       <c r="AC279">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD279">
         <v>1.44</v>
@@ -45840,7 +45840,7 @@
         <v>1.14</v>
       </c>
       <c r="AF279">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AG279">
         <v>2</v>
@@ -45949,28 +45949,28 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O280">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P280">
         <v>2.17</v>
       </c>
       <c r="Q280">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R280">
         <v>2.2</v>
       </c>
       <c r="S280">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T280">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="U280">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V280">
         <v>1.4</v>
@@ -46151,7 +46151,7 @@
         <v>3.95</v>
       </c>
       <c r="AA281">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB281">
         <v>2.05</v>
@@ -46278,10 +46278,10 @@
         <v>2</v>
       </c>
       <c r="O282">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P282">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46438,16 +46438,16 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O283">
         <v>3</v>
       </c>
       <c r="P283">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q283">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R283">
         <v>2.1</v>
@@ -46459,7 +46459,7 @@
         <v>2.75</v>
       </c>
       <c r="U283">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="V283">
         <v>1.32</v>
@@ -46511,7 +46511,7 @@
         <v>1.35</v>
       </c>
       <c r="AK283">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46613,22 +46613,22 @@
         <v>2.04</v>
       </c>
       <c r="R284">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="S284">
         <v>1.32</v>
       </c>
       <c r="T284">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U284">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V284">
         <v>1.44</v>
       </c>
       <c r="W284">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X284">
         <v>1.03</v>
@@ -46640,10 +46640,10 @@
         <v>3.9</v>
       </c>
       <c r="AA284">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB284">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC284">
         <v>2.9</v>
@@ -46671,7 +46671,7 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AK284">
         <v>2.65</v>
@@ -46764,19 +46764,19 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O285">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P285">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q285">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="R285">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S285">
         <v>1.42</v>
@@ -46785,7 +46785,7 @@
         <v>2.65</v>
       </c>
       <c r="U285">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V285">
         <v>1.3</v>
@@ -46837,7 +46837,7 @@
         <v>1.21</v>
       </c>
       <c r="AK285">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46930,7 +46930,7 @@
         <v>1.3</v>
       </c>
       <c r="O286">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P286">
         <v>7</v>
@@ -46939,7 +46939,7 @@
         <v>1.73</v>
       </c>
       <c r="R286">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="S286">
         <v>1.25</v>
@@ -46966,16 +46966,16 @@
         <v>5.1</v>
       </c>
       <c r="AA286">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB286">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC286">
         <v>2.08</v>
       </c>
       <c r="AD286">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE286">
         <v>1.29</v>
@@ -47256,13 +47256,13 @@
         <v>1.16</v>
       </c>
       <c r="O288">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="P288">
         <v>11</v>
       </c>
       <c r="Q288">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R288">
         <v>3.35</v>
@@ -47326,7 +47326,7 @@
         <v>1.08</v>
       </c>
       <c r="AK288">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47416,7 +47416,7 @@
         </is>
       </c>
       <c r="N289">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="O289">
         <v>3.75</v>
@@ -47425,10 +47425,10 @@
         <v>1.65</v>
       </c>
       <c r="Q289">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R289">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S289">
         <v>1.25</v>
@@ -47437,7 +47437,7 @@
         <v>3.6</v>
       </c>
       <c r="U289">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V289">
         <v>1.62</v>
@@ -47455,13 +47455,13 @@
         <v>4.8</v>
       </c>
       <c r="AA289">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB289">
+        <v>2.4</v>
+      </c>
+      <c r="AC289">
         <v>2.45</v>
-      </c>
-      <c r="AC289">
-        <v>2.36</v>
       </c>
       <c r="AD289">
         <v>1.53</v>
@@ -47470,7 +47470,7 @@
         <v>1.2</v>
       </c>
       <c r="AF289">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG289">
         <v>2.2</v>
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AK289">
         <v>1.09</v>
@@ -47588,7 +47588,7 @@
         <v>2.8</v>
       </c>
       <c r="Q290">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="R290">
         <v>1.75</v>
@@ -47597,37 +47597,37 @@
         <v>1.67</v>
       </c>
       <c r="T290">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="U290">
         <v>4.5</v>
       </c>
       <c r="V290">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W290">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X290">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y290">
         <v>1.72</v>
       </c>
       <c r="Z290">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AA290">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB290">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC290">
         <v>7.1</v>
       </c>
       <c r="AD290">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE290">
         <v>1.01</v>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK290">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="O291">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="P291">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q291">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R291">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S291">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T291">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U291">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="V291">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W291">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X291">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y291">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Z291">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA291">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB291">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC291">
-        <v>5.05</v>
+        <v>6.15</v>
       </c>
       <c r="AD291">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE291">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF291">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AG291">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK291">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,65 +47905,65 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O292">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="P292">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="Q292">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="R292">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S292">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T292">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="U292">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="V292">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W292">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X292">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y292">
+        <v>1.49</v>
+      </c>
+      <c r="Z292">
+        <v>2.45</v>
+      </c>
+      <c r="AA292">
+        <v>2.6</v>
+      </c>
+      <c r="AB292">
+        <v>1.44</v>
+      </c>
+      <c r="AC292">
+        <v>5.17</v>
+      </c>
+      <c r="AD292">
+        <v>1.15</v>
+      </c>
+      <c r="AE292">
+        <v>1.04</v>
+      </c>
+      <c r="AF292">
+        <v>2.18</v>
+      </c>
+      <c r="AG292">
         <v>1.56</v>
       </c>
-      <c r="Z292">
-        <v>2.25</v>
-      </c>
-      <c r="AA292">
-        <v>2.88</v>
-      </c>
-      <c r="AB292">
-        <v>1.38</v>
-      </c>
-      <c r="AC292">
-        <v>6.05</v>
-      </c>
-      <c r="AD292">
-        <v>1.06</v>
-      </c>
-      <c r="AE292">
-        <v>1.02</v>
-      </c>
-      <c r="AF292">
-        <v>2.3</v>
-      </c>
-      <c r="AG292">
-        <v>1.52</v>
-      </c>
       <c r="AH292" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK292">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48077,7 +48077,7 @@
         <v>8.75</v>
       </c>
       <c r="Q293">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="R293">
         <v>2.5</v>
@@ -48089,7 +48089,7 @@
         <v>3.1</v>
       </c>
       <c r="U293">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V293">
         <v>1.44</v>
@@ -48101,19 +48101,19 @@
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z293">
         <v>3.62</v>
       </c>
       <c r="AA293">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB293">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC293">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AD293">
         <v>1.36</v>
@@ -48231,19 +48231,19 @@
         </is>
       </c>
       <c r="N294">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O294">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P294">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q294">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R294">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S294">
         <v>1.44</v>
@@ -48252,7 +48252,7 @@
         <v>2.38</v>
       </c>
       <c r="U294">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V294">
         <v>1.29</v>
@@ -48264,22 +48264,22 @@
         <v>1.07</v>
       </c>
       <c r="Y294">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z294">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AA294">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB294">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC294">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AD294">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE294">
         <v>1.05</v>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AK294">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48403,7 +48403,7 @@
         <v>1.25</v>
       </c>
       <c r="Q295">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R295">
         <v>2.89</v>
@@ -48448,7 +48448,7 @@
         <v>1.3</v>
       </c>
       <c r="AF295">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG295">
         <v>1.95</v>
@@ -48566,10 +48566,10 @@
         <v>1.67</v>
       </c>
       <c r="Q296">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="R296">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="S296">
         <v>1.29</v>
@@ -48587,7 +48587,7 @@
         <v>1.08</v>
       </c>
       <c r="X296">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y296">
         <v>1.28</v>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="AK296">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48883,28 +48883,28 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="O298">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P298">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q298">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R298">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S298">
         <v>1.37</v>
       </c>
       <c r="T298">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U298">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V298">
         <v>1.36</v>
@@ -48913,7 +48913,7 @@
         <v>1.08</v>
       </c>
       <c r="X298">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y298">
         <v>1.27</v>
@@ -48928,10 +48928,10 @@
         <v>1.78</v>
       </c>
       <c r="AC298">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AD298">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE298">
         <v>1.07</v>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK298">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O299">
         <v>6.5</v>
       </c>
       <c r="P299">
-        <v>10.63</v>
+        <v>11</v>
       </c>
       <c r="Q299">
         <v>1.44</v>
@@ -49067,10 +49067,10 @@
         <v>5</v>
       </c>
       <c r="U299">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V299">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="W299">
         <v>1.25</v>
@@ -49085,13 +49085,13 @@
         <v>8</v>
       </c>
       <c r="AA299">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB299">
         <v>3.6</v>
       </c>
       <c r="AC299">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD299">
         <v>1.94</v>
@@ -49100,10 +49100,10 @@
         <v>1.4</v>
       </c>
       <c r="AF299">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG299">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK299">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49209,34 +49209,34 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O300">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="P300">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="Q300">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R300">
         <v>1.85</v>
       </c>
       <c r="S300">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="T300">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U300">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="V300">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W300">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X300">
         <v>1.14</v>
@@ -49248,13 +49248,13 @@
         <v>2.2</v>
       </c>
       <c r="AA300">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AB300">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC300">
-        <v>6.21</v>
+        <v>6.29</v>
       </c>
       <c r="AD300">
         <v>1.11</v>
@@ -49263,10 +49263,10 @@
         <v>1.03</v>
       </c>
       <c r="AF300">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AG300">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK300">
         <v>1.44</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,61 +49372,61 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O301">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P301">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q301">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="R301">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="S301">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="T301">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U301">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="V301">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W301">
         <v>1.03</v>
       </c>
       <c r="X301">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y301">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="Z301">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AA301">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="AB301">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC301">
-        <v>4.27</v>
+        <v>6</v>
       </c>
       <c r="AD301">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE301">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF301">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG301">
         <v>1.6</v>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK301">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
+        <v>1.69</v>
+      </c>
+      <c r="O302">
+        <v>3.3</v>
+      </c>
+      <c r="P302">
+        <v>4.63</v>
+      </c>
+      <c r="Q302">
+        <v>2.42</v>
+      </c>
+      <c r="R302">
         <v>2.1</v>
       </c>
-      <c r="O302">
-        <v>2.87</v>
-      </c>
-      <c r="P302">
-        <v>3.6</v>
-      </c>
-      <c r="Q302">
-        <v>2.8</v>
-      </c>
-      <c r="R302">
-        <v>1.79</v>
-      </c>
       <c r="S302">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="T302">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U302">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="V302">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W302">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X302">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y302">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="Z302">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AA302">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="AB302">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AC302">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AD302">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE302">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF302">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG302">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK302">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49737,7 +49737,7 @@
         <v>2.54</v>
       </c>
       <c r="AA303">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AB303">
         <v>1.59</v>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK303">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O304">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P304">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="Q304">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R304">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S304">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T304">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U304">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V304">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W304">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X304">
         <v>1.02</v>
       </c>
       <c r="Y304">
+        <v>1.2</v>
+      </c>
+      <c r="Z304">
+        <v>3.9</v>
+      </c>
+      <c r="AA304">
+        <v>1.7</v>
+      </c>
+      <c r="AB304">
+        <v>2.1</v>
+      </c>
+      <c r="AC304">
+        <v>2.74</v>
+      </c>
+      <c r="AD304">
         <v>1.34</v>
       </c>
-      <c r="Z304">
-        <v>3.5</v>
-      </c>
-      <c r="AA304">
-        <v>1.85</v>
-      </c>
-      <c r="AB304">
-        <v>1.95</v>
-      </c>
-      <c r="AC304">
-        <v>2.94</v>
-      </c>
-      <c r="AD304">
-        <v>1.35</v>
-      </c>
       <c r="AE304">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF304">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AG304">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>1.25</v>
       </c>
       <c r="AK304">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50027,7 +50027,7 @@
         <v>2.95</v>
       </c>
       <c r="O305">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P305">
         <v>2.35</v>
@@ -50039,10 +50039,10 @@
         <v>2.3</v>
       </c>
       <c r="S305">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T305">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="U305">
         <v>2.38</v>
@@ -50051,7 +50051,7 @@
         <v>1.5</v>
       </c>
       <c r="W305">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X305">
         <v>1.04</v>
@@ -50066,13 +50066,13 @@
         <v>1.67</v>
       </c>
       <c r="AB305">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC305">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD305">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE305">
         <v>1.18</v>
@@ -50097,7 +50097,7 @@
         <v>1.3</v>
       </c>
       <c r="AK305">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50679,10 +50679,10 @@
         <v>2.1</v>
       </c>
       <c r="O309">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P309">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q309">
         <v>2.7</v>
@@ -50694,7 +50694,7 @@
         <v>1.5</v>
       </c>
       <c r="T309">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U309">
         <v>3.6</v>
@@ -50715,16 +50715,16 @@
         <v>2.45</v>
       </c>
       <c r="AA309">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AB309">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC309">
         <v>5.4</v>
       </c>
       <c r="AD309">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE309">
         <v>1.02</v>
@@ -50749,7 +50749,7 @@
         <v>1.2</v>
       </c>
       <c r="AK309">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O310">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P310">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q310">
         <v>2.6</v>
@@ -50854,10 +50854,10 @@
         <v>1.95</v>
       </c>
       <c r="S310">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T310">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="U310">
         <v>3.75</v>
@@ -50869,16 +50869,16 @@
         <v>1.01</v>
       </c>
       <c r="X310">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y310">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="Z310">
         <v>2.5</v>
       </c>
       <c r="AA310">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AB310">
         <v>1.47</v>
@@ -50893,7 +50893,7 @@
         <v>1.03</v>
       </c>
       <c r="AF310">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AG310">
         <v>1.52</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK310">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51500,7 +51500,7 @@
         <v>6.97</v>
       </c>
       <c r="Q314">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R314">
         <v>2.45</v>
@@ -51518,7 +51518,7 @@
         <v>1.55</v>
       </c>
       <c r="W314">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X314">
         <v>1.03</v>
@@ -51663,28 +51663,28 @@
         <v>3.5</v>
       </c>
       <c r="Q315">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="R315">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S315">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T315">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U315">
         <v>3.2</v>
       </c>
       <c r="V315">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W315">
         <v>1.03</v>
       </c>
       <c r="X315">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y315">
         <v>1.4</v>
@@ -51699,7 +51699,7 @@
         <v>1.61</v>
       </c>
       <c r="AC315">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD315">
         <v>1.2</v>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK315">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51817,10 +51817,10 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O316">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P316">
         <v>3.4</v>
@@ -51832,7 +51832,7 @@
         <v>1.98</v>
       </c>
       <c r="S316">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T316">
         <v>2.24</v>
@@ -51844,7 +51844,7 @@
         <v>1.21</v>
       </c>
       <c r="W316">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X316">
         <v>1.13</v>
@@ -51983,7 +51983,7 @@
         <v>1.67</v>
       </c>
       <c r="O317">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P317">
         <v>4.8</v>
@@ -51998,10 +51998,10 @@
         <v>1.5</v>
       </c>
       <c r="T317">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U317">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V317">
         <v>1.29</v>
@@ -52025,7 +52025,7 @@
         <v>1.54</v>
       </c>
       <c r="AC317">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD317">
         <v>1.17</v>
@@ -52037,7 +52037,7 @@
         <v>2.3</v>
       </c>
       <c r="AG317">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="O318">
         <v>3</v>
       </c>
       <c r="P318">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q318">
         <v>2.8</v>
@@ -52158,43 +52158,43 @@
         <v>2.08</v>
       </c>
       <c r="S318">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T318">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U318">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="V318">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W318">
         <v>1.05</v>
       </c>
       <c r="X318">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y318">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z318">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AA318">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="AB318">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AC318">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AD318">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE318">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF318">
         <v>1.87</v>
@@ -52318,22 +52318,22 @@
         <v>2.4</v>
       </c>
       <c r="R319">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S319">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T319">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U319">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V319">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W319">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X319">
         <v>1.02</v>
@@ -52342,25 +52342,25 @@
         <v>1.14</v>
       </c>
       <c r="Z319">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA319">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB319">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AC319">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD319">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE319">
         <v>1.19</v>
       </c>
       <c r="AF319">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG319">
         <v>2.42</v>
@@ -52478,13 +52478,13 @@
         <v>4.2</v>
       </c>
       <c r="Q320">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R320">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="S320">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T320">
         <v>2.3</v>
@@ -52496,7 +52496,7 @@
         <v>1.22</v>
       </c>
       <c r="W320">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X320">
         <v>1.1</v>
@@ -52508,16 +52508,16 @@
         <v>2.5</v>
       </c>
       <c r="AA320">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AB320">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC320">
         <v>6</v>
       </c>
       <c r="AD320">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE320">
         <v>1.03</v>
@@ -52542,7 +52542,7 @@
         <v>1.36</v>
       </c>
       <c r="AK320">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52795,22 +52795,22 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O322">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P322">
         <v>5.4</v>
       </c>
       <c r="Q322">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="R322">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S322">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T322">
         <v>2.5</v>
@@ -52828,31 +52828,31 @@
         <v>1.08</v>
       </c>
       <c r="Y322">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z322">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AA322">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AB322">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AC322">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="AD322">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE322">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF322">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG322">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AK322">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52967,13 +52967,13 @@
         <v>4.2</v>
       </c>
       <c r="Q323">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R323">
         <v>2.1</v>
       </c>
       <c r="S323">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T323">
         <v>2.56</v>
@@ -53003,19 +53003,19 @@
         <v>1.6</v>
       </c>
       <c r="AC323">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AD323">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE323">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF323">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG323">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK323">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53130,10 +53130,10 @@
         <v>1.63</v>
       </c>
       <c r="Q324">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="R324">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="S324">
         <v>1.26</v>
@@ -53151,10 +53151,10 @@
         <v>1.11</v>
       </c>
       <c r="X324">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y324">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z324">
         <v>4.2</v>
@@ -53172,7 +53172,7 @@
         <v>1.48</v>
       </c>
       <c r="AE324">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF324">
         <v>1.62</v>
@@ -53191,7 +53191,7 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK324">
         <v>1.17</v>
@@ -53447,7 +53447,7 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="O326">
         <v>3.2</v>
@@ -53610,7 +53610,7 @@
         </is>
       </c>
       <c r="N327">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O327">
         <v>3.5</v>
@@ -53619,7 +53619,7 @@
         <v>4.8</v>
       </c>
       <c r="Q327">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R327">
         <v>2.15</v>
@@ -53631,16 +53631,16 @@
         <v>2.88</v>
       </c>
       <c r="U327">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="V327">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W327">
         <v>1.06</v>
       </c>
       <c r="X327">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y327">
         <v>1.34</v>
@@ -53655,7 +53655,7 @@
         <v>1.65</v>
       </c>
       <c r="AC327">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD327">
         <v>1.22</v>
@@ -53667,7 +53667,7 @@
         <v>1.98</v>
       </c>
       <c r="AG327">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53773,16 +53773,16 @@
         </is>
       </c>
       <c r="N328">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="O328">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P328">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q328">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="R328">
         <v>2.1</v>
@@ -53797,7 +53797,7 @@
         <v>2.45</v>
       </c>
       <c r="V328">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W328">
         <v>1.08</v>
@@ -53812,16 +53812,16 @@
         <v>3.4</v>
       </c>
       <c r="AA328">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB328">
         <v>1.9</v>
       </c>
       <c r="AC328">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AD328">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE328">
         <v>1.09</v>
@@ -53843,7 +53843,7 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK328">
         <v>1.3</v>
@@ -54108,7 +54108,7 @@
         <v>1.38</v>
       </c>
       <c r="Q330">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="R330">
         <v>2.5</v>
@@ -54132,10 +54132,10 @@
         <v>1.01</v>
       </c>
       <c r="Y330">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z330">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA330">
         <v>1.33</v>
@@ -54153,10 +54153,10 @@
         <v>1.4</v>
       </c>
       <c r="AF330">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG330">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>2.68</v>
       </c>
       <c r="AK330">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL330">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="O2">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="P2">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="Q2">
         <v>2.8</v>
@@ -659,40 +659,40 @@
         <v>2.6</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA2">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AC2">
         <v>2.92</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
+        <v>1.24</v>
+      </c>
+      <c r="Z10">
+        <v>3.5</v>
+      </c>
+      <c r="AA10">
+        <v>1.95</v>
+      </c>
+      <c r="AB10">
+        <v>1.85</v>
+      </c>
+      <c r="AC10">
+        <v>2.97</v>
+      </c>
+      <c r="AD10">
+        <v>1.35</v>
+      </c>
+      <c r="AE10">
+        <v>1.1</v>
+      </c>
+      <c r="AF10">
+        <v>1.67</v>
+      </c>
+      <c r="AG10">
+        <v>1.94</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.25</v>
       </c>
-      <c r="Z10">
-        <v>3.3</v>
-      </c>
-      <c r="AA10">
-        <v>1.91</v>
-      </c>
-      <c r="AB10">
-        <v>1.8</v>
-      </c>
-      <c r="AC10">
-        <v>3.4</v>
-      </c>
-      <c r="AD10">
-        <v>1.29</v>
-      </c>
-      <c r="AE10">
-        <v>1.12</v>
-      </c>
-      <c r="AF10">
-        <v>1.69</v>
-      </c>
-      <c r="AG10">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.26</v>
-      </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4067,13 +4067,13 @@
         <v>2.05</v>
       </c>
       <c r="Q23">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="R23">
         <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
         <v>2.6</v>
@@ -4088,7 +4088,7 @@
         <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.29</v>
@@ -4097,13 +4097,13 @@
         <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC23">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD23">
         <v>1.3</v>
@@ -7828,10 +7828,10 @@
         <v>4.2</v>
       </c>
       <c r="U46">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
         <v>1.18</v>
@@ -7846,25 +7846,25 @@
         <v>6</v>
       </c>
       <c r="AA46">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB46">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="AC46">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AD46">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE46">
         <v>1.28</v>
       </c>
       <c r="AF46">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG46">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="AK46">
         <v>1</v>
@@ -8305,10 +8305,10 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R49">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8317,10 +8317,10 @@
         <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="V49">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W49">
         <v>1.15</v>
@@ -8335,25 +8335,25 @@
         <v>4.7</v>
       </c>
       <c r="AA49">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AB49">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC49">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD49">
         <v>1.56</v>
       </c>
       <c r="AE49">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK49">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8670,10 +8670,10 @@
         <v>2.17</v>
       </c>
       <c r="AD51">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AE51">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF51">
         <v>1.93</v>
@@ -8809,7 +8809,7 @@
         <v>2.07</v>
       </c>
       <c r="V52">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="W52">
         <v>1.11</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q61">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U61">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="V61">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AB61">
-        <v>3.16</v>
+        <v>2.48</v>
       </c>
       <c r="AC61">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD61">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AE61">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG61">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK61">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
         <v>2.1</v>
       </c>
-      <c r="O62">
-        <v>3.75</v>
-      </c>
-      <c r="P62">
-        <v>2.8</v>
-      </c>
-      <c r="Q62">
-        <v>2.4</v>
-      </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="V62">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA62">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AB62">
-        <v>2.48</v>
+        <v>3.16</v>
       </c>
       <c r="AC62">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD62">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF62">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AG62">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK62">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
+        <v>3.4</v>
+      </c>
+      <c r="P66">
+        <v>2.55</v>
+      </c>
+      <c r="Q66">
+        <v>3.1</v>
+      </c>
+      <c r="R66">
+        <v>2.15</v>
+      </c>
+      <c r="S66">
+        <v>1.33</v>
+      </c>
+      <c r="T66">
         <v>3</v>
       </c>
-      <c r="P66">
-        <v>2.3</v>
-      </c>
-      <c r="Q66">
-        <v>3.3</v>
-      </c>
-      <c r="R66">
-        <v>2.05</v>
-      </c>
-      <c r="S66">
-        <v>1.36</v>
-      </c>
-      <c r="T66">
-        <v>2.53</v>
-      </c>
       <c r="U66">
+        <v>2.63</v>
+      </c>
+      <c r="V66">
+        <v>1.44</v>
+      </c>
+      <c r="W66">
+        <v>1.1</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="Y66">
+        <v>1.23</v>
+      </c>
+      <c r="Z66">
+        <v>3.42</v>
+      </c>
+      <c r="AA66">
+        <v>1.79</v>
+      </c>
+      <c r="AB66">
+        <v>1.9</v>
+      </c>
+      <c r="AC66">
         <v>2.88</v>
       </c>
-      <c r="V66">
-        <v>1.35</v>
-      </c>
-      <c r="W66">
-        <v>1.04</v>
-      </c>
-      <c r="X66">
-        <v>1.05</v>
-      </c>
-      <c r="Y66">
-        <v>1.3</v>
-      </c>
-      <c r="Z66">
-        <v>3.4</v>
-      </c>
-      <c r="AA66">
-        <v>1.95</v>
-      </c>
-      <c r="AB66">
-        <v>1.75</v>
-      </c>
-      <c r="AC66">
-        <v>3.5</v>
-      </c>
       <c r="AD66">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE66">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG66">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="P67">
+        <v>2.3</v>
+      </c>
+      <c r="Q67">
+        <v>3.3</v>
+      </c>
+      <c r="R67">
+        <v>2.05</v>
+      </c>
+      <c r="S67">
+        <v>1.36</v>
+      </c>
+      <c r="T67">
+        <v>2.53</v>
+      </c>
+      <c r="U67">
+        <v>2.88</v>
+      </c>
+      <c r="V67">
+        <v>1.35</v>
+      </c>
+      <c r="W67">
+        <v>1.04</v>
+      </c>
+      <c r="X67">
+        <v>1.05</v>
+      </c>
+      <c r="Y67">
+        <v>1.3</v>
+      </c>
+      <c r="Z67">
         <v>3.4</v>
       </c>
-      <c r="P67">
-        <v>2.55</v>
-      </c>
-      <c r="Q67">
-        <v>3.1</v>
-      </c>
-      <c r="R67">
-        <v>2.15</v>
-      </c>
-      <c r="S67">
-        <v>1.33</v>
-      </c>
-      <c r="T67">
-        <v>3</v>
-      </c>
-      <c r="U67">
-        <v>2.63</v>
-      </c>
-      <c r="V67">
-        <v>1.44</v>
-      </c>
-      <c r="W67">
+      <c r="AA67">
+        <v>1.95</v>
+      </c>
+      <c r="AB67">
+        <v>1.75</v>
+      </c>
+      <c r="AC67">
+        <v>3.5</v>
+      </c>
+      <c r="AD67">
+        <v>1.24</v>
+      </c>
+      <c r="AE67">
         <v>1.1</v>
       </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>1.23</v>
-      </c>
-      <c r="Z67">
-        <v>3.42</v>
-      </c>
-      <c r="AA67">
-        <v>1.79</v>
-      </c>
-      <c r="AB67">
-        <v>1.9</v>
-      </c>
-      <c r="AC67">
-        <v>2.88</v>
-      </c>
-      <c r="AD67">
-        <v>1.32</v>
-      </c>
-      <c r="AE67">
-        <v>1.09</v>
-      </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>2.28</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
         <v>3.3</v>
@@ -12561,7 +12561,7 @@
         <v>1.48</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12570,22 +12570,22 @@
         <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA75">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB75">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC75">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AD75">
         <v>1.41</v>
       </c>
       <c r="AE75">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF75">
         <v>1.5</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O77">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="P77">
         <v>10</v>
@@ -13032,7 +13032,7 @@
         <v>3.9</v>
       </c>
       <c r="Q78">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R78">
         <v>2.25</v>
@@ -14659,7 +14659,7 @@
         <v>5.5</v>
       </c>
       <c r="P88">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="Q88">
         <v>1.58</v>
@@ -14674,13 +14674,13 @@
         <v>4.33</v>
       </c>
       <c r="U88">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V88">
         <v>1.81</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,25 +16120,25 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P97">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q97">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R97">
         <v>1.83</v>
       </c>
       <c r="S97">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T97">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="U97">
         <v>3.75</v>
@@ -16147,37 +16147,37 @@
         <v>1.22</v>
       </c>
       <c r="W97">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X97">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y97">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Z97">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA97">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AB97">
         <v>1.4</v>
       </c>
       <c r="AC97">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AD97">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE97">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF97">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG97">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK97">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,25 +16283,25 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q98">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R98">
         <v>1.83</v>
       </c>
       <c r="S98">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T98">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="U98">
         <v>3.75</v>
@@ -16310,37 +16310,37 @@
         <v>1.22</v>
       </c>
       <c r="W98">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y98">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Z98">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA98">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AB98">
         <v>1.4</v>
       </c>
       <c r="AC98">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AD98">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE98">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF98">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG98">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17261,31 +17261,31 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O104">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P104">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q104">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R104">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U104">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V104">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W104">
         <v>1.11</v>
@@ -17294,10 +17294,10 @@
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z104">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="AA104">
         <v>1.6</v>
@@ -17315,10 +17315,10 @@
         <v>1.14</v>
       </c>
       <c r="AF104">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG104">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK104">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="R105">
+        <v>2.31</v>
+      </c>
+      <c r="S105">
+        <v>1.28</v>
+      </c>
+      <c r="T105">
+        <v>3.18</v>
+      </c>
+      <c r="U105">
         <v>2.4</v>
-      </c>
-      <c r="S105">
-        <v>1.27</v>
-      </c>
-      <c r="T105">
-        <v>3.32</v>
-      </c>
-      <c r="U105">
-        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.5</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
+        <v>1.2</v>
+      </c>
+      <c r="Z105">
+        <v>4.5</v>
+      </c>
+      <c r="AA105">
+        <v>1.64</v>
+      </c>
+      <c r="AB105">
+        <v>2.2</v>
+      </c>
+      <c r="AC105">
+        <v>2.63</v>
+      </c>
+      <c r="AD105">
+        <v>1.47</v>
+      </c>
+      <c r="AE105">
         <v>1.17</v>
       </c>
-      <c r="Z105">
-        <v>3.96</v>
-      </c>
-      <c r="AA105">
-        <v>1.69</v>
-      </c>
-      <c r="AB105">
-        <v>2.04</v>
-      </c>
-      <c r="AC105">
-        <v>2.7</v>
-      </c>
-      <c r="AD105">
-        <v>1.36</v>
-      </c>
-      <c r="AE105">
-        <v>1.1</v>
-      </c>
       <c r="AF105">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>2.55</v>
+        <v>1.11</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="R107">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S107">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T107">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U107">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V107">
         <v>1.5</v>
       </c>
       <c r="W107">
+        <v>1.08</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.17</v>
+      </c>
+      <c r="Z107">
+        <v>3.96</v>
+      </c>
+      <c r="AA107">
+        <v>1.69</v>
+      </c>
+      <c r="AB107">
+        <v>2.04</v>
+      </c>
+      <c r="AC107">
+        <v>2.7</v>
+      </c>
+      <c r="AD107">
+        <v>1.36</v>
+      </c>
+      <c r="AE107">
         <v>1.1</v>
       </c>
-      <c r="X107">
-        <v>1.02</v>
-      </c>
-      <c r="Y107">
-        <v>1.2</v>
-      </c>
-      <c r="Z107">
-        <v>4.5</v>
-      </c>
-      <c r="AA107">
-        <v>1.64</v>
-      </c>
-      <c r="AB107">
-        <v>2.2</v>
-      </c>
-      <c r="AC107">
-        <v>2.63</v>
-      </c>
-      <c r="AD107">
-        <v>1.47</v>
-      </c>
-      <c r="AE107">
-        <v>1.17</v>
-      </c>
       <c r="AF107">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG107">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK107">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,31 +20358,31 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O123">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P123">
+        <v>2.5</v>
+      </c>
+      <c r="Q123">
+        <v>3.38</v>
+      </c>
+      <c r="R123">
+        <v>2.03</v>
+      </c>
+      <c r="S123">
+        <v>1.35</v>
+      </c>
+      <c r="T123">
         <v>2.8</v>
       </c>
-      <c r="Q123">
-        <v>3.2</v>
-      </c>
-      <c r="R123">
-        <v>1.93</v>
-      </c>
-      <c r="S123">
-        <v>1.45</v>
-      </c>
-      <c r="T123">
-        <v>2.44</v>
-      </c>
       <c r="U123">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V123">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W123">
         <v>0</v>
@@ -20391,31 +20391,31 @@
         <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z123">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="AA123">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB123">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AC123">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD123">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE123">
         <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG123">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,31 +20521,31 @@
         </is>
       </c>
       <c r="N124">
+        <v>2.6</v>
+      </c>
+      <c r="O124">
+        <v>3.2</v>
+      </c>
+      <c r="P124">
         <v>2.8</v>
       </c>
-      <c r="O124">
-        <v>3.4</v>
-      </c>
-      <c r="P124">
-        <v>2.5</v>
-      </c>
       <c r="Q124">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="R124">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="S124">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T124">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="U124">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V124">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W124">
         <v>0</v>
@@ -20554,47 +20554,47 @@
         <v>0</v>
       </c>
       <c r="Y124">
+        <v>1.37</v>
+      </c>
+      <c r="Z124">
+        <v>2.66</v>
+      </c>
+      <c r="AA124">
+        <v>2.25</v>
+      </c>
+      <c r="AB124">
+        <v>1.56</v>
+      </c>
+      <c r="AC124">
+        <v>4.15</v>
+      </c>
+      <c r="AD124">
+        <v>1.16</v>
+      </c>
+      <c r="AE124">
+        <v>0</v>
+      </c>
+      <c r="AF124">
+        <v>1.9</v>
+      </c>
+      <c r="AG124">
+        <v>1.78</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
         <v>1.28</v>
       </c>
-      <c r="Z124">
-        <v>3.08</v>
-      </c>
-      <c r="AA124">
-        <v>2</v>
-      </c>
-      <c r="AB124">
-        <v>1.71</v>
-      </c>
-      <c r="AC124">
-        <v>3.5</v>
-      </c>
-      <c r="AD124">
-        <v>1.22</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>1.87</v>
-      </c>
-      <c r="AG124">
-        <v>1.8</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.25</v>
-      </c>
       <c r="AK124">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O132">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P132">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q132">
         <v>2.63</v>
@@ -21840,7 +21840,7 @@
         <v>2.2</v>
       </c>
       <c r="S132">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
         <v>2.88</v>
@@ -21849,25 +21849,25 @@
         <v>2.63</v>
       </c>
       <c r="V132">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W132">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y132">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA132">
         <v>1.73</v>
       </c>
       <c r="AB132">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AC132">
         <v>2.75</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,65 +22151,65 @@
         </is>
       </c>
       <c r="N134">
+        <v>2.05</v>
+      </c>
+      <c r="O134">
+        <v>3</v>
+      </c>
+      <c r="P134">
+        <v>3.46</v>
+      </c>
+      <c r="Q134">
+        <v>2.54</v>
+      </c>
+      <c r="R134">
+        <v>2.01</v>
+      </c>
+      <c r="S134">
+        <v>1.55</v>
+      </c>
+      <c r="T134">
+        <v>2.33</v>
+      </c>
+      <c r="U134">
+        <v>3.36</v>
+      </c>
+      <c r="V134">
+        <v>1.25</v>
+      </c>
+      <c r="W134">
+        <v>1.01</v>
+      </c>
+      <c r="X134">
+        <v>1.06</v>
+      </c>
+      <c r="Y134">
+        <v>1.47</v>
+      </c>
+      <c r="Z134">
+        <v>2.65</v>
+      </c>
+      <c r="AA134">
+        <v>2.48</v>
+      </c>
+      <c r="AB134">
+        <v>1.53</v>
+      </c>
+      <c r="AC134">
+        <v>4.4</v>
+      </c>
+      <c r="AD134">
+        <v>1.18</v>
+      </c>
+      <c r="AE134">
+        <v>1.01</v>
+      </c>
+      <c r="AF134">
+        <v>2.05</v>
+      </c>
+      <c r="AG134">
         <v>1.69</v>
       </c>
-      <c r="O134">
-        <v>3.6</v>
-      </c>
-      <c r="P134">
-        <v>5.3</v>
-      </c>
-      <c r="Q134">
-        <v>2.27</v>
-      </c>
-      <c r="R134">
-        <v>2.25</v>
-      </c>
-      <c r="S134">
-        <v>1.39</v>
-      </c>
-      <c r="T134">
-        <v>2.92</v>
-      </c>
-      <c r="U134">
-        <v>2.97</v>
-      </c>
-      <c r="V134">
-        <v>1.38</v>
-      </c>
-      <c r="W134">
-        <v>1.04</v>
-      </c>
-      <c r="X134">
-        <v>1.01</v>
-      </c>
-      <c r="Y134">
-        <v>1.28</v>
-      </c>
-      <c r="Z134">
-        <v>3.37</v>
-      </c>
-      <c r="AA134">
-        <v>2</v>
-      </c>
-      <c r="AB134">
-        <v>1.76</v>
-      </c>
-      <c r="AC134">
-        <v>3.28</v>
-      </c>
-      <c r="AD134">
-        <v>1.25</v>
-      </c>
-      <c r="AE134">
-        <v>1.11</v>
-      </c>
-      <c r="AF134">
-        <v>1.88</v>
-      </c>
-      <c r="AG134">
-        <v>1.8</v>
-      </c>
       <c r="AH134" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK134">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="O135">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P135">
-        <v>3.46</v>
+        <v>5.3</v>
       </c>
       <c r="Q135">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="R135">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="T135">
-        <v>2.33</v>
+        <v>2.92</v>
       </c>
       <c r="U135">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="V135">
+        <v>1.38</v>
+      </c>
+      <c r="W135">
+        <v>1.04</v>
+      </c>
+      <c r="X135">
+        <v>1.01</v>
+      </c>
+      <c r="Y135">
+        <v>1.28</v>
+      </c>
+      <c r="Z135">
+        <v>3.37</v>
+      </c>
+      <c r="AA135">
+        <v>2</v>
+      </c>
+      <c r="AB135">
+        <v>1.76</v>
+      </c>
+      <c r="AC135">
+        <v>3.28</v>
+      </c>
+      <c r="AD135">
         <v>1.25</v>
       </c>
-      <c r="W135">
-        <v>1.01</v>
-      </c>
-      <c r="X135">
-        <v>1.06</v>
-      </c>
-      <c r="Y135">
-        <v>1.47</v>
-      </c>
-      <c r="Z135">
-        <v>2.65</v>
-      </c>
-      <c r="AA135">
-        <v>2.48</v>
-      </c>
-      <c r="AB135">
-        <v>1.53</v>
-      </c>
-      <c r="AC135">
-        <v>4.4</v>
-      </c>
-      <c r="AD135">
-        <v>1.18</v>
-      </c>
       <c r="AE135">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AG135">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK135">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,31 +23292,31 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P141">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q141">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="R141">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S141">
         <v>1.44</v>
       </c>
       <c r="T141">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U141">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V141">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W141">
         <v>0</v>
@@ -23325,31 +23325,31 @@
         <v>0</v>
       </c>
       <c r="Y141">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z141">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AA141">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AB141">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC141">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="AD141">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE141">
         <v>0</v>
       </c>
       <c r="AF141">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG141">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK141">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,80 +23455,80 @@
         </is>
       </c>
       <c r="N142">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O142">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P142">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q142">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="R142">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S142">
         <v>1.44</v>
       </c>
       <c r="T142">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U142">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="V142">
+        <v>1.3</v>
+      </c>
+      <c r="W142">
+        <v>0</v>
+      </c>
+      <c r="X142">
+        <v>0</v>
+      </c>
+      <c r="Y142">
+        <v>1.39</v>
+      </c>
+      <c r="Z142">
+        <v>2.59</v>
+      </c>
+      <c r="AA142">
+        <v>2.27</v>
+      </c>
+      <c r="AB142">
+        <v>1.55</v>
+      </c>
+      <c r="AC142">
+        <v>4.15</v>
+      </c>
+      <c r="AD142">
+        <v>1.16</v>
+      </c>
+      <c r="AE142">
+        <v>0</v>
+      </c>
+      <c r="AF142">
+        <v>1.93</v>
+      </c>
+      <c r="AG142">
+        <v>1.75</v>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ142">
         <v>1.28</v>
       </c>
-      <c r="W142">
-        <v>0</v>
-      </c>
-      <c r="X142">
-        <v>0</v>
-      </c>
-      <c r="Y142">
-        <v>1.36</v>
-      </c>
-      <c r="Z142">
-        <v>2.69</v>
-      </c>
-      <c r="AA142">
-        <v>2.19</v>
-      </c>
-      <c r="AB142">
-        <v>1.59</v>
-      </c>
-      <c r="AC142">
-        <v>3.94</v>
-      </c>
-      <c r="AD142">
-        <v>1.17</v>
-      </c>
-      <c r="AE142">
-        <v>0</v>
-      </c>
-      <c r="AF142">
-        <v>1.95</v>
-      </c>
-      <c r="AG142">
-        <v>1.74</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>1.26</v>
-      </c>
       <c r="AK142">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23633,28 +23633,28 @@
         <v>3.25</v>
       </c>
       <c r="S143">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T143">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="U143">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V143">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="W143">
         <v>1.25</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z143">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA143">
         <v>1.26</v>
@@ -23691,7 +23691,7 @@
         <v>1.06</v>
       </c>
       <c r="AK143">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23956,31 +23956,31 @@
         <v>2.5</v>
       </c>
       <c r="R145">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="S145">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T145">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U145">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V145">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W145">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X145">
         <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z145">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="AA145">
         <v>1.36</v>
@@ -23989,19 +23989,19 @@
         <v>3</v>
       </c>
       <c r="AC145">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AD145">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AE145">
+        <v>1.44</v>
+      </c>
+      <c r="AF145">
         <v>1.33</v>
       </c>
-      <c r="AF145">
-        <v>1.32</v>
-      </c>
       <c r="AG145">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O146">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P146">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q146">
         <v>1.91</v>
@@ -24122,19 +24122,19 @@
         <v>2.96</v>
       </c>
       <c r="S146">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T146">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="U146">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V146">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="W146">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X146">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>13</v>
       </c>
       <c r="AA146">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AB146">
-        <v>5.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC146">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AD146">
         <v>2.7</v>
       </c>
       <c r="AE146">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF146">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AG146">
         <v>3.94</v>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK146">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24279,7 +24279,7 @@
         <v>4.53</v>
       </c>
       <c r="Q147">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R147">
         <v>2.8</v>
@@ -24297,19 +24297,19 @@
         <v>1.94</v>
       </c>
       <c r="W147">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z147">
         <v>7.5</v>
       </c>
       <c r="AA147">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB147">
         <v>2.75</v>
@@ -24327,7 +24327,7 @@
         <v>1.34</v>
       </c>
       <c r="AG147">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AK147">
         <v>2.38</v>
@@ -24433,10 +24433,10 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O148">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P148">
         <v>3.52</v>
@@ -24448,16 +24448,16 @@
         <v>2.8</v>
       </c>
       <c r="S148">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T148">
         <v>4.65</v>
       </c>
       <c r="U148">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V148">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="W148">
         <v>1.25</v>
@@ -24466,16 +24466,16 @@
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z148">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA148">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AB148">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AC148">
         <v>1.73</v>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK148">
         <v>1.95</v>
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="O150">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P150">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="Q150">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="R150">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S150">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T150">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="U150">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V150">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W150">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X150">
         <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z150">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA150">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB150">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC150">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD150">
         <v>1.53</v>
       </c>
       <c r="AE150">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF150">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG150">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK150">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -27551,7 +27551,7 @@
         <v>3.85</v>
       </c>
       <c r="U167">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V167">
         <v>1.75</v>
@@ -29649,10 +29649,10 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O180">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P180">
         <v>2.55</v>
@@ -29673,7 +29673,7 @@
         <v>2.4</v>
       </c>
       <c r="V180">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W180">
         <v>1.11</v>
@@ -29833,10 +29833,10 @@
         <v>3.45</v>
       </c>
       <c r="U181">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V181">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W181">
         <v>1.13</v>
@@ -29981,10 +29981,10 @@
         <v>4.3</v>
       </c>
       <c r="P182">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q182">
-        <v>4.2</v>
+        <v>3.61</v>
       </c>
       <c r="R182">
         <v>2.45</v>
@@ -30138,7 +30138,7 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O183">
         <v>3.6</v>
@@ -30147,10 +30147,10 @@
         <v>2.62</v>
       </c>
       <c r="Q183">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="R183">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="S183">
         <v>1.26</v>
@@ -30165,7 +30165,7 @@
         <v>1.58</v>
       </c>
       <c r="W183">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X183">
         <v>1.03</v>
@@ -30211,7 +30211,7 @@
         <v>1.22</v>
       </c>
       <c r="AK183">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="O186">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="P186">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q186">
-        <v>4.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R186">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="S186">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="T186">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="U186">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="V186">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="W186">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X186">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y186">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="Z186">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AA186">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AB186">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AC186">
-        <v>6.05</v>
+        <v>4.4</v>
       </c>
       <c r="AD186">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AE186">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF186">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG186">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK186">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,80 +30790,80 @@
         </is>
       </c>
       <c r="N187">
-        <v>7</v>
+        <v>2.95</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="P187">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="Q187">
-        <v>8.550000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="R187">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="S187">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="T187">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="U187">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="V187">
+        <v>1.16</v>
+      </c>
+      <c r="W187">
+        <v>1.03</v>
+      </c>
+      <c r="X187">
+        <v>1.09</v>
+      </c>
+      <c r="Y187">
+        <v>1.61</v>
+      </c>
+      <c r="Z187">
+        <v>2.15</v>
+      </c>
+      <c r="AA187">
+        <v>2.88</v>
+      </c>
+      <c r="AB187">
+        <v>1.32</v>
+      </c>
+      <c r="AC187">
+        <v>6.05</v>
+      </c>
+      <c r="AD187">
+        <v>1.06</v>
+      </c>
+      <c r="AE187">
+        <v>1.02</v>
+      </c>
+      <c r="AF187">
+        <v>2.3</v>
+      </c>
+      <c r="AG187">
+        <v>1.57</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ187">
+        <v>1.36</v>
+      </c>
+      <c r="AK187">
         <v>1.28</v>
-      </c>
-      <c r="W187">
-        <v>1.05</v>
-      </c>
-      <c r="X187">
-        <v>1.04</v>
-      </c>
-      <c r="Y187">
-        <v>1.41</v>
-      </c>
-      <c r="Z187">
-        <v>2.52</v>
-      </c>
-      <c r="AA187">
-        <v>2.38</v>
-      </c>
-      <c r="AB187">
-        <v>1.53</v>
-      </c>
-      <c r="AC187">
-        <v>4.4</v>
-      </c>
-      <c r="AD187">
-        <v>1.14</v>
-      </c>
-      <c r="AE187">
-        <v>1.01</v>
-      </c>
-      <c r="AF187">
-        <v>2.5</v>
-      </c>
-      <c r="AG187">
-        <v>1.45</v>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ187">
-        <v>1.29</v>
-      </c>
-      <c r="AK187">
-        <v>1.08</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -36018,13 +36018,13 @@
         <v>2.17</v>
       </c>
       <c r="R219">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S219">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T219">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U219">
         <v>2.55</v>
@@ -36033,7 +36033,7 @@
         <v>1.38</v>
       </c>
       <c r="W219">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X219">
         <v>1.01</v>
@@ -36045,10 +36045,10 @@
         <v>3.42</v>
       </c>
       <c r="AA219">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB219">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC219">
         <v>3.05</v>
@@ -36057,13 +36057,13 @@
         <v>1.26</v>
       </c>
       <c r="AE219">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF219">
         <v>1.74</v>
       </c>
       <c r="AG219">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -39266,31 +39266,31 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O239">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P239">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q239">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R239">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S239">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T239">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U239">
         <v>2.12</v>
       </c>
       <c r="V239">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W239">
         <v>1.14</v>
@@ -39305,25 +39305,25 @@
         <v>5</v>
       </c>
       <c r="AA239">
+        <v>1.54</v>
+      </c>
+      <c r="AB239">
+        <v>2.25</v>
+      </c>
+      <c r="AC239">
+        <v>2.55</v>
+      </c>
+      <c r="AD239">
         <v>1.5</v>
-      </c>
-      <c r="AB239">
-        <v>2.5</v>
-      </c>
-      <c r="AC239">
-        <v>2.25</v>
-      </c>
-      <c r="AD239">
-        <v>1.57</v>
       </c>
       <c r="AE239">
         <v>1.2</v>
       </c>
       <c r="AF239">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG239">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK239">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39429,61 +39429,61 @@
         </is>
       </c>
       <c r="N240">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O240">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="P240">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q240">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R240">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="S240">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T240">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="U240">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="V240">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W240">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X240">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z240">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA240">
         <v>1.45</v>
       </c>
       <c r="AB240">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC240">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD240">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE240">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF240">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG240">
         <v>1.81</v>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK240">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -42698,10 +42698,10 @@
         <v>2.62</v>
       </c>
       <c r="Q260">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R260">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S260">
         <v>1.46</v>
@@ -42728,19 +42728,19 @@
         <v>2.8</v>
       </c>
       <c r="AA260">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AB260">
         <v>1.58</v>
       </c>
       <c r="AC260">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD260">
         <v>1.2</v>
       </c>
       <c r="AE260">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF260">
         <v>2</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O261">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="P261">
-        <v>15.92</v>
+        <v>15</v>
       </c>
       <c r="Q261">
         <v>1.52</v>
@@ -42903,7 +42903,7 @@
         <v>1.65</v>
       </c>
       <c r="AE261">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF261">
         <v>2.3</v>
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK261">
         <v>5.5</v>
@@ -43887,7 +43887,7 @@
         <v>1.5</v>
       </c>
       <c r="AG267">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -44482,25 +44482,25 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="O271">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P271">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="Q271">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="R271">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S271">
         <v>1.29</v>
       </c>
       <c r="T271">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U271">
         <v>2.38</v>
@@ -44509,37 +44509,37 @@
         <v>1.5</v>
       </c>
       <c r="W271">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X271">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y271">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z271">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA271">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB271">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC271">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD271">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE271">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF271">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG271">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44645,25 +44645,25 @@
         </is>
       </c>
       <c r="N272">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="O272">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P272">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Q272">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="R272">
         <v>2.38</v>
       </c>
       <c r="S272">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T272">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U272">
         <v>2.17</v>
@@ -44672,16 +44672,16 @@
         <v>1.53</v>
       </c>
       <c r="W272">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X272">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y272">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z272">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA272">
         <v>1.56</v>
@@ -44696,7 +44696,7 @@
         <v>1.47</v>
       </c>
       <c r="AE272">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF272">
         <v>1.56</v>
@@ -44715,7 +44715,7 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AK272">
         <v>1.16</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="O279">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="P279">
-        <v>6.5</v>
+        <v>2.17</v>
       </c>
       <c r="Q279">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="R279">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S279">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T279">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="U279">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V279">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W279">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X279">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z279">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA279">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB279">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC279">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AD279">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE279">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF279">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG279">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK279">
-        <v>2.28</v>
+        <v>1.41</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="O280">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="P280">
-        <v>2.17</v>
+        <v>6.5</v>
       </c>
       <c r="Q280">
+        <v>1.91</v>
+      </c>
+      <c r="R280">
+        <v>2.4</v>
+      </c>
+      <c r="S280">
+        <v>1.24</v>
+      </c>
+      <c r="T280">
         <v>3.3</v>
       </c>
-      <c r="R280">
-        <v>2.2</v>
-      </c>
-      <c r="S280">
-        <v>1.3</v>
-      </c>
-      <c r="T280">
-        <v>3.09</v>
-      </c>
       <c r="U280">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V280">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W280">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X280">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y280">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z280">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA280">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB280">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC280">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AD280">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE280">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF280">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG280">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK280">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46785,7 +46785,7 @@
         <v>2.65</v>
       </c>
       <c r="U285">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V285">
         <v>1.3</v>
@@ -46797,16 +46797,16 @@
         <v>1.03</v>
       </c>
       <c r="Y285">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z285">
         <v>2.73</v>
       </c>
       <c r="AA285">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB285">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC285">
         <v>4.33</v>
@@ -48723,10 +48723,10 @@
         <v>1.75</v>
       </c>
       <c r="O297">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P297">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="Q297">
         <v>2.33</v>
@@ -48765,7 +48765,7 @@
         <v>1.83</v>
       </c>
       <c r="AC297">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="AD297">
         <v>1.29</v>
@@ -48774,10 +48774,10 @@
         <v>1.11</v>
       </c>
       <c r="AF297">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG297">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -49046,34 +49046,34 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="O299">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P299">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q299">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R299">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="S299">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T299">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U299">
+        <v>1.87</v>
+      </c>
+      <c r="V299">
         <v>1.81</v>
       </c>
-      <c r="V299">
-        <v>1.86</v>
-      </c>
       <c r="W299">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X299">
         <v>1.01</v>
@@ -49085,13 +49085,13 @@
         <v>8</v>
       </c>
       <c r="AA299">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB299">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AC299">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AD299">
         <v>1.94</v>
@@ -49100,10 +49100,10 @@
         <v>1.4</v>
       </c>
       <c r="AF299">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG299">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK299">
         <v>3.05</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="O300">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P300">
-        <v>3.33</v>
+        <v>4.63</v>
       </c>
       <c r="Q300">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="R300">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S300">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="T300">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U300">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="V300">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="W300">
         <v>1.03</v>
       </c>
       <c r="X300">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Y300">
+        <v>1.37</v>
+      </c>
+      <c r="Z300">
+        <v>2.63</v>
+      </c>
+      <c r="AA300">
+        <v>2.14</v>
+      </c>
+      <c r="AB300">
         <v>1.58</v>
       </c>
-      <c r="Z300">
-        <v>2.2</v>
-      </c>
-      <c r="AA300">
-        <v>2.74</v>
-      </c>
-      <c r="AB300">
-        <v>1.35</v>
-      </c>
       <c r="AC300">
-        <v>6.29</v>
+        <v>4.2</v>
       </c>
       <c r="AD300">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE300">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF300">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AG300">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK300">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="O302">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P302">
-        <v>4.63</v>
+        <v>3.33</v>
       </c>
       <c r="Q302">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="R302">
+        <v>1.85</v>
+      </c>
+      <c r="S302">
+        <v>1.63</v>
+      </c>
+      <c r="T302">
         <v>2.1</v>
       </c>
-      <c r="S302">
-        <v>1.43</v>
-      </c>
-      <c r="T302">
-        <v>2.45</v>
-      </c>
       <c r="U302">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="V302">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="W302">
         <v>1.03</v>
       </c>
       <c r="X302">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Y302">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="Z302">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AA302">
-        <v>2.14</v>
+        <v>2.74</v>
       </c>
       <c r="AB302">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AC302">
-        <v>4.2</v>
+        <v>6.29</v>
       </c>
       <c r="AD302">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE302">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF302">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AG302">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK302">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="O306">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P306">
-        <v>3.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q306">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="R306">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S306">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T306">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U306">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V306">
         <v>1.29</v>
       </c>
       <c r="W306">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X306">
         <v>1.05</v>
       </c>
       <c r="Y306">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z306">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA306">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB306">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AC306">
         <v>4.5</v>
       </c>
       <c r="AD306">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE306">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF306">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG306">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>1.3</v>
       </c>
       <c r="AK306">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="O307">
         <v>2.95</v>
       </c>
       <c r="P307">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q307">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R307">
+        <v>1.85</v>
+      </c>
+      <c r="S307">
+        <v>1.5</v>
+      </c>
+      <c r="T307">
+        <v>2.41</v>
+      </c>
+      <c r="U307">
+        <v>3.6</v>
+      </c>
+      <c r="V307">
+        <v>1.25</v>
+      </c>
+      <c r="W307">
+        <v>1.02</v>
+      </c>
+      <c r="X307">
+        <v>1.06</v>
+      </c>
+      <c r="Y307">
+        <v>1.42</v>
+      </c>
+      <c r="Z307">
+        <v>2.49</v>
+      </c>
+      <c r="AA307">
+        <v>2.34</v>
+      </c>
+      <c r="AB307">
+        <v>1.51</v>
+      </c>
+      <c r="AC307">
+        <v>5</v>
+      </c>
+      <c r="AD307">
+        <v>1.14</v>
+      </c>
+      <c r="AE307">
+        <v>1.02</v>
+      </c>
+      <c r="AF307">
         <v>2.01</v>
       </c>
-      <c r="S307">
-        <v>1.52</v>
-      </c>
-      <c r="T307">
-        <v>2.31</v>
-      </c>
-      <c r="U307">
-        <v>3.25</v>
-      </c>
-      <c r="V307">
-        <v>1.29</v>
-      </c>
-      <c r="W307">
-        <v>1.04</v>
-      </c>
-      <c r="X307">
-        <v>1.05</v>
-      </c>
-      <c r="Y307">
-        <v>1.44</v>
-      </c>
-      <c r="Z307">
-        <v>2.7</v>
-      </c>
-      <c r="AA307">
-        <v>2.27</v>
-      </c>
-      <c r="AB307">
-        <v>1.44</v>
-      </c>
-      <c r="AC307">
-        <v>4.5</v>
-      </c>
-      <c r="AD307">
-        <v>1.17</v>
-      </c>
-      <c r="AE307">
-        <v>1.05</v>
-      </c>
-      <c r="AF307">
-        <v>1.95</v>
-      </c>
       <c r="AG307">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK307">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O308">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P308">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q308">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R308">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S308">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T308">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U308">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="V308">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W308">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X308">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y308">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z308">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AA308">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB308">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AC308">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD308">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE308">
         <v>1.02</v>
       </c>
       <c r="AF308">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AG308">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK308">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -51168,7 +51168,7 @@
         <v>5.29</v>
       </c>
       <c r="O312">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P312">
         <v>1.43</v>
@@ -51238,7 +51238,7 @@
         <v>2.37</v>
       </c>
       <c r="AK312">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51328,37 +51328,37 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="O313">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P313">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q313">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="R313">
         <v>2.32</v>
       </c>
       <c r="S313">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T313">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U313">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V313">
         <v>1.42</v>
       </c>
       <c r="W313">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X313">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y313">
         <v>1.3</v>
@@ -51382,10 +51382,10 @@
         <v>1.09</v>
       </c>
       <c r="AF313">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG313">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51672,13 +51672,13 @@
         <v>1.47</v>
       </c>
       <c r="T315">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U315">
         <v>3.2</v>
       </c>
       <c r="V315">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W315">
         <v>1.03</v>
@@ -51696,7 +51696,7 @@
         <v>2.2</v>
       </c>
       <c r="AB315">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC315">
         <v>4.5</v>
@@ -52306,19 +52306,19 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="O319">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P319">
-        <v>3.43</v>
+        <v>3.85</v>
       </c>
       <c r="Q319">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="R319">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S319">
         <v>1.22</v>
@@ -52327,13 +52327,13 @@
         <v>3.75</v>
       </c>
       <c r="U319">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V319">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W319">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X319">
         <v>1.02</v>
@@ -52342,28 +52342,28 @@
         <v>1.14</v>
       </c>
       <c r="Z319">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA319">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB319">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AC319">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD319">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE319">
         <v>1.19</v>
       </c>
       <c r="AF319">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG319">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK319">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="O322">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P322">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q322">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R322">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S322">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T322">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U322">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="V322">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W322">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X322">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y322">
         <v>1.36</v>
       </c>
       <c r="Z322">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA322">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB322">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC322">
-        <v>4.28</v>
+        <v>3.75</v>
       </c>
       <c r="AD322">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE322">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF322">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AG322">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK322">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="O323">
+        <v>3.4</v>
+      </c>
+      <c r="P323">
+        <v>5.4</v>
+      </c>
+      <c r="Q323">
+        <v>2.25</v>
+      </c>
+      <c r="R323">
+        <v>2.08</v>
+      </c>
+      <c r="S323">
+        <v>1.44</v>
+      </c>
+      <c r="T323">
+        <v>2.5</v>
+      </c>
+      <c r="U323">
         <v>3.3</v>
       </c>
-      <c r="P323">
-        <v>4.2</v>
-      </c>
-      <c r="Q323">
-        <v>2.45</v>
-      </c>
-      <c r="R323">
-        <v>2.1</v>
-      </c>
-      <c r="S323">
-        <v>1.42</v>
-      </c>
-      <c r="T323">
-        <v>2.56</v>
-      </c>
-      <c r="U323">
-        <v>3.06</v>
-      </c>
       <c r="V323">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W323">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X323">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y323">
         <v>1.36</v>
       </c>
       <c r="Z323">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA323">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB323">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC323">
-        <v>3.75</v>
+        <v>4.28</v>
       </c>
       <c r="AD323">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE323">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF323">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AG323">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK323">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53628,16 +53628,16 @@
         <v>1.42</v>
       </c>
       <c r="T327">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U327">
         <v>2.95</v>
       </c>
       <c r="V327">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W327">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X327">
         <v>1.05</v>
@@ -53649,7 +53649,7 @@
         <v>2.95</v>
       </c>
       <c r="AA327">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB327">
         <v>1.65</v>
@@ -53658,13 +53658,13 @@
         <v>3.48</v>
       </c>
       <c r="AD327">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE327">
         <v>1.06</v>
       </c>
       <c r="AF327">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG327">
         <v>1.7</v>
@@ -53803,7 +53803,7 @@
         <v>1.08</v>
       </c>
       <c r="X328">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y328">
         <v>1.26</v>
@@ -53815,7 +53815,7 @@
         <v>1.87</v>
       </c>
       <c r="AB328">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC328">
         <v>3</v>
@@ -53945,10 +53945,10 @@
         <v>0</v>
       </c>
       <c r="Q329">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R329">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="S329">
         <v>1.14</v>
@@ -53957,13 +53957,13 @@
         <v>4.8</v>
       </c>
       <c r="U329">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V329">
         <v>1.8</v>
       </c>
       <c r="W329">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X329">
         <v>1.01</v>
@@ -53978,7 +53978,7 @@
         <v>1.3</v>
       </c>
       <c r="AB329">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AC329">
         <v>1.9</v>
@@ -54009,7 +54009,7 @@
         <v>1.13</v>
       </c>
       <c r="AK329">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>5.72</v>
+        <v>5.5</v>
       </c>
       <c r="O330">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P330">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q330">
         <v>5</v>
@@ -54117,10 +54117,10 @@
         <v>1.17</v>
       </c>
       <c r="T330">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U330">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V330">
         <v>1.75</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AD10">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
+        <v>1.24</v>
+      </c>
+      <c r="Z11">
+        <v>3.5</v>
+      </c>
+      <c r="AA11">
+        <v>1.95</v>
+      </c>
+      <c r="AB11">
+        <v>1.85</v>
+      </c>
+      <c r="AC11">
+        <v>2.97</v>
+      </c>
+      <c r="AD11">
+        <v>1.35</v>
+      </c>
+      <c r="AE11">
+        <v>1.1</v>
+      </c>
+      <c r="AF11">
+        <v>1.67</v>
+      </c>
+      <c r="AG11">
+        <v>1.94</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.25</v>
       </c>
-      <c r="Z11">
-        <v>3.3</v>
-      </c>
-      <c r="AA11">
-        <v>1.91</v>
-      </c>
-      <c r="AB11">
-        <v>1.8</v>
-      </c>
-      <c r="AC11">
-        <v>3.4</v>
-      </c>
-      <c r="AD11">
-        <v>1.29</v>
-      </c>
-      <c r="AE11">
-        <v>1.12</v>
-      </c>
-      <c r="AF11">
-        <v>1.69</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.26</v>
-      </c>
       <c r="AK11">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O17">
         <v>2.81</v>
       </c>
       <c r="P17">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18">
         <v>3.25</v>
       </c>
-      <c r="O18">
-        <v>3.1</v>
-      </c>
       <c r="P18">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -6669,7 +6669,7 @@
         <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
         <v>2.9</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -7321,10 +7321,10 @@
         <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="P43">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
         <v>2.1</v>
       </c>
-      <c r="O61">
-        <v>3.75</v>
-      </c>
-      <c r="P61">
-        <v>2.8</v>
-      </c>
-      <c r="Q61">
-        <v>2.4</v>
-      </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="V61">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA61">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AB61">
-        <v>2.48</v>
+        <v>3.16</v>
       </c>
       <c r="AC61">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD61">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AG61">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q62">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U62">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA62">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AB62">
-        <v>3.16</v>
+        <v>2.48</v>
       </c>
       <c r="AC62">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD62">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AE62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG62">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G106">
@@ -17596,56 +17596,56 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>2.96</v>
+        <v>1.95</v>
       </c>
       <c r="R106">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T106">
-        <v>2.92</v>
+        <v>3.32</v>
       </c>
       <c r="U106">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="V106">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="AA106">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AB106">
+        <v>2.04</v>
+      </c>
+      <c r="AC106">
+        <v>2.7</v>
+      </c>
+      <c r="AD106">
+        <v>1.36</v>
+      </c>
+      <c r="AE106">
+        <v>1.1</v>
+      </c>
+      <c r="AF106">
+        <v>1.8</v>
+      </c>
+      <c r="AG106">
         <v>1.9</v>
       </c>
-      <c r="AC106">
-        <v>3.25</v>
-      </c>
-      <c r="AD106">
-        <v>1.28</v>
-      </c>
-      <c r="AE106">
-        <v>1.07</v>
-      </c>
-      <c r="AF106">
-        <v>1.67</v>
-      </c>
-      <c r="AG106">
-        <v>2.05</v>
-      </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AK106">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1.95</v>
+        <v>2.96</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S107">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T107">
-        <v>3.32</v>
+        <v>2.92</v>
       </c>
       <c r="U107">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="V107">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z107">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
       <c r="AA107">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AB107">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AC107">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD107">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O110">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P110">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q110">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="R110">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S110">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T110">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="U110">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="V110">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y110">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z110">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AA110">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB110">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC110">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD110">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE110">
         <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK110">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
+        <v>2.15</v>
+      </c>
+      <c r="O111">
+        <v>2.9</v>
+      </c>
+      <c r="P111">
+        <v>3.2</v>
+      </c>
+      <c r="Q111">
+        <v>3.02</v>
+      </c>
+      <c r="R111">
+        <v>1.91</v>
+      </c>
+      <c r="S111">
+        <v>1.55</v>
+      </c>
+      <c r="T111">
+        <v>2.39</v>
+      </c>
+      <c r="U111">
+        <v>3.42</v>
+      </c>
+      <c r="V111">
+        <v>1.23</v>
+      </c>
+      <c r="W111">
+        <v>1.01</v>
+      </c>
+      <c r="X111">
+        <v>1.11</v>
+      </c>
+      <c r="Y111">
+        <v>1.47</v>
+      </c>
+      <c r="Z111">
+        <v>2.4</v>
+      </c>
+      <c r="AA111">
         <v>2.5</v>
       </c>
-      <c r="O111">
-        <v>3</v>
-      </c>
-      <c r="P111">
-        <v>2.7</v>
-      </c>
-      <c r="Q111">
-        <v>3.4</v>
-      </c>
-      <c r="R111">
-        <v>1.95</v>
-      </c>
-      <c r="S111">
-        <v>1.5</v>
-      </c>
-      <c r="T111">
-        <v>2.31</v>
-      </c>
-      <c r="U111">
-        <v>3.25</v>
-      </c>
-      <c r="V111">
-        <v>1.25</v>
-      </c>
-      <c r="W111">
-        <v>1.03</v>
-      </c>
-      <c r="X111">
-        <v>1.1</v>
-      </c>
-      <c r="Y111">
-        <v>1.4</v>
-      </c>
-      <c r="Z111">
-        <v>2.5</v>
-      </c>
-      <c r="AA111">
-        <v>2.25</v>
-      </c>
       <c r="AB111">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC111">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD111">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE111">
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q129">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="R129">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S129">
         <v>1.4</v>
@@ -21357,10 +21357,10 @@
         <v>2.6</v>
       </c>
       <c r="U129">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="V129">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W129">
         <v>0</v>
@@ -21369,22 +21369,22 @@
         <v>0</v>
       </c>
       <c r="Y129">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z129">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA129">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB129">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC129">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AD129">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE129">
         <v>0</v>
@@ -21393,7 +21393,7 @@
         <v>1.83</v>
       </c>
       <c r="AG129">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,31 +21499,31 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>2.58</v>
+        <v>3.24</v>
       </c>
       <c r="R130">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S130">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T130">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U130">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="V130">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W130">
         <v>0</v>
@@ -21532,31 +21532,31 @@
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z130">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA130">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB130">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC130">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD130">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE130">
         <v>0</v>
       </c>
       <c r="AF130">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG130">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>1.25</v>
       </c>
       <c r="AK130">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G131">
@@ -21671,22 +21671,22 @@
         <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.24</v>
+        <v>2.79</v>
       </c>
       <c r="R131">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S131">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U131">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="V131">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W131">
         <v>0</v>
@@ -21695,31 +21695,31 @@
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z131">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA131">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB131">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC131">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="AD131">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE131">
         <v>0</v>
       </c>
       <c r="AF131">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AG131">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK131">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,80 +23292,80 @@
         </is>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O141">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P141">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q141">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="R141">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S141">
         <v>1.44</v>
       </c>
       <c r="T141">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U141">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="V141">
+        <v>1.3</v>
+      </c>
+      <c r="W141">
+        <v>0</v>
+      </c>
+      <c r="X141">
+        <v>0</v>
+      </c>
+      <c r="Y141">
+        <v>1.39</v>
+      </c>
+      <c r="Z141">
+        <v>2.59</v>
+      </c>
+      <c r="AA141">
+        <v>2.27</v>
+      </c>
+      <c r="AB141">
+        <v>1.55</v>
+      </c>
+      <c r="AC141">
+        <v>4.15</v>
+      </c>
+      <c r="AD141">
+        <v>1.16</v>
+      </c>
+      <c r="AE141">
+        <v>0</v>
+      </c>
+      <c r="AF141">
+        <v>1.93</v>
+      </c>
+      <c r="AG141">
+        <v>1.75</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
         <v>1.28</v>
       </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>1.36</v>
-      </c>
-      <c r="Z141">
-        <v>2.69</v>
-      </c>
-      <c r="AA141">
-        <v>2.19</v>
-      </c>
-      <c r="AB141">
-        <v>1.59</v>
-      </c>
-      <c r="AC141">
-        <v>3.94</v>
-      </c>
-      <c r="AD141">
-        <v>1.17</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>1.95</v>
-      </c>
-      <c r="AG141">
-        <v>1.74</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>1.26</v>
-      </c>
       <c r="AK141">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,31 +23455,31 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O142">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="Q142">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="R142">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S142">
         <v>1.44</v>
       </c>
       <c r="T142">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U142">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V142">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W142">
         <v>0</v>
@@ -23488,31 +23488,31 @@
         <v>0</v>
       </c>
       <c r="Y142">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z142">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AA142">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AB142">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AC142">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="AD142">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE142">
         <v>0</v>
       </c>
       <c r="AF142">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG142">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK142">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="O155">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P155">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q155">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="R155">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T155">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U155">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="V155">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W155">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y155">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z155">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA155">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AB155">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC155">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD155">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF155">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AG155">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK155">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,31 +25737,31 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O156">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="P156">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q156">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="R156">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S156">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T156">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="U156">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V156">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W156">
         <v>0</v>
@@ -25770,31 +25770,31 @@
         <v>0</v>
       </c>
       <c r="Y156">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z156">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AA156">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB156">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC156">
-        <v>3.34</v>
+        <v>3.92</v>
       </c>
       <c r="AD156">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF156">
         <v>1.88</v>
       </c>
       <c r="AG156">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK156">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,19 +25900,19 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O157">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P157">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q157">
-        <v>2.99</v>
+        <v>1.97</v>
       </c>
       <c r="R157">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S157">
         <v>1.39</v>
@@ -25921,59 +25921,59 @@
         <v>2.64</v>
       </c>
       <c r="U157">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="V157">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y157">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z157">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA157">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB157">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC157">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="AD157">
+        <v>1.24</v>
+      </c>
+      <c r="AE157">
+        <v>1.08</v>
+      </c>
+      <c r="AF157">
+        <v>2.2</v>
+      </c>
+      <c r="AG157">
+        <v>1.57</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.17</v>
       </c>
-      <c r="AE157">
-        <v>0</v>
-      </c>
-      <c r="AF157">
-        <v>1.84</v>
-      </c>
-      <c r="AG157">
-        <v>1.83</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.27</v>
-      </c>
       <c r="AK157">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q158">
+        <v>1.98</v>
+      </c>
+      <c r="R158">
         <v>2.1</v>
       </c>
-      <c r="R158">
-        <v>2.08</v>
-      </c>
       <c r="S158">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T158">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="U158">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V158">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y158">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z158">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA158">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB158">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC158">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD158">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF158">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AG158">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK158">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O192">
         <v>3.1</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O194">
         <v>3.05</v>
@@ -32257,31 +32257,31 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W196">
         <v>0</v>
@@ -32290,31 +32290,31 @@
         <v>0</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK196">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -35523,7 +35523,7 @@
         <v>3.1</v>
       </c>
       <c r="P216">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35556,10 +35556,10 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC216">
         <v>0</v>
@@ -40733,19 +40733,19 @@
         </is>
       </c>
       <c r="N248">
+        <v>2.5</v>
+      </c>
+      <c r="O248">
+        <v>3</v>
+      </c>
+      <c r="P248">
         <v>2.65</v>
       </c>
-      <c r="O248">
-        <v>3.2</v>
-      </c>
-      <c r="P248">
-        <v>2.75</v>
-      </c>
       <c r="Q248">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R248">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S248">
         <v>1.42</v>
@@ -40766,10 +40766,10 @@
         <v>0</v>
       </c>
       <c r="Y248">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z248">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA248">
         <v>2.23</v>
@@ -40778,13 +40778,13 @@
         <v>1.57</v>
       </c>
       <c r="AC248">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD248">
         <v>1.16</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF248">
         <v>1.88</v>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK248">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O262">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P262">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43178,10 +43178,10 @@
         </is>
       </c>
       <c r="N263">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O263">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P263">
         <v>4.4</v>
@@ -43341,7 +43341,7 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="O264">
         <v>2.97</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="O279">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="P279">
-        <v>2.17</v>
+        <v>6.5</v>
       </c>
       <c r="Q279">
+        <v>1.91</v>
+      </c>
+      <c r="R279">
+        <v>2.4</v>
+      </c>
+      <c r="S279">
+        <v>1.24</v>
+      </c>
+      <c r="T279">
         <v>3.3</v>
       </c>
-      <c r="R279">
-        <v>2.2</v>
-      </c>
-      <c r="S279">
-        <v>1.3</v>
-      </c>
-      <c r="T279">
-        <v>3.09</v>
-      </c>
       <c r="U279">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V279">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W279">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X279">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y279">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z279">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA279">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB279">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC279">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AD279">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE279">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF279">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG279">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK279">
-        <v>1.41</v>
+        <v>2.28</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="O280">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="P280">
-        <v>6.5</v>
+        <v>2.17</v>
       </c>
       <c r="Q280">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="R280">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S280">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T280">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="U280">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V280">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W280">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X280">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y280">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z280">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA280">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB280">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC280">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AD280">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE280">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF280">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG280">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK280">
-        <v>2.28</v>
+        <v>1.41</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46151,7 +46151,7 @@
         <v>3.95</v>
       </c>
       <c r="AA281">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB281">
         <v>2.05</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="O282">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P282">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -47579,7 +47579,7 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O290">
         <v>2.65</v>
@@ -47597,7 +47597,7 @@
         <v>1.67</v>
       </c>
       <c r="T290">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U290">
         <v>4.5</v>
@@ -47618,10 +47618,10 @@
         <v>2.07</v>
       </c>
       <c r="AA290">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="AB290">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC290">
         <v>7.1</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O291">
         <v>2.8</v>
       </c>
       <c r="P291">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q291">
         <v>2.9</v>
@@ -47763,7 +47763,7 @@
         <v>2.18</v>
       </c>
       <c r="U291">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="V291">
         <v>1.2</v>
@@ -47787,10 +47787,10 @@
         <v>1.38</v>
       </c>
       <c r="AC291">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="AD291">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE291">
         <v>1.03</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O292">
         <v>3.4</v>
@@ -47914,10 +47914,10 @@
         <v>6</v>
       </c>
       <c r="Q292">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="R292">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S292">
         <v>1.5</v>
@@ -47926,10 +47926,10 @@
         <v>2.4</v>
       </c>
       <c r="U292">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="V292">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W292">
         <v>1.02</v>
@@ -47938,7 +47938,7 @@
         <v>1.11</v>
       </c>
       <c r="Y292">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z292">
         <v>2.45</v>
@@ -47950,13 +47950,13 @@
         <v>1.44</v>
       </c>
       <c r="AC292">
-        <v>5.17</v>
+        <v>5.05</v>
       </c>
       <c r="AD292">
         <v>1.15</v>
       </c>
       <c r="AE292">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF292">
         <v>2.18</v>
@@ -48883,16 +48883,16 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="O298">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P298">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q298">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R298">
         <v>2.23</v>
@@ -48910,7 +48910,7 @@
         <v>1.36</v>
       </c>
       <c r="W298">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X298">
         <v>1</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,80 +49209,80 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="O300">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P300">
-        <v>4.63</v>
+        <v>3.6</v>
       </c>
       <c r="Q300">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="R300">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S300">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="T300">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="U300">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="V300">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W300">
+        <v>1.04</v>
+      </c>
+      <c r="X300">
+        <v>1.1</v>
+      </c>
+      <c r="Y300">
+        <v>1.57</v>
+      </c>
+      <c r="Z300">
+        <v>2.38</v>
+      </c>
+      <c r="AA300">
+        <v>2.75</v>
+      </c>
+      <c r="AB300">
+        <v>1.36</v>
+      </c>
+      <c r="AC300">
+        <v>6</v>
+      </c>
+      <c r="AD300">
+        <v>1.13</v>
+      </c>
+      <c r="AE300">
         <v>1.03</v>
       </c>
-      <c r="X300">
-        <v>1.06</v>
-      </c>
-      <c r="Y300">
-        <v>1.37</v>
-      </c>
-      <c r="Z300">
-        <v>2.63</v>
-      </c>
-      <c r="AA300">
-        <v>2.14</v>
-      </c>
-      <c r="AB300">
+      <c r="AF300">
+        <v>2.25</v>
+      </c>
+      <c r="AG300">
+        <v>1.53</v>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ300">
+        <v>1.2</v>
+      </c>
+      <c r="AK300">
         <v>1.58</v>
-      </c>
-      <c r="AC300">
-        <v>4.2</v>
-      </c>
-      <c r="AD300">
-        <v>1.22</v>
-      </c>
-      <c r="AE300">
-        <v>1.06</v>
-      </c>
-      <c r="AF300">
-        <v>2</v>
-      </c>
-      <c r="AG300">
-        <v>1.6</v>
-      </c>
-      <c r="AH300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ300">
-        <v>1.26</v>
-      </c>
-      <c r="AK300">
-        <v>1.91</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,28 +49372,28 @@
         </is>
       </c>
       <c r="N301">
+        <v>2.25</v>
+      </c>
+      <c r="O301">
+        <v>2.8</v>
+      </c>
+      <c r="P301">
+        <v>3.3</v>
+      </c>
+      <c r="Q301">
+        <v>3.1</v>
+      </c>
+      <c r="R301">
+        <v>1.85</v>
+      </c>
+      <c r="S301">
+        <v>1.65</v>
+      </c>
+      <c r="T301">
         <v>2.1</v>
       </c>
-      <c r="O301">
-        <v>2.87</v>
-      </c>
-      <c r="P301">
-        <v>3.6</v>
-      </c>
-      <c r="Q301">
-        <v>2.66</v>
-      </c>
-      <c r="R301">
-        <v>1.83</v>
-      </c>
-      <c r="S301">
-        <v>1.57</v>
-      </c>
-      <c r="T301">
-        <v>2.25</v>
-      </c>
       <c r="U301">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V301">
         <v>1.22</v>
@@ -49402,34 +49402,34 @@
         <v>1.03</v>
       </c>
       <c r="X301">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y301">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z301">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AA301">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AB301">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC301">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AD301">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE301">
         <v>1.03</v>
       </c>
       <c r="AF301">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG301">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK301">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O302">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P302">
-        <v>3.33</v>
+        <v>5.05</v>
       </c>
       <c r="Q302">
+        <v>2.45</v>
+      </c>
+      <c r="R302">
+        <v>2.1</v>
+      </c>
+      <c r="S302">
+        <v>1.43</v>
+      </c>
+      <c r="T302">
+        <v>2.45</v>
+      </c>
+      <c r="U302">
         <v>3.1</v>
       </c>
-      <c r="R302">
-        <v>1.85</v>
-      </c>
-      <c r="S302">
-        <v>1.63</v>
-      </c>
-      <c r="T302">
-        <v>2.1</v>
-      </c>
-      <c r="U302">
-        <v>3.85</v>
-      </c>
       <c r="V302">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="W302">
         <v>1.03</v>
       </c>
       <c r="X302">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Y302">
+        <v>1.37</v>
+      </c>
+      <c r="Z302">
+        <v>2.63</v>
+      </c>
+      <c r="AA302">
+        <v>2.12</v>
+      </c>
+      <c r="AB302">
         <v>1.58</v>
       </c>
-      <c r="Z302">
-        <v>2.2</v>
-      </c>
-      <c r="AA302">
-        <v>2.74</v>
-      </c>
-      <c r="AB302">
-        <v>1.35</v>
-      </c>
       <c r="AC302">
-        <v>6.29</v>
+        <v>4.2</v>
       </c>
       <c r="AD302">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE302">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF302">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AG302">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK302">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O304">
         <v>3.3</v>
@@ -49891,7 +49891,7 @@
         <v>1.1</v>
       </c>
       <c r="X304">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y304">
         <v>1.2</v>
@@ -49900,22 +49900,22 @@
         <v>3.9</v>
       </c>
       <c r="AA304">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB304">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC304">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD304">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE304">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF304">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG304">
         <v>2.2</v>
@@ -49931,7 +49931,7 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK304">
         <v>1.6</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O310">
         <v>3</v>
       </c>
       <c r="P310">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q310">
         <v>2.6</v>
@@ -50857,7 +50857,7 @@
         <v>1.63</v>
       </c>
       <c r="T310">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U310">
         <v>3.75</v>
@@ -50887,7 +50887,7 @@
         <v>5</v>
       </c>
       <c r="AD310">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE310">
         <v>1.03</v>
@@ -50896,7 +50896,7 @@
         <v>2.2</v>
       </c>
       <c r="AG310">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -51494,25 +51494,25 @@
         <v>1.4</v>
       </c>
       <c r="O314">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P314">
         <v>6.97</v>
       </c>
       <c r="Q314">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="R314">
         <v>2.45</v>
       </c>
       <c r="S314">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T314">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="U314">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="V314">
         <v>1.55</v>
@@ -51521,7 +51521,7 @@
         <v>1.1</v>
       </c>
       <c r="X314">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y314">
         <v>1.18</v>
@@ -51542,7 +51542,7 @@
         <v>1.44</v>
       </c>
       <c r="AE314">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF314">
         <v>1.77</v>
@@ -51820,10 +51820,10 @@
         <v>2.15</v>
       </c>
       <c r="O316">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P316">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="Q316">
         <v>2.9</v>
@@ -51841,7 +51841,7 @@
         <v>3.6</v>
       </c>
       <c r="V316">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W316">
         <v>1.01</v>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O318">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="P318">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q318">
         <v>2.8</v>
@@ -52164,25 +52164,25 @@
         <v>2.55</v>
       </c>
       <c r="U318">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V318">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W318">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X318">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y318">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Z318">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="AA318">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AB318">
         <v>1.58</v>
@@ -52490,16 +52490,16 @@
         <v>2.3</v>
       </c>
       <c r="U320">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="V320">
         <v>1.22</v>
       </c>
       <c r="W320">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X320">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y320">
         <v>1.53</v>
@@ -52508,16 +52508,16 @@
         <v>2.5</v>
       </c>
       <c r="AA320">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AB320">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC320">
         <v>6</v>
       </c>
       <c r="AD320">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE320">
         <v>1.03</v>
@@ -52632,34 +52632,34 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O321">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P321">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="Q321">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R321">
         <v>2.5</v>
       </c>
       <c r="S321">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T321">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U321">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V321">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W321">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X321">
         <v>1.02</v>
@@ -52677,19 +52677,19 @@
         <v>2.5</v>
       </c>
       <c r="AC321">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AD321">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE321">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF321">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG321">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>1.22</v>
       </c>
       <c r="AK321">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -53127,13 +53127,13 @@
         <v>4.1</v>
       </c>
       <c r="P324">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q324">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="R324">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S324">
         <v>1.26</v>
@@ -53151,34 +53151,34 @@
         <v>1.11</v>
       </c>
       <c r="X324">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y324">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z324">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA324">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB324">
         <v>2.25</v>
       </c>
       <c r="AC324">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AD324">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE324">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF324">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG324">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>1.62</v>
       </c>
       <c r="R325">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="S325">
         <v>1.18</v>
@@ -53338,10 +53338,10 @@
         <v>1.3</v>
       </c>
       <c r="AF325">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG325">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="O326">
         <v>3.2</v>
@@ -53477,7 +53477,7 @@
         <v>1.1</v>
       </c>
       <c r="X326">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y326">
         <v>1.24</v>
@@ -54262,16 +54262,16 @@
         </is>
       </c>
       <c r="N331">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O331">
         <v>3.5</v>
       </c>
       <c r="P331">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q331">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R331">
         <v>2.4</v>
@@ -54298,10 +54298,10 @@
         <v>1.11</v>
       </c>
       <c r="Z331">
-        <v>5.61</v>
+        <v>5.75</v>
       </c>
       <c r="AA331">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB331">
         <v>2.5</v>
@@ -54316,7 +54316,7 @@
         <v>1.25</v>
       </c>
       <c r="AF331">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG331">
         <v>2.7</v>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK331">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL331">
         <v>0</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -631,17 +631,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="P2">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="Q2">
         <v>2.8</v>
@@ -696,19 +696,19 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1", "-1", "-1"]</t>
         </is>
       </c>
       <c r="AJ2">
         <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -790,39 +790,39 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
         <v>3.15</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
         <v>1.01</v>
@@ -831,7 +831,7 @@
         <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
         <v>2.88</v>
@@ -840,35 +840,35 @@
         <v>2.2</v>
       </c>
       <c r="AB3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
         <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "43"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74", "90+4"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AK3">
         <v>1.44</v>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,24 +950,24 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="O4">
         <v>3.1</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q4">
         <v>3.3</v>
@@ -982,7 +982,7 @@
         <v>2.75</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V4">
         <v>1.35</v>
@@ -991,10 +991,10 @@
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
         <v>2.88</v>
@@ -1006,23 +1006,23 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG4">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,33 +1101,33 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
         <v>2</v>
@@ -1145,13 +1145,13 @@
         <v>2.8</v>
       </c>
       <c r="U5">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="V5">
         <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.06</v>
@@ -1160,7 +1160,7 @@
         <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA5">
         <v>1.93</v>
@@ -1178,23 +1178,23 @@
         <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "68"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "76"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
         <v>1.22</v>
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O8">
         <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "89", "90+6"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "37"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1710,10 +1710,10 @@
         <v>0</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,36 +1753,36 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
         <v>2.95</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
@@ -1791,10 +1791,10 @@
         <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U9">
         <v>2.78</v>
@@ -1803,7 +1803,7 @@
         <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1812,10 +1812,10 @@
         <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB9">
         <v>1.7</v>
@@ -1837,46 +1837,46 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "66", "90+6"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "35", "60"]</t>
         </is>
       </c>
       <c r="AJ9">
+        <v>1.44</v>
+      </c>
+      <c r="AK9">
         <v>1.4</v>
       </c>
-      <c r="AK9">
-        <v>1.44</v>
-      </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.94</v>
+        <v>2.15</v>
       </c>
       <c r="R10">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA10">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD10">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q11">
-        <v>2.33</v>
+        <v>3.06</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
+        <v>3.3</v>
+      </c>
+      <c r="AA11">
+        <v>1.91</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
         <v>3.4</v>
       </c>
-      <c r="AA11">
-        <v>1.85</v>
-      </c>
-      <c r="AB11">
-        <v>1.95</v>
-      </c>
-      <c r="AC11">
-        <v>2.92</v>
-      </c>
       <c r="AD11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
         <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK11">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,16 +2268,16 @@
         <v>2.15</v>
       </c>
       <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
         <v>3.1</v>
       </c>
-      <c r="P12">
-        <v>3</v>
-      </c>
       <c r="Q12">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S12">
         <v>1.47</v>
@@ -2310,7 +2310,7 @@
         <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="AD12">
         <v>1.23</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="O14">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="P14">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -2612,7 +2612,7 @@
         <v>2.85</v>
       </c>
       <c r="U14">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
         <v>1.36</v>
@@ -2664,7 +2664,7 @@
         <v>1.34</v>
       </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
         <v>3.4</v>
@@ -4067,34 +4067,34 @@
         <v>2.05</v>
       </c>
       <c r="Q23">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="R23">
         <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
         <v>2.6</v>
       </c>
       <c r="U23">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
         <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA23">
         <v>1.9</v>
@@ -4106,10 +4106,10 @@
         <v>3.4</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
         <v>1.74</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="Q24">
         <v>2.02</v>
@@ -4248,7 +4248,7 @@
         <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4263,16 +4263,16 @@
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AC24">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD24">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
         <v>1.57</v>
@@ -4294,7 +4294,7 @@
         <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4405,37 +4405,37 @@
         <v>3.1</v>
       </c>
       <c r="U25">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V25">
         <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA25">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB25">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AC25">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
         <v>1.73</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -7819,7 +7819,7 @@
         <v>8.4</v>
       </c>
       <c r="R46">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="S46">
         <v>1.19</v>
@@ -7828,43 +7828,43 @@
         <v>4.2</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V46">
         <v>1.7</v>
       </c>
       <c r="W46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
         <v>6</v>
       </c>
       <c r="AA46">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB46">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AC46">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AD46">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE46">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF46">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG46">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AK46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R49">
         <v>2.43</v>
@@ -8338,7 +8338,7 @@
         <v>1.48</v>
       </c>
       <c r="AB49">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AC49">
         <v>2.29</v>
@@ -8353,7 +8353,7 @@
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK49">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8631,13 +8631,13 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="R51">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="S51">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T51">
         <v>4.7</v>
@@ -8649,7 +8649,7 @@
         <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -8676,7 +8676,7 @@
         <v>1.22</v>
       </c>
       <c r="AF51">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AG51">
         <v>1.8</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8797,7 +8797,7 @@
         <v>2.95</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S52">
         <v>1.25</v>
@@ -8818,13 +8818,13 @@
         <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AB52">
         <v>2.38</v>
@@ -8842,7 +8842,7 @@
         <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O58">
         <v>3.8</v>
       </c>
       <c r="P58">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q58">
         <v>5</v>
@@ -9778,22 +9778,22 @@
         <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
         <v>3.12</v>
       </c>
       <c r="U58">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V58">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W58">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.21</v>
@@ -9802,19 +9802,19 @@
         <v>3.9</v>
       </c>
       <c r="AA58">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AB58">
         <v>2.07</v>
       </c>
       <c r="AC58">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AD58">
         <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
         <v>1.77</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
         <v>1.11</v>
@@ -10744,10 +10744,10 @@
         <v>1.58</v>
       </c>
       <c r="O64">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P64">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q64">
         <v>2.05</v>
@@ -10792,7 +10792,7 @@
         <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF64">
         <v>1.57</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AK64">
         <v>2.08</v>
@@ -12561,7 +12561,7 @@
         <v>1.48</v>
       </c>
       <c r="W75">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12570,22 +12570,22 @@
         <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB75">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AC75">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD75">
         <v>1.41</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
         <v>1.5</v>
@@ -12863,31 +12863,31 @@
         <v>1.2</v>
       </c>
       <c r="O77">
-        <v>6.8</v>
+        <v>7.05</v>
       </c>
       <c r="P77">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q77">
         <v>1.55</v>
       </c>
       <c r="R77">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S77">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T77">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="U77">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V77">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="W77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -12902,7 +12902,7 @@
         <v>1.35</v>
       </c>
       <c r="AB77">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AC77">
         <v>1.9</v>
@@ -12914,10 +12914,10 @@
         <v>1.4</v>
       </c>
       <c r="AF77">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q78">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R78">
         <v>2.25</v>
@@ -13041,7 +13041,7 @@
         <v>1.33</v>
       </c>
       <c r="T78">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U78">
         <v>2.6</v>
@@ -13050,7 +13050,7 @@
         <v>1.42</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
         <v>1.05</v>
@@ -13062,10 +13062,10 @@
         <v>3.6</v>
       </c>
       <c r="AA78">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB78">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC78">
         <v>3.1</v>
@@ -13077,10 +13077,10 @@
         <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG78">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="O82">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="Q82">
         <v>2.25</v>
@@ -13690,10 +13690,10 @@
         <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T82">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U82">
         <v>2.56</v>
@@ -13720,7 +13720,7 @@
         <v>1.91</v>
       </c>
       <c r="AC82">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AD82">
         <v>1.33</v>
@@ -14013,7 +14013,7 @@
         <v>1.57</v>
       </c>
       <c r="R84">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="S84">
         <v>1.18</v>
@@ -14025,10 +14025,10 @@
         <v>1.75</v>
       </c>
       <c r="V84">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W84">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14055,10 +14055,10 @@
         <v>1.3</v>
       </c>
       <c r="AF84">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG84">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O88">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="P88">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="Q88">
         <v>1.58</v>
@@ -14668,28 +14668,28 @@
         <v>3.1</v>
       </c>
       <c r="S88">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T88">
         <v>4.33</v>
       </c>
       <c r="U88">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="V88">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W88">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA88">
         <v>1.36</v>
@@ -14707,7 +14707,7 @@
         <v>1.38</v>
       </c>
       <c r="AF88">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG88">
         <v>2.05</v>
@@ -17261,31 +17261,31 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O104">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P104">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="Q104">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="R104">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S104">
         <v>1.22</v>
       </c>
       <c r="T104">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U104">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V104">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W104">
         <v>1.11</v>
@@ -17294,10 +17294,10 @@
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z104">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA104">
         <v>1.6</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK104">
         <v>2.75</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,56 +17433,56 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>3.12</v>
+        <v>1.95</v>
       </c>
       <c r="R105">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="U105">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="V105">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z105">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="AA105">
+        <v>1.69</v>
+      </c>
+      <c r="AB105">
+        <v>2.04</v>
+      </c>
+      <c r="AC105">
+        <v>2.7</v>
+      </c>
+      <c r="AD105">
+        <v>1.36</v>
+      </c>
+      <c r="AE105">
+        <v>1.1</v>
+      </c>
+      <c r="AF105">
+        <v>1.8</v>
+      </c>
+      <c r="AG105">
         <v>1.9</v>
       </c>
-      <c r="AB105">
-        <v>1.9</v>
-      </c>
-      <c r="AC105">
-        <v>3.25</v>
-      </c>
-      <c r="AD105">
-        <v>1.3</v>
-      </c>
-      <c r="AE105">
-        <v>1.07</v>
-      </c>
-      <c r="AF105">
-        <v>1.67</v>
-      </c>
-      <c r="AG105">
-        <v>2.1</v>
-      </c>
       <c r="AH105" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK105">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="R107">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S107">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U107">
-        <v>2.39</v>
+        <v>2.71</v>
       </c>
       <c r="V107">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z107">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
       <c r="AA107">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB107">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AC107">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD107">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,46 +18076,46 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O109">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P109">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q109">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="R109">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T109">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="U109">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V109">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W109">
         <v>1.04</v>
       </c>
       <c r="X109">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y109">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z109">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AA109">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AB109">
         <v>1.44</v>
@@ -18130,10 +18130,10 @@
         <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG109">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
+        <v>2.15</v>
+      </c>
+      <c r="O110">
+        <v>2.8</v>
+      </c>
+      <c r="P110">
+        <v>3.25</v>
+      </c>
+      <c r="Q110">
+        <v>3.04</v>
+      </c>
+      <c r="R110">
+        <v>1.91</v>
+      </c>
+      <c r="S110">
+        <v>1.55</v>
+      </c>
+      <c r="T110">
+        <v>2.39</v>
+      </c>
+      <c r="U110">
+        <v>3.3</v>
+      </c>
+      <c r="V110">
+        <v>1.23</v>
+      </c>
+      <c r="W110">
+        <v>1.04</v>
+      </c>
+      <c r="X110">
+        <v>1.11</v>
+      </c>
+      <c r="Y110">
+        <v>1.44</v>
+      </c>
+      <c r="Z110">
+        <v>2.4</v>
+      </c>
+      <c r="AA110">
         <v>2.5</v>
       </c>
-      <c r="O110">
-        <v>2.87</v>
-      </c>
-      <c r="P110">
-        <v>2.62</v>
-      </c>
-      <c r="Q110">
-        <v>3.4</v>
-      </c>
-      <c r="R110">
-        <v>1.95</v>
-      </c>
-      <c r="S110">
-        <v>1.5</v>
-      </c>
-      <c r="T110">
-        <v>2.31</v>
-      </c>
-      <c r="U110">
-        <v>3.25</v>
-      </c>
-      <c r="V110">
-        <v>1.25</v>
-      </c>
-      <c r="W110">
-        <v>1.03</v>
-      </c>
-      <c r="X110">
-        <v>1.1</v>
-      </c>
-      <c r="Y110">
-        <v>1.4</v>
-      </c>
-      <c r="Z110">
-        <v>2.5</v>
-      </c>
-      <c r="AA110">
-        <v>2.25</v>
-      </c>
       <c r="AB110">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC110">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD110">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE110">
         <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P111">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q111">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
         <v>1.95</v>
@@ -18423,43 +18423,43 @@
         <v>2.31</v>
       </c>
       <c r="U111">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V111">
         <v>1.25</v>
       </c>
       <c r="W111">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X111">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y111">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z111">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA111">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB111">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC111">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD111">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE111">
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG111">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK111">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="O124">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P124">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q124">
-        <v>3.16</v>
+        <v>2.81</v>
       </c>
       <c r="R124">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="S124">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T124">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U124">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="V124">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W124">
         <v>1.05</v>
       </c>
       <c r="X124">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y124">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z124">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AA124">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB124">
+        <v>1.55</v>
+      </c>
+      <c r="AC124">
+        <v>4.2</v>
+      </c>
+      <c r="AD124">
+        <v>1.15</v>
+      </c>
+      <c r="AE124">
+        <v>1.06</v>
+      </c>
+      <c r="AF124">
+        <v>1.95</v>
+      </c>
+      <c r="AG124">
         <v>1.71</v>
-      </c>
-      <c r="AC124">
-        <v>3.48</v>
-      </c>
-      <c r="AD124">
-        <v>1.22</v>
-      </c>
-      <c r="AE124">
-        <v>1.07</v>
-      </c>
-      <c r="AF124">
-        <v>1.75</v>
-      </c>
-      <c r="AG124">
-        <v>1.93</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20594,7 +20594,7 @@
         <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="O125">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P125">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q125">
-        <v>2.81</v>
+        <v>3.16</v>
       </c>
       <c r="R125">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="S125">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T125">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U125">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="V125">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W125">
         <v>1.05</v>
       </c>
       <c r="X125">
+        <v>1.03</v>
+      </c>
+      <c r="Y125">
+        <v>1.28</v>
+      </c>
+      <c r="Z125">
+        <v>3.05</v>
+      </c>
+      <c r="AA125">
+        <v>2</v>
+      </c>
+      <c r="AB125">
+        <v>1.71</v>
+      </c>
+      <c r="AC125">
+        <v>3.48</v>
+      </c>
+      <c r="AD125">
+        <v>1.22</v>
+      </c>
+      <c r="AE125">
         <v>1.07</v>
       </c>
-      <c r="Y125">
-        <v>1.38</v>
-      </c>
-      <c r="Z125">
-        <v>2.62</v>
-      </c>
-      <c r="AA125">
-        <v>2.3</v>
-      </c>
-      <c r="AB125">
-        <v>1.55</v>
-      </c>
-      <c r="AC125">
-        <v>4.2</v>
-      </c>
-      <c r="AD125">
-        <v>1.15</v>
-      </c>
-      <c r="AE125">
-        <v>1.06</v>
-      </c>
       <c r="AF125">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG125">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.28</v>
       </c>
       <c r="AK125">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q130">
-        <v>2.77</v>
+        <v>3.44</v>
       </c>
       <c r="R130">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S130">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T130">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U130">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="V130">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y130">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z130">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA130">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB130">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC130">
-        <v>3.85</v>
+        <v>3.42</v>
       </c>
       <c r="AD130">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF130">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG130">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK130">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>3.44</v>
+        <v>2.77</v>
       </c>
       <c r="R131">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S131">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U131">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="V131">
+        <v>1.29</v>
+      </c>
+      <c r="W131">
+        <v>0</v>
+      </c>
+      <c r="X131">
+        <v>0</v>
+      </c>
+      <c r="Y131">
         <v>1.32</v>
       </c>
-      <c r="W131">
-        <v>1.07</v>
-      </c>
-      <c r="X131">
-        <v>1.04</v>
-      </c>
-      <c r="Y131">
-        <v>1.3</v>
-      </c>
       <c r="Z131">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA131">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB131">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC131">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AD131">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE131">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF131">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG131">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK131">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21828,7 +21828,7 @@
         <v>2.45</v>
       </c>
       <c r="O132">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P132">
         <v>2.45</v>
@@ -21840,22 +21840,22 @@
         <v>2.2</v>
       </c>
       <c r="S132">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T132">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U132">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V132">
         <v>1.43</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X132">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y132">
         <v>1.18</v>
@@ -21864,10 +21864,10 @@
         <v>3.6</v>
       </c>
       <c r="AA132">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB132">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC132">
         <v>2.75</v>
@@ -21876,7 +21876,7 @@
         <v>1.32</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF132">
         <v>1.53</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="O134">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="Q134">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="R134">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S134">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T134">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="U134">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="V134">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="W134">
+        <v>1.04</v>
+      </c>
+      <c r="X134">
         <v>1.01</v>
       </c>
-      <c r="X134">
-        <v>1.05</v>
-      </c>
       <c r="Y134">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>2.76</v>
+        <v>3.42</v>
       </c>
       <c r="AA134">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AB134">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC134">
-        <v>4.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD134">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE134">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF134">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AG134">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK134">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="O135">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P135">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="Q135">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="R135">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S135">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T135">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="U135">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="V135">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="W135">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="Z135">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="AA135">
+        <v>2.38</v>
+      </c>
+      <c r="AB135">
+        <v>1.57</v>
+      </c>
+      <c r="AC135">
+        <v>4.6</v>
+      </c>
+      <c r="AD135">
+        <v>1.19</v>
+      </c>
+      <c r="AE135">
+        <v>1.02</v>
+      </c>
+      <c r="AF135">
         <v>2.02</v>
       </c>
-      <c r="AB135">
-        <v>1.78</v>
-      </c>
-      <c r="AC135">
-        <v>3.28</v>
-      </c>
-      <c r="AD135">
-        <v>1.25</v>
-      </c>
-      <c r="AE135">
-        <v>1.11</v>
-      </c>
-      <c r="AF135">
-        <v>1.88</v>
-      </c>
       <c r="AG135">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK135">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22480,16 +22480,16 @@
         <v>2.5</v>
       </c>
       <c r="O136">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P136">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q136">
         <v>3.2</v>
       </c>
       <c r="R136">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="S136">
         <v>1.33</v>
@@ -22501,22 +22501,22 @@
         <v>2.55</v>
       </c>
       <c r="V136">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
         <v>1.1</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z136">
         <v>3.58</v>
       </c>
       <c r="AA136">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AB136">
         <v>1.96</v>
@@ -22525,16 +22525,16 @@
         <v>2.7</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
         <v>1.11</v>
       </c>
       <c r="AF136">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG136">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="O138">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P138">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="Q138">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R138">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S138">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T138">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U138">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V138">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W138">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X138">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y138">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z138">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA138">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB138">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC138">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD138">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF138">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG138">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AK138">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="O139">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="P139">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA139">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB139">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,19 +23129,19 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O140">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P140">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="Q140">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="R140">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="S140">
         <v>1.46</v>
@@ -23150,43 +23150,43 @@
         <v>2.42</v>
       </c>
       <c r="U140">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="V140">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W140">
         <v>1.06</v>
       </c>
       <c r="X140">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y140">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z140">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AA140">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB140">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AC140">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="AD140">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE140">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF140">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG140">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK140">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,31 +23292,31 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="O141">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="P141">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="Q141">
-        <v>3.24</v>
+        <v>2.03</v>
       </c>
       <c r="R141">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S141">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T141">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U141">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="V141">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W141">
         <v>1.06</v>
@@ -23325,16 +23325,16 @@
         <v>1.07</v>
       </c>
       <c r="Y141">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z141">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AA141">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB141">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC141">
         <v>3.82</v>
@@ -23346,10 +23346,10 @@
         <v>1.06</v>
       </c>
       <c r="AF141">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AG141">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AK141">
-        <v>1.41</v>
+        <v>2.43</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.49</v>
+        <v>2.62</v>
       </c>
       <c r="O142">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="P142">
-        <v>7</v>
+        <v>2.45</v>
       </c>
       <c r="Q142">
-        <v>2.03</v>
+        <v>3.54</v>
       </c>
       <c r="R142">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S142">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T142">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="U142">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="V142">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W142">
         <v>1.06</v>
       </c>
       <c r="X142">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y142">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AA142">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB142">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC142">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD142">
         <v>1.18</v>
       </c>
       <c r="AE142">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF142">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="AG142">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AK142">
-        <v>2.43</v>
+        <v>1.35</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23627,25 +23627,25 @@
         <v>0</v>
       </c>
       <c r="Q143">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R143">
         <v>3.25</v>
       </c>
       <c r="S143">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T143">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="U143">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V143">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="W143">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X143">
         <v>1.01</v>
@@ -23654,7 +23654,7 @@
         <v>1.07</v>
       </c>
       <c r="Z143">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA143">
         <v>1.26</v>
@@ -23691,7 +23691,7 @@
         <v>1.06</v>
       </c>
       <c r="AK143">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24759,16 +24759,16 @@
         </is>
       </c>
       <c r="N150">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O150">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P150">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q150">
-        <v>4.61</v>
+        <v>4.33</v>
       </c>
       <c r="R150">
         <v>2.31</v>
@@ -24792,7 +24792,7 @@
         <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z150">
         <v>5</v>
@@ -24807,10 +24807,10 @@
         <v>2.45</v>
       </c>
       <c r="AD150">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE150">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF150">
         <v>1.53</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
+        <v>3.32</v>
+      </c>
+      <c r="O163">
+        <v>3.4</v>
+      </c>
+      <c r="P163">
         <v>2</v>
       </c>
-      <c r="O163">
-        <v>3.9</v>
-      </c>
-      <c r="P163">
-        <v>2.8</v>
-      </c>
       <c r="Q163">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="R163">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="S163">
+        <v>1.25</v>
+      </c>
+      <c r="T163">
+        <v>3.22</v>
+      </c>
+      <c r="U163">
+        <v>2.23</v>
+      </c>
+      <c r="V163">
+        <v>1.6</v>
+      </c>
+      <c r="W163">
+        <v>1.11</v>
+      </c>
+      <c r="X163">
+        <v>1.03</v>
+      </c>
+      <c r="Y163">
+        <v>1.2</v>
+      </c>
+      <c r="Z163">
+        <v>4.5</v>
+      </c>
+      <c r="AA163">
+        <v>1.63</v>
+      </c>
+      <c r="AB163">
+        <v>2.25</v>
+      </c>
+      <c r="AC163">
+        <v>2.42</v>
+      </c>
+      <c r="AD163">
+        <v>1.5</v>
+      </c>
+      <c r="AE163">
         <v>1.17</v>
       </c>
-      <c r="T163">
-        <v>4.05</v>
-      </c>
-      <c r="U163">
-        <v>1.96</v>
-      </c>
-      <c r="V163">
-        <v>1.76</v>
-      </c>
-      <c r="W163">
-        <v>1.18</v>
-      </c>
-      <c r="X163">
-        <v>1.01</v>
-      </c>
-      <c r="Y163">
-        <v>1.07</v>
-      </c>
-      <c r="Z163">
-        <v>6.5</v>
-      </c>
-      <c r="AA163">
-        <v>1.34</v>
-      </c>
-      <c r="AB163">
-        <v>2.95</v>
-      </c>
-      <c r="AC163">
-        <v>1.89</v>
-      </c>
-      <c r="AD163">
-        <v>1.78</v>
-      </c>
-      <c r="AE163">
-        <v>1.32</v>
-      </c>
       <c r="AF163">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG163">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK163">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,80 +27041,80 @@
         </is>
       </c>
       <c r="N164">
-        <v>3.32</v>
+        <v>2</v>
       </c>
       <c r="O164">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P164">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="Q164">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="R164">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="S164">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T164">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="U164">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="V164">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="W164">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X164">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y164">
+        <v>1.07</v>
+      </c>
+      <c r="Z164">
+        <v>6.5</v>
+      </c>
+      <c r="AA164">
+        <v>1.34</v>
+      </c>
+      <c r="AB164">
+        <v>2.95</v>
+      </c>
+      <c r="AC164">
+        <v>1.89</v>
+      </c>
+      <c r="AD164">
+        <v>1.78</v>
+      </c>
+      <c r="AE164">
+        <v>1.32</v>
+      </c>
+      <c r="AF164">
+        <v>1.36</v>
+      </c>
+      <c r="AG164">
+        <v>2.88</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ164">
         <v>1.2</v>
       </c>
-      <c r="Z164">
-        <v>4.5</v>
-      </c>
-      <c r="AA164">
-        <v>1.63</v>
-      </c>
-      <c r="AB164">
-        <v>2.25</v>
-      </c>
-      <c r="AC164">
-        <v>2.42</v>
-      </c>
-      <c r="AD164">
-        <v>1.5</v>
-      </c>
-      <c r="AE164">
-        <v>1.17</v>
-      </c>
-      <c r="AF164">
-        <v>1.5</v>
-      </c>
-      <c r="AG164">
-        <v>2.35</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ164">
-        <v>1.57</v>
-      </c>
       <c r="AK164">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27536,28 +27536,28 @@
         <v>4.8</v>
       </c>
       <c r="P167">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="Q167">
         <v>1.73</v>
       </c>
       <c r="R167">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S167">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T167">
         <v>3.85</v>
       </c>
       <c r="U167">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V167">
         <v>1.75</v>
       </c>
       <c r="W167">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X167">
         <v>1.02</v>
@@ -29818,7 +29818,7 @@
         <v>4</v>
       </c>
       <c r="P181">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q181">
         <v>3.35</v>
@@ -29845,25 +29845,25 @@
         <v>1.03</v>
       </c>
       <c r="Y181">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z181">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA181">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB181">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC181">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD181">
         <v>1.57</v>
       </c>
       <c r="AE181">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF181">
         <v>1.48</v>
@@ -29975,10 +29975,10 @@
         </is>
       </c>
       <c r="N182">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="O182">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P182">
         <v>1.67</v>
@@ -30138,34 +30138,34 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O183">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P183">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q183">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R183">
         <v>2.32</v>
       </c>
       <c r="S183">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T183">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U183">
         <v>2.25</v>
       </c>
       <c r="V183">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W183">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X183">
         <v>1.03</v>
@@ -30177,16 +30177,16 @@
         <v>4.5</v>
       </c>
       <c r="AA183">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB183">
         <v>2.35</v>
       </c>
       <c r="AC183">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AD183">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE183">
         <v>1.22</v>
@@ -30211,7 +30211,7 @@
         <v>1.22</v>
       </c>
       <c r="AK183">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -34050,10 +34050,10 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O207">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P207">
         <v>3.7</v>
@@ -34071,19 +34071,19 @@
         <v>2.9</v>
       </c>
       <c r="U207">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V207">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W207">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z207">
         <v>3.05</v>
@@ -34101,7 +34101,7 @@
         <v>1.25</v>
       </c>
       <c r="AE207">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF207">
         <v>1.82</v>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK207">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -35843,37 +35843,37 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O218">
         <v>3.2</v>
       </c>
       <c r="P218">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q218">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R218">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S218">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T218">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="U218">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="V218">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W218">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y218">
         <v>1.29</v>
@@ -35891,16 +35891,16 @@
         <v>2.9</v>
       </c>
       <c r="AD218">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE218">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF218">
         <v>1.63</v>
       </c>
       <c r="AG218">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK218">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O219">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P219">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q219">
         <v>2.17</v>
@@ -36021,10 +36021,10 @@
         <v>2.25</v>
       </c>
       <c r="S219">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T219">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U219">
         <v>2.55</v>
@@ -36036,16 +36036,16 @@
         <v>1.08</v>
       </c>
       <c r="X219">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y219">
         <v>1.23</v>
       </c>
       <c r="Z219">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA219">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB219">
         <v>1.75</v>
@@ -36057,13 +36057,13 @@
         <v>1.26</v>
       </c>
       <c r="AE219">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF219">
         <v>1.74</v>
       </c>
       <c r="AG219">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.05</v>
+        <v>9.5</v>
       </c>
       <c r="O239">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="P239">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="Q239">
-        <v>2.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R239">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="S239">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="T239">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U239">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V239">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W239">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X239">
         <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z239">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA239">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB239">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC239">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AD239">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AE239">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF239">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG239">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AK239">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>10</v>
+        <v>2.05</v>
       </c>
       <c r="O240">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="P240">
-        <v>1.24</v>
+        <v>2.9</v>
       </c>
       <c r="Q240">
-        <v>8.300000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="R240">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="S240">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T240">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U240">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V240">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="W240">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X240">
         <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z240">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AA240">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AB240">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AC240">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD240">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE240">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF240">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AG240">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AK240">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -43851,22 +43851,22 @@
         <v>3.3</v>
       </c>
       <c r="U267">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V267">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W267">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X267">
         <v>1.04</v>
       </c>
       <c r="Y267">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z267">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA267">
         <v>1.58</v>
@@ -43881,7 +43881,7 @@
         <v>1.46</v>
       </c>
       <c r="AE267">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF267">
         <v>1.5</v>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK267">
         <v>1.53</v>
@@ -44497,7 +44497,7 @@
         <v>2.24</v>
       </c>
       <c r="S271">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T271">
         <v>3.25</v>
@@ -44512,7 +44512,7 @@
         <v>1.11</v>
       </c>
       <c r="X271">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y271">
         <v>1.2</v>
@@ -44527,10 +44527,10 @@
         <v>2.15</v>
       </c>
       <c r="AC271">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD271">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE271">
         <v>1.13</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O272">
         <v>3.55</v>
       </c>
       <c r="P272">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q272">
         <v>4.1</v>
@@ -44681,7 +44681,7 @@
         <v>1.18</v>
       </c>
       <c r="Z272">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="AA272">
         <v>1.56</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O278">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P278">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q278">
         <v>2.25</v>
@@ -45653,7 +45653,7 @@
         <v>1.06</v>
       </c>
       <c r="X278">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y278">
         <v>1.3</v>
@@ -45662,25 +45662,25 @@
         <v>3</v>
       </c>
       <c r="AA278">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AB278">
         <v>1.68</v>
       </c>
       <c r="AC278">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD278">
         <v>1.22</v>
       </c>
       <c r="AE278">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF278">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG278">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>3.95</v>
       </c>
       <c r="AA281">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB281">
         <v>2.05</v>
@@ -48756,7 +48756,7 @@
         <v>1.29</v>
       </c>
       <c r="Z297">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA297">
         <v>1.93</v>
@@ -48774,7 +48774,7 @@
         <v>1.11</v>
       </c>
       <c r="AF297">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG297">
         <v>1.87</v>
@@ -48913,7 +48913,7 @@
         <v>1.07</v>
       </c>
       <c r="X298">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y298">
         <v>1.27</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O299">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="P299">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q299">
         <v>1.5</v>
@@ -49061,19 +49061,19 @@
         <v>3.1</v>
       </c>
       <c r="S299">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T299">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U299">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V299">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="W299">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X299">
         <v>1.01</v>
@@ -49085,13 +49085,13 @@
         <v>8</v>
       </c>
       <c r="AA299">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB299">
         <v>3.3</v>
       </c>
       <c r="AC299">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD299">
         <v>1.94</v>
@@ -49116,7 +49116,7 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK299">
         <v>3.05</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,61 +49209,61 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O300">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P300">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q300">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="R300">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S300">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="T300">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="U300">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V300">
         <v>1.22</v>
       </c>
       <c r="W300">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X300">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y300">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z300">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AA300">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AB300">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC300">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AD300">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE300">
         <v>1.03</v>
       </c>
       <c r="AF300">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG300">
         <v>1.53</v>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK300">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
+        <v>1.7</v>
+      </c>
+      <c r="O301">
+        <v>3.3</v>
+      </c>
+      <c r="P301">
+        <v>5.05</v>
+      </c>
+      <c r="Q301">
+        <v>2.45</v>
+      </c>
+      <c r="R301">
         <v>2.1</v>
       </c>
-      <c r="O301">
-        <v>2.9</v>
-      </c>
-      <c r="P301">
-        <v>3.6</v>
-      </c>
-      <c r="Q301">
-        <v>2.66</v>
-      </c>
-      <c r="R301">
-        <v>1.9</v>
-      </c>
       <c r="S301">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="T301">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="U301">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="V301">
+        <v>1.31</v>
+      </c>
+      <c r="W301">
+        <v>1.03</v>
+      </c>
+      <c r="X301">
+        <v>1.06</v>
+      </c>
+      <c r="Y301">
+        <v>1.37</v>
+      </c>
+      <c r="Z301">
+        <v>2.63</v>
+      </c>
+      <c r="AA301">
+        <v>2.12</v>
+      </c>
+      <c r="AB301">
+        <v>1.58</v>
+      </c>
+      <c r="AC301">
+        <v>4.2</v>
+      </c>
+      <c r="AD301">
         <v>1.22</v>
       </c>
-      <c r="W301">
-        <v>1.04</v>
-      </c>
-      <c r="X301">
-        <v>1.1</v>
-      </c>
-      <c r="Y301">
-        <v>1.57</v>
-      </c>
-      <c r="Z301">
-        <v>2.38</v>
-      </c>
-      <c r="AA301">
-        <v>2.75</v>
-      </c>
-      <c r="AB301">
-        <v>1.36</v>
-      </c>
-      <c r="AC301">
-        <v>6</v>
-      </c>
-      <c r="AD301">
-        <v>1.13</v>
-      </c>
       <c r="AE301">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF301">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG301">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK301">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O302">
+        <v>2.8</v>
+      </c>
+      <c r="P302">
         <v>3.3</v>
       </c>
-      <c r="P302">
-        <v>5.05</v>
-      </c>
       <c r="Q302">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R302">
+        <v>1.85</v>
+      </c>
+      <c r="S302">
+        <v>1.65</v>
+      </c>
+      <c r="T302">
         <v>2.1</v>
       </c>
-      <c r="S302">
-        <v>1.43</v>
-      </c>
-      <c r="T302">
-        <v>2.45</v>
-      </c>
       <c r="U302">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="V302">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W302">
         <v>1.03</v>
       </c>
       <c r="X302">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Y302">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="Z302">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AA302">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="AB302">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AC302">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD302">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE302">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF302">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AG302">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK302">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,80 +50187,80 @@
         </is>
       </c>
       <c r="N306">
+        <v>3.3</v>
+      </c>
+      <c r="O306">
+        <v>2.95</v>
+      </c>
+      <c r="P306">
+        <v>2.05</v>
+      </c>
+      <c r="Q306">
+        <v>4.2</v>
+      </c>
+      <c r="R306">
         <v>1.95</v>
-      </c>
-      <c r="O306">
-        <v>3.1</v>
-      </c>
-      <c r="P306">
-        <v>3.48</v>
-      </c>
-      <c r="Q306">
-        <v>2.4</v>
-      </c>
-      <c r="R306">
-        <v>2</v>
       </c>
       <c r="S306">
         <v>1.44</v>
       </c>
       <c r="T306">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U306">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V306">
         <v>1.29</v>
       </c>
       <c r="W306">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X306">
         <v>1.08</v>
       </c>
       <c r="Y306">
+        <v>1.44</v>
+      </c>
+      <c r="Z306">
+        <v>2.5</v>
+      </c>
+      <c r="AA306">
+        <v>2.4</v>
+      </c>
+      <c r="AB306">
+        <v>1.44</v>
+      </c>
+      <c r="AC306">
+        <v>4.5</v>
+      </c>
+      <c r="AD306">
+        <v>1.17</v>
+      </c>
+      <c r="AE306">
+        <v>1.04</v>
+      </c>
+      <c r="AF306">
+        <v>1.95</v>
+      </c>
+      <c r="AG306">
+        <v>1.73</v>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ306">
         <v>1.36</v>
       </c>
-      <c r="Z306">
-        <v>2.75</v>
-      </c>
-      <c r="AA306">
-        <v>2.15</v>
-      </c>
-      <c r="AB306">
-        <v>1.6</v>
-      </c>
-      <c r="AC306">
-        <v>4</v>
-      </c>
-      <c r="AD306">
-        <v>1.2</v>
-      </c>
-      <c r="AE306">
-        <v>1.02</v>
-      </c>
-      <c r="AF306">
-        <v>1.93</v>
-      </c>
-      <c r="AG306">
-        <v>1.75</v>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ306">
-        <v>1.3</v>
-      </c>
       <c r="AK306">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O307">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P307">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="Q307">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R307">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S307">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T307">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U307">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="V307">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W307">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X307">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y307">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z307">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AA307">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AB307">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AC307">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD307">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE307">
         <v>1.02</v>
       </c>
       <c r="AF307">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AG307">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK307">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O308">
         <v>2.95</v>
       </c>
       <c r="P308">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="Q308">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R308">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S308">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T308">
         <v>2.31</v>
       </c>
       <c r="U308">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="V308">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W308">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X308">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y308">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z308">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AA308">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AB308">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AC308">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD308">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE308">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF308">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AG308">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK308">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -51343,10 +51343,10 @@
         <v>2.32</v>
       </c>
       <c r="S313">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T313">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U313">
         <v>2.8</v>
@@ -51358,7 +51358,7 @@
         <v>1.07</v>
       </c>
       <c r="X313">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y313">
         <v>1.3</v>
@@ -51494,10 +51494,10 @@
         <v>1.4</v>
       </c>
       <c r="O314">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P314">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="Q314">
         <v>1.8</v>
@@ -51509,7 +51509,7 @@
         <v>1.3</v>
       </c>
       <c r="T314">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U314">
         <v>2.3</v>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O318">
         <v>2.55</v>
       </c>
       <c r="P318">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q318">
         <v>2.8</v>
@@ -52188,10 +52188,10 @@
         <v>1.58</v>
       </c>
       <c r="AC318">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD318">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE318">
         <v>1.01</v>
@@ -52306,49 +52306,49 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O319">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P319">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="Q319">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="R319">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="S319">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T319">
         <v>3.75</v>
       </c>
       <c r="U319">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="V319">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W319">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X319">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y319">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z319">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA319">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AB319">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AC319">
         <v>2.35</v>
@@ -52357,13 +52357,13 @@
         <v>1.48</v>
       </c>
       <c r="AE319">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF319">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG319">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK319">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -53450,7 +53450,7 @@
         <v>2.45</v>
       </c>
       <c r="O326">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P326">
         <v>2.5</v>
@@ -53474,7 +53474,7 @@
         <v>1.4</v>
       </c>
       <c r="W326">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X326">
         <v>1.05</v>
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O330">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P330">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Q330">
         <v>5</v>
       </c>
       <c r="R330">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S330">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T330">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="U330">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V330">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W330">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X330">
         <v>1.01</v>
       </c>
       <c r="Y330">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z330">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA330">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB330">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC330">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AD330">
         <v>1.73</v>
       </c>
       <c r="AE330">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AF330">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG330">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AK330">
         <v>1.08</v>

--- a/jogos_2026-09-13.xlsx
+++ b/jogos_2026-09-13.xlsx
@@ -41691,7 +41691,7 @@
         <v>0</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I254">
         <v>0</v>
@@ -41703,21 +41703,21 @@
         <v>0</v>
       </c>
       <c r="L254">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC254">
         <v>0</v>
@@ -41777,7 +41777,7 @@
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81", "90+4", "90+6"]</t>
         </is>
       </c>
       <c r="AJ254">
@@ -41790,28 +41790,28 @@
         <v>0</v>
       </c>
       <c r="AM254">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN254">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO254">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP254">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ254">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR254">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS254">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT254">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N257">
@@ -42279,28 +42279,28 @@
         <v>0</v>
       </c>
       <c r="AM257">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN257">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO257">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP257">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ257">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR257">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS257">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT257">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
@@ -43807,16 +43807,16 @@
         </is>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -43826,7 +43826,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N267">
@@ -43891,12 +43891,12 @@
       </c>
       <c r="AH267" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AJ267">
@@ -43909,28 +43909,28 @@
         <v>0</v>
       </c>
       <c r="AM267">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN267">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO267">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP267">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ267">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR267">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS267">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT267">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
@@ -43970,26 +43970,26 @@
         </is>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I268">
         <v>0</v>
       </c>
       <c r="J268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N268">
@@ -44054,12 +44054,12 @@
       </c>
       <c r="AH268" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "90"]</t>
         </is>
       </c>
       <c r="AJ268">
@@ -44072,28 +44072,28 @@
         <v>0</v>
       </c>
       <c r="AM268">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN268">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO268">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP268">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ268">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR268">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS268">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT268">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
@@ -44296,26 +44296,26 @@
         </is>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270">
         <v>0</v>
       </c>
       <c r="L270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N270">
@@ -44380,12 +44380,12 @@
       </c>
       <c r="AH270" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "37"]</t>
         </is>
       </c>
       <c r="AI270" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "90+3"]</t>
         </is>
       </c>
       <c r="AJ270">
@@ -44398,28 +44398,28 @@
         <v>0</v>
       </c>
       <c r="AM270">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN270">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO270">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP270">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ270">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR270">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS270">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT270">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
@@ -44459,26 +44459,26 @@
         </is>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L271">
         <v>0</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N271">
@@ -44543,12 +44543,12 @@
       </c>
       <c r="AH271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "69"]</t>
         </is>
       </c>
       <c r="AI271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "24"]</t>
         </is>
       </c>
       <c r="AJ271">
@@ -44561,28 +44561,28 @@
         <v>0</v>
       </c>
       <c r="AM271">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN271">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO271">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP271">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ271">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR271">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS271">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT271">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
@@ -44622,26 +44622,26 @@
         </is>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K272">
         <v>0</v>
       </c>
       <c r="L272">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N272">
@@ -44706,12 +44706,12 @@
       </c>
       <c r="AH272" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AI272" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "29", "74", "90+3"]</t>
         </is>
       </c>
       <c r="AJ272">
@@ -44724,16 +44724,16 @@
         <v>0</v>
       </c>
       <c r="AM272">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN272">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO272">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP272">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ272">
         <v>0</v>
@@ -44785,10 +44785,10 @@
         </is>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I273">
         <v>0</v>
@@ -44797,14 +44797,14 @@
         <v>0</v>
       </c>
       <c r="K273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N273">
@@ -44869,12 +44869,12 @@
       </c>
       <c r="AH273" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AI273" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "63", "67", "78"]</t>
         </is>
       </c>
       <c r="AJ273">
@@ -44887,28 +44887,28 @@
         <v>0</v>
       </c>
       <c r="AM273">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN273">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO273">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP273">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ273">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR273">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS273">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT273">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>0</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I274">
         <v>0</v>
@@ -44963,11 +44963,11 @@
         <v>0</v>
       </c>
       <c r="L274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N274">
@@ -45037,7 +45037,7 @@
       </c>
       <c r="AI274" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "57"]</t>
         </is>
       </c>
       <c r="AJ274">
@@ -45050,28 +45050,28 @@
         <v>0</v>
       </c>
       <c r="AM274">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN274">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO274">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP274">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ274">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR274">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS274">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT274">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
@@ -45437,26 +45437,26 @@
         </is>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H277">
         <v>0</v>
       </c>
       <c r="I277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277">
         <v>0</v>
       </c>
       <c r="K277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L277">
         <v>0</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N277">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="AH277" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "90+5", "90+5"]</t>
         </is>
       </c>
       <c r="AI277" t="inlineStr">
@@ -45539,28 +45539,28 @@
         <v>0</v>
       </c>
       <c r="AM277">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN277">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO277">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP277">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ277">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR277">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS277">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT277">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         </is>
       </c>
       <c r="G278">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -45612,14 +45612,14 @@
         <v>0</v>
       </c>
       <c r="K278">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L278">
         <v>0</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N278">
@@ -45684,7 +45684,7 @@
       </c>
       <c r="AH278" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "89"]</t>
         </is>
       </c>
       <c r="AI278" t="inlineStr">
@@ -45702,28 +45702,28 @@
         <v>0</v>
       </c>
       <c r="AM278">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN278">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO278">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP278">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ278">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR278">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS278">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT278">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N279">
@@ -45865,28 +45865,28 @@
         <v>0</v>
       </c>
       <c r="AM279">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN279">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO279">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP279">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ279">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR279">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS279">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT279">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>0</v>
       </c>
       <c r="H280">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I280">
         <v>0</v>
@@ -45941,11 +45941,11 @@
         <v>0</v>
       </c>
       <c r="L280">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N280">
@@ -46015,7 +46015,7 @@
       </c>
       <c r="AI280" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "55", "90+4"]</t>
         </is>
       </c>
       <c r="AJ280">
@@ -46028,28 +46028,28 @@
         <v>0</v>
       </c>
       <c r="AM280">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN280">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO280">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP280">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ280">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR280">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS280">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT280">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
@@ -46089,10 +46089,10 @@
         </is>
       </c>
       <c r="G281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281">
         <v>0</v>
@@ -46101,14 +46101,14 @@
         <v>0</v>
       </c>
       <c r="K281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N281">
@@ -46173,12 +46173,12 @@
       </c>
       <c r="AH281" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI281" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ281">
@@ -46191,28 +46191,28 @@
         <v>0</v>
       </c>
       <c r="AM281">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN281">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO281">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP281">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ281">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AR281">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="AS281">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT281">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N282">
@@ -46354,28 +46354,28 @@
         <v>0</v>
       </c>
       <c r="AM282">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN282">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO282">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP282">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ282">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR282">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS282">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT282">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
@@ -46415,13 +46415,13 @@
         </is>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H283">
         <v>0</v>
       </c>
       <c r="I283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J283">
         <v>0</v>
@@ -46434,7 +46434,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N283">
@@ -46499,7 +46499,7 @@
       </c>
       <c r="AH283" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "42"]</t>
         </is>
       </c>
       <c r="AI283" t="inlineStr">
@@ -46517,28 +46517,28 @@
         <v>0</v>
       </c>
       <c r="AM283">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN283">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO283">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP283">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ283">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR283">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS283">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT283">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
@@ -46581,13 +46581,13 @@
         <v>0</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I284">
         <v>0</v>
       </c>
       <c r="J284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K284">
         <v>0</v>
@@ -46597,23 +46597,23 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N284">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O284">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P284">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q284">
         <v>2.4</v>
       </c>
       <c r="R284">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S284">
         <v>1.42</v>
@@ -46622,7 +46622,7 @@
         <v>2.65</v>
       </c>
       <c r="U284">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V284">
         <v>1.3</v>
@@ -46631,13 +46631,13 @@
         <v>1.05</v>
       </c>
       <c r="X284">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y284">
         <v>1.38</v>
       </c>
       <c r="Z284">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AA284">
         <v>2.23</v>
@@ -46646,7 +46646,7 @@
         <v>1.57</v>
       </c>
       <c r="AC284">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD284">
         <v>1.17</v>
@@ -46658,7 +46658,7 @@
         <v>1.95</v>
       </c>
       <c r="AG284">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
       </c>
       <c r="AI284" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AJ284">
@@ -46680,28 +46680,28 @@
         <v>0</v>
       </c>
       <c r="AM284">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN284">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO284">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP284">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ284">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR284">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS284">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT284">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
@@ -46741,13 +46741,13 @@
         </is>
       </c>
       <c r="G285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H285">
         <v>0</v>
       </c>
       <c r="I285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -46760,7 +46760,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N285">
@@ -46825,7 +46825,7 @@
       </c>
       <c r="AH285" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AI285" t="inlineStr">
@@ -46843,28 +46843,28 @@
         <v>0</v>
       </c>
       <c r="AM285">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN285">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO285">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP285">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ285">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR285">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS285">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT285">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
@@ -46904,26 +46904,26 @@
         </is>
       </c>
       <c r="G286">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J286">
         <v>0</v>
       </c>
       <c r="K286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N286">
@@ -46988,12 +46988,12 @@
       </c>
       <c r="AH286" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "90"]</t>
         </is>
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AJ286">
@@ -47233,23 +47233,23 @@
         <v>0</v>
       </c>
       <c r="H288">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I288">
         <v>0</v>
       </c>
       <c r="J288">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K288">
         <v>0</v>
       </c>
       <c r="L288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N288">
@@ -47319,7 +47319,7 @@
       </c>
       <c r="AI288" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "34", "69"]</t>
         </is>
       </c>
       <c r="AJ288">
@@ -47332,28 +47332,28 @@
         <v>0</v>
       </c>
       <c r="AM288">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN288">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO288">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP288">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ288">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR288">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS288">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT288">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N289">
@@ -47495,28 +47495,28 @@
         <v>0</v>
       </c>
       <c r="AM289">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN289">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO289">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP289">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ289">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR289">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS289">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT289">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N290">
@@ -47658,28 +47658,28 @@
         <v>0</v>
       </c>
       <c r="AM290">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN290">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO290">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP290">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ290">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR290">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS290">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT290">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         </is>
       </c>
       <c r="G291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -47731,14 +47731,14 @@
         <v>0</v>
       </c>
       <c r="K291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L291">
         <v>0</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N291">
@@ -47803,7 +47803,7 @@
       </c>
       <c r="AH291" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AI291" t="inlineStr">
@@ -47821,28 +47821,28 @@
         <v>0</v>
       </c>
       <c r="AM291">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN291">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO291">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP291">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ291">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR291">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS291">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT291">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
@@ -47882,26 +47882,26 @@
         </is>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H292">
         <v>0</v>
       </c>
       <c r="I292">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J292">
         <v>0</v>
       </c>
       <c r="K292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L292">
         <v>0</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N292">
@@ -47966,7 +47966,7 @@
       </c>
       <c r="AH292" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "39", "90+2"]</t>
         </is>
       </c>
       <c r="AI292" t="inlineStr">
@@ -47984,16 +47984,16 @@
         <v>0</v>
       </c>
       <c r="AM292">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN292">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO292">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP292">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ292">
         <v>0</v>
@@ -48045,7 +48045,7 @@
         </is>
       </c>
       <c r="G293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293">
         <v>0</v>
@@ -48057,14 +48057,14 @@
         <v>0</v>
       </c>
       <c r="K293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L293">
         <v>0</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N293">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="AH293" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AI293" t="inlineStr">
@@ -48147,28 +48147,28 @@
         <v>0</v>
       </c>
       <c r="AM293">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN293">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO293">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP293">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ293">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AR293">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS293">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT293">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
@@ -48211,13 +48211,13 @@
         <v>0</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294">
         <v>0</v>
       </c>
       <c r="J294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K294">
         <v>0</v>
@@ -48227,7 +48227,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N294">
@@ -48297,7 +48297,7 @@
       </c>
       <c r="AI294" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AJ294">
@@ -48310,28 +48310,28 @@
         <v>0</v>
       </c>
       <c r="AM294">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN294">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO294">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP294">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ294">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR294">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS294">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT294">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
@@ -48371,10 +48371,10 @@
         </is>
       </c>
       <c r="G295">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I295">
         <v>0</v>
@@ -48383,14 +48383,14 @@
         <v>0</v>
       </c>
       <c r="K295">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L295">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N295">
@@ -48455,12 +48455,12 @@
       </c>
       <c r="AH295" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "89", "90+4"]</t>
         </is>
       </c>
       <c r="AI295" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82", "90+1"]</t>
         </is>
       </c>
       <c r="AJ295">
@@ -48473,28 +48473,28 @@
         <v>0</v>
       </c>
       <c r="AM295">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN295">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO295">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP295">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ295">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR295">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS295">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT295">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
@@ -48534,36 +48534,36 @@
         </is>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I296">
         <v>0</v>
       </c>
       <c r="J296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L296">
         <v>0</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N296">
         <v>1.75</v>
       </c>
       <c r="O296">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P296">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="Q296">
         <v>2.33</v>
@@ -48578,13 +48578,13 @@
         <v>2.85</v>
       </c>
       <c r="U296">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V296">
         <v>1.42</v>
       </c>
       <c r="W296">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X296">
         <v>1.03</v>
@@ -48602,7 +48602,7 @@
         <v>1.83</v>
       </c>
       <c r="AC296">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="AD296">
         <v>1.29</v>
@@ -48611,19 +48611,19 @@
         <v>1.11</v>
       </c>
       <c r="AF296">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG296">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68", "90"]</t>
         </is>
       </c>
       <c r="AI296" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "12"]</t>
         </is>
       </c>
       <c r="AJ296">
@@ -48636,28 +48636,28 @@
         <v>0</v>
       </c>
       <c r="AM296">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN296">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO296">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP296">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ296">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AR296">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS296">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT296">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
@@ -48697,13 +48697,13 @@
         </is>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H297">
         <v>0</v>
       </c>
       <c r="I297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J297">
         <v>0</v>
@@ -48716,7 +48716,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N297">
@@ -48781,7 +48781,7 @@
       </c>
       <c r="AH297" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI297" t="inlineStr">
@@ -48799,28 +48799,28 @@
         <v>0</v>
       </c>
       <c r="AM297">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN297">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO297">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP297">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ297">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR297">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS297">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT297">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
@@ -48860,26 +48860,26 @@
         </is>
       </c>
       <c r="G298">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H298">
         <v>0</v>
       </c>
       <c r="I298">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J298">
         <v>0</v>
       </c>
       <c r="K298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L298">
         <v>0</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N298">
@@ -48944,7 +48944,7 @@
       </c>
       <c r="AH298" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "20", "35", "40", "45+1", "88"]</t>
         </is>
       </c>
       <c r="AI298" t="inlineStr">
@@ -48962,28 +48962,28 @@
         <v>0</v>
       </c>
       <c r="AM298">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN298">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO298">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP298">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ298">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AR298">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AS298">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT298">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
@@ -49023,26 +49023,26 @@
         </is>
       </c>
       <c r="G299">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J299">
         <v>0</v>
       </c>
       <c r="K299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N299">
@@ -49107,12 +49107,12 @@
       </c>
       <c r="AH299" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "50"]</t>
         </is>
       </c>
       <c r="AI299" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ299">
@@ -49125,28 +49125,28 @@
         <v>0</v>
       </c>
       <c r="AM299">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN299">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO299">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP299">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ299">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR299">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS299">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT299">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
@@ -49186,26 +49186,26 @@
         </is>
       </c>
       <c r="G300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I300">
         <v>0</v>
       </c>
       <c r="J300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N300">
@@ -49270,12 +49270,12 @@
       </c>
       <c r="AH300" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI300" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "72"]</t>
         </is>
       </c>
       <c r="AJ300">
@@ -49288,28 +49288,28 @@
         <v>0</v>
       </c>
       <c r="AM300">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN300">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO300">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP300">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ300">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR300">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS300">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT300">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
@@ -49368,7 +49368,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N301">
@@ -49469,10 +49469,10 @@
         <v>0</v>
       </c>
       <c r="AS301">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT301">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
@@ -49512,26 +49512,26 @@
         </is>
       </c>
       <c r="G302">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H302">
         <v>0</v>
       </c>
       <c r="I302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302">
         <v>0</v>
       </c>
       <c r="K302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L302">
         <v>0</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N302">
@@ -49596,7 +49596,7 @@
       </c>
       <c r="AH302" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "74"]</t>
         </is>
       </c>
       <c r="AI302" t="inlineStr">
@@ -49614,28 +49614,28 @@
         <v>0</v>
       </c>
       <c r="AM302">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN302">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO302">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP302">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ302">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR302">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS302">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT302">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
@@ -49675,66 +49675,66 @@
         </is>
       </c>
       <c r="G303">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303">
         <v>0</v>
       </c>
       <c r="K303">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N303">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O303">
         <v>3.3</v>
       </c>
       <c r="P303">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="Q303">
         <v>3.1</v>
       </c>
       <c r="R303">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S303">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T303">
         <v>3.3</v>
       </c>
       <c r="U303">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V303">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W303">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X303">
         <v>1.01</v>
       </c>
       <c r="Y303">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="Z303">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA303">
         <v>1.65</v>
@@ -49743,62 +49743,62 @@
         <v>2.1</v>
       </c>
       <c r="AC303">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD303">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE303">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF303">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG303">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "50", "56"]</t>
         </is>
       </c>
       <c r="AI303" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AJ303">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK303">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL303">
         <v>0</v>
       </c>
       <c r="AM303">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN303">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO303">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP303">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ303">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR303">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS303">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT303">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>0</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I304">
         <v>0</v>
@@ -49853,11 +49853,11 @@
         <v>0</v>
       </c>
       <c r="L304">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N304">
@@ -49927,7 +49927,7 @@
       </c>
       <c r="AI304" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84", "90", "90+5"]</t>
         </is>
       </c>
       <c r="AJ304">
@@ -49940,28 +49940,28 @@
         <v>0</v>
       </c>
       <c r="AM304">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN304">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO304">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP304">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ304">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR304">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS304">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT304">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G305">
@@ -50020,23 +50020,23 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N305">
+        <v>3.3</v>
+      </c>
+      <c r="O305">
+        <v>2.85</v>
+      </c>
+      <c r="P305">
+        <v>2.05</v>
+      </c>
+      <c r="Q305">
+        <v>4.2</v>
+      </c>
+      <c r="R305">
         <v>1.95</v>
-      </c>
-      <c r="O305">
-        <v>3.1</v>
-      </c>
-      <c r="P305">
-        <v>3.65</v>
-      </c>
-      <c r="Q305">
-        <v>2.4</v>
-      </c>
-      <c r="R305">
-        <v>2.05</v>
       </c>
       <c r="S305">
         <v>1.44</v>
@@ -50045,43 +50045,43 @@
         <v>2.63</v>
       </c>
       <c r="U305">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V305">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W305">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X305">
         <v>1.08</v>
       </c>
       <c r="Y305">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z305">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AA305">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AB305">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AC305">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AD305">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE305">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF305">
         <v>1.95</v>
       </c>
       <c r="AG305">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,37 +50094,37 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK305">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AL305">
         <v>0</v>
       </c>
       <c r="AM305">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN305">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO305">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP305">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ305">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR305">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS305">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT305">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
@@ -50164,10 +50164,10 @@
         </is>
       </c>
       <c r="G306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H306">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I306">
         <v>0</v>
@@ -50176,14 +50176,14 @@
         <v>0</v>
       </c>
       <c r="K306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L306">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N306">
@@ -50248,12 +50248,12 @@
       </c>
       <c r="AH306" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AI306" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90", "90+4"]</t>
         </is>
       </c>
       <c r="AJ306">
@@ -50266,28 +50266,28 @@
         <v>0</v>
       </c>
       <c r="AM306">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN306">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO306">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP306">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ306">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR306">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS306">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT306">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU306" t="inlineStr">
         <is>
@@ -50318,25 +50318,25 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G307">
         <v>0</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I307">
         <v>0</v>
       </c>
       <c r="J307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K307">
         <v>0</v>
@@ -50346,23 +50346,23 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N307">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="O307">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P307">
+        <v>3.65</v>
+      </c>
+      <c r="Q307">
+        <v>2.4</v>
+      </c>
+      <c r="R307">
         <v>2.05</v>
-      </c>
-      <c r="Q307">
-        <v>4.2</v>
-      </c>
-      <c r="R307">
-        <v>1.95</v>
       </c>
       <c r="S307">
         <v>1.44</v>
@@ -50371,43 +50371,43 @@
         <v>2.63</v>
       </c>
       <c r="U307">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V307">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W307">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X307">
         <v>1.08</v>
       </c>
       <c r="Y307">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z307">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA307">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB307">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC307">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD307">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE307">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF307">
         <v>1.95</v>
       </c>
       <c r="AG307">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50416,41 +50416,41 @@
       </c>
       <c r="AI307" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AJ307">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK307">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AL307">
         <v>0</v>
       </c>
       <c r="AM307">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN307">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO307">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP307">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ307">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR307">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS307">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT307">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU307" t="inlineStr">
         <is>
@@ -50490,26 +50490,26 @@
         </is>
       </c>
       <c r="G308">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H308">
         <v>0</v>
       </c>
       <c r="I308">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J308">
         <v>0</v>
       </c>
       <c r="K308">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L308">
         <v>0</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N308">
@@ -50574,7 +50574,7 @@
       </c>
       <c r="AH308" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "45+7", "57", "62"]</t>
         </is>
       </c>
       <c r="AI308" t="inlineStr">
@@ -50592,28 +50592,28 @@
         <v>0</v>
       </c>
       <c r="AM308">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN308">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO308">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP308">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ308">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR308">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS308">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT308">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU308" t="inlineStr">
         <is>
@@ -50653,13 +50653,13 @@
         </is>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H309">
         <v>0</v>
       </c>
       <c r="I309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -50672,14 +50672,14 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N309">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O309">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P309">
         <v>4</v>
@@ -50688,19 +50688,19 @@
         <v>2.6</v>
       </c>
       <c r="R309">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S309">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="T309">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U309">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V309">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W309">
         <v>1.03</v>
@@ -50715,7 +50715,7 @@
         <v>2.5</v>
       </c>
       <c r="AA309">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AB309">
         <v>1.47</v>
@@ -50724,7 +50724,7 @@
         <v>5</v>
       </c>
       <c r="AD309">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE309">
         <v>1.01</v>
@@ -50733,50 +50733,50 @@
         <v>2.2</v>
       </c>
       <c r="AG309">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
+          <t>["39"]</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI309" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ309">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK309">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL309">
         <v>0</v>
       </c>
       <c r="AM309">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN309">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO309">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP309">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ309">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR309">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS309">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT309">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU309" t="inlineStr">
         <is>
@@ -50816,36 +50816,36 @@
         </is>
       </c>
       <c r="G310">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J310">
         <v>0</v>
       </c>
       <c r="K310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N310">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O310">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P310">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="Q310">
         <v>2.75</v>
@@ -50860,7 +50860,7 @@
         <v>2.7</v>
       </c>
       <c r="U310">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="V310">
         <v>1.35</v>
@@ -50875,13 +50875,13 @@
         <v>1.33</v>
       </c>
       <c r="Z310">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA310">
         <v>2.08</v>
       </c>
       <c r="AB310">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC310">
         <v>3.5</v>
@@ -50900,46 +50900,46 @@
       </c>
       <c r="AH310" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "84"]</t>
         </is>
       </c>
       <c r="AI310" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AJ310">
         <v>1.3</v>
       </c>
       <c r="AK310">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AL310">
         <v>0</v>
       </c>
       <c r="AM310">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN310">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO310">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP310">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ310">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR310">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS310">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT310">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU310" t="inlineStr">
         <is>
@@ -50979,10 +50979,10 @@
         </is>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I311">
         <v>0</v>
@@ -50991,24 +50991,24 @@
         <v>0</v>
       </c>
       <c r="K311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N311">
-        <v>5.85</v>
+        <v>6.24</v>
       </c>
       <c r="O311">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="P311">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Q311">
         <v>6</v>
@@ -51017,25 +51017,25 @@
         <v>2.3</v>
       </c>
       <c r="S311">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T311">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U311">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="V311">
         <v>1.48</v>
       </c>
       <c r="W311">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X311">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y311">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z311">
         <v>4.1</v>
@@ -51056,53 +51056,53 @@
         <v>1.13</v>
       </c>
       <c r="AF311">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG311">
         <v>1.87</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI311" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ311">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AK311">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL311">
         <v>0</v>
       </c>
       <c r="AM311">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN311">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO311">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP311">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ311">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR311">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS311">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT311">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU311" t="inlineStr">
         <is>
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O312">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="P312">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q312">
         <v>1.85</v>
@@ -51186,16 +51186,16 @@
         <v>3.3</v>
       </c>
       <c r="U312">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V312">
         <v>1.42</v>
       </c>
       <c r="W312">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X312">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y312">
         <v>1.3</v>
@@ -51219,7 +51219,7 @@
         <v>1.09</v>
       </c>
       <c r="AF312">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG312">
         <v>1.68</v>
@@ -51331,10 +51331,10 @@
         <v>1.4</v>
       </c>
       <c r="O313">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P313">
-        <v>6.72</v>
+        <v>6.84</v>
       </c>
       <c r="Q313">
         <v>1.8</v>
@@ -51349,16 +51349,16 @@
         <v>3.4</v>
       </c>
       <c r="U313">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="V313">
         <v>1.55</v>
       </c>
       <c r="W313">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X313">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y313">
         <v>1.18</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="O314">
         <v>3.2</v>
       </c>
       <c r="P314">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q314">
         <v>2.75</v>
@@ -51509,13 +51509,13 @@
         <v>1.47</v>
       </c>
       <c r="T314">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="U314">
         <v>3.2</v>
       </c>
       <c r="V314">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W314">
         <v>1.03</v>
@@ -51533,7 +51533,7 @@
         <v>2.2</v>
       </c>
       <c r="AB314">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC314">
         <v>4.5</v>
@@ -51669,7 +51669,7 @@
         <v>1.98</v>
       </c>
       <c r="S315">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T315">
         <v>2.14</v>
@@ -51678,7 +51678,7 @@
         <v>3.6</v>
       </c>
       <c r="V315">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W315">
         <v>1.01</v>
@@ -51693,7 +51693,7 @@
         <v>2.48</v>
       </c>
       <c r="AA315">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AB315">
         <v>1.4</v>
@@ -51702,7 +51702,7 @@
         <v>6</v>
       </c>
       <c r="AD315">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE315">
         <v>1.03</v>
@@ -51724,7 +51724,7 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK315">
         <v>1.58</v>
@@ -51933,12 +51933,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G317">
@@ -51980,64 +51980,64 @@
         </is>
       </c>
       <c r="N317">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="O317">
-        <v>2.6</v>
+        <v>3.76</v>
       </c>
       <c r="P317">
-        <v>3.1</v>
+        <v>4.31</v>
       </c>
       <c r="Q317">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R317">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="S317">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T317">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="U317">
-        <v>3.15</v>
+        <v>2.26</v>
       </c>
       <c r="V317">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="W317">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X317">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y317">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="Z317">
-        <v>2.58</v>
+        <v>4.3</v>
       </c>
       <c r="AA317">
-        <v>2.34</v>
+        <v>1.54</v>
       </c>
       <c r="AB317">
+        <v>2.2</v>
+      </c>
+      <c r="AC317">
+        <v>2.35</v>
+      </c>
+      <c r="AD317">
+        <v>1.48</v>
+      </c>
+      <c r="AE317">
+        <v>1.16</v>
+      </c>
+      <c r="AF317">
         <v>1.58</v>
       </c>
-      <c r="AC317">
-        <v>4.8</v>
-      </c>
-      <c r="AD317">
-        <v>1.15</v>
-      </c>
-      <c r="AE317">
-        <v>1.05</v>
-      </c>
-      <c r="AF317">
-        <v>1.87</v>
-      </c>
       <c r="AG317">
-        <v>1.77</v>
+        <v>2.19</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK317">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52084,7 +52084,7 @@
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>2026-09-13 18:30:00</t>
+          <t>2026-09-13 18:15:00</t>
         </is>
       </c>
     </row>
@@ -52101,7 +52101,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,64 +52143,64 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O318">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="P318">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="Q318">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R318">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S318">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="T318">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="U318">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="V318">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="W318">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X318">
+        <v>1.06</v>
+      </c>
+      <c r="Y318">
+        <v>1.43</v>
+      </c>
+      <c r="Z318">
+        <v>2.58</v>
+      </c>
+      <c r="AA318">
+        <v>2.33</v>
+      </c>
+      <c r="AB318">
+        <v>1.53</v>
+      </c>
+      <c r="AC318">
+        <v>4.8</v>
+      </c>
+      <c r="AD318">
+        <v>1.15</v>
+      </c>
+      <c r="AE318">
         <v>1.01</v>
       </c>
-      <c r="Y318">
-        <v>1.2</v>
-      </c>
-      <c r="Z318">
-        <v>4.6</v>
-      </c>
-      <c r="AA318">
-        <v>1.59</v>
-      </c>
-      <c r="AB318">
-        <v>2.17</v>
-      </c>
-      <c r="AC318">
-        <v>2.35</v>
-      </c>
-      <c r="AD318">
-        <v>1.48</v>
-      </c>
-      <c r="AE318">
-        <v>1.16</v>
-      </c>
       <c r="AF318">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AG318">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK318">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52327,13 +52327,13 @@
         <v>2.38</v>
       </c>
       <c r="U319">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="V319">
         <v>1.22</v>
       </c>
       <c r="W319">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X319">
         <v>1.12</v>
@@ -52345,16 +52345,16 @@
         <v>2.5</v>
       </c>
       <c r="AA319">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB319">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC319">
-        <v>6</v>
+        <v>5.61</v>
       </c>
       <c r="AD319">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE319">
         <v>1.03</v>
@@ -52958,80 +52958,80 @@
         </is>
       </c>
       <c r="N323">
-        <v>4.34</v>
+        <v>4.25</v>
       </c>
       <c r="O323">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P323">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q323">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="R323">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S323">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T323">
         <v>3.28</v>
       </c>
       <c r="U323">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V323">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W323">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X323">
         <v>1.01</v>
       </c>
       <c r="Y323">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z323">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA323">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB323">
         <v>2.25</v>
       </c>
       <c r="AC323">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AD323">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE323">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF323">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG323">
+        <v>2.1</v>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ323">
         <v>2.2</v>
       </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI323" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ323">
-        <v>1.25</v>
-      </c>
       <c r="AK323">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53290,7 +53290,7 @@
         <v>3.2</v>
       </c>
       <c r="P325">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q325">
         <v>2.85</v>
@@ -53299,7 +53299,7 @@
         <v>2.12</v>
       </c>
       <c r="S325">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T325">
         <v>3</v>
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O326">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P326">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q326">
         <v>2.15</v>
@@ -53465,16 +53465,16 @@
         <v>1.42</v>
       </c>
       <c r="T326">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U326">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V326">
         <v>1.35</v>
       </c>
       <c r="W326">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X326">
         <v>1.05</v>
@@ -53486,13 +53486,13 @@
         <v>2.95</v>
       </c>
       <c r="AA326">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AB326">
         <v>1.65</v>
       </c>
       <c r="AC326">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD326">
         <v>1.2</v>
@@ -53501,7 +53501,7 @@
         <v>1.06</v>
       </c>
       <c r="AF326">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AG326">
         <v>1.7</v>
@@ -53517,7 +53517,7 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK326">
         <v>2.1</v>
@@ -53610,19 +53610,19 @@
         </is>
       </c>
       <c r="N327">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="O327">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P327">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q327">
         <v>3.95</v>
       </c>
       <c r="R327">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S327">
         <v>1.33</v>
@@ -53634,7 +53634,7 @@
         <v>2.45</v>
       </c>
       <c r="V327">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W327">
         <v>1.08</v>
@@ -53649,19 +53649,19 @@
         <v>3.4</v>
       </c>
       <c r="AA327">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB327">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC327">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD327">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE327">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF327">
         <v>1.67</v>
@@ -53680,7 +53680,7 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK327">
         <v>1.3</v>
@@ -53794,13 +53794,13 @@
         <v>4.8</v>
       </c>
       <c r="U328">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V328">
         <v>1.8</v>
       </c>
       <c r="W328">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X328">
         <v>1.01</v>
@@ -53936,25 +53936,25 @@
         </is>
       </c>
       <c r="N329">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O329">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P329">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q329">
         <v>4.75</v>
       </c>
       <c r="R329">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S329">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T329">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U329">
         <v>2.08</v>
@@ -53972,13 +53972,13 @@
         <v>1.1</v>
       </c>
       <c r="Z329">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA329">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB329">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC329">
         <v>2.04</v>
@@ -53990,10 +53990,10 @@
         <v>1.3</v>
       </c>
       <c r="AF329">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG329">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK329">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL329">
         <v>0</v>
